--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53 UTC</t>
+          <t>2026-09-13 16:34:08 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3110,7 +3110,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:18:53</t>
+          <t>2026-09-13 16:34:08</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08 UTC</t>
+          <t>2026-09-13 18:58:25 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3110,7 +3110,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 16:34:08</t>
+          <t>2026-09-13 18:58:25</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25 UTC</t>
+          <t>2026-09-13 21:23:46 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3110,7 +3110,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:58:25</t>
+          <t>2026-09-13 21:23:46</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46 UTC</t>
+          <t>2026-09-13 23:20:44 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3110,7 +3110,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 21:23:46</t>
+          <t>2026-09-13 23:20:44</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44 UTC</t>
+          <t>2026-09-14 01:24:10 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3110,7 +3110,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 23:20:44</t>
+          <t>2026-09-14 01:24:10</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10 UTC</t>
+          <t>2026-09-14 06:47:05 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>42d7c1bc5ee14bec61656a510b7fb694ee3db71d</t>
+          <t>2627701770d3c2525e8f70378fce09e9c1722e18</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
@@ -3110,7 +3110,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:24:10</t>
+          <t>2026-09-14 06:47:05</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>42d7c1bc5ee14bec61656a510b7fb694ee3db71d</t>
+          <t>2627701770d3c2525e8f70378fce09e9c1722e18</t>
         </is>
       </c>
     </row>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P2" headerRowCount="1">
-  <autoFilter ref="A1:P2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P14" headerRowCount="1">
+  <autoFilter ref="A1:P14"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 13:42:11 UTC</t>
+          <t>2026-09-14 14:57:56 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -772,80 +772,1040 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>cusat-admission-2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>cusat-admission-2026.html</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>cusat-btech-2026</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>cusat-btech-2026.html</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>cusat-campus-hostel</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>cusat-campus-hostel.html</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>cusat-fees-scholarships-2026</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>cusat-fees-scholarships-2026.html</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>cusat-kochi</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>cusat-kochi.html</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>cusat-law-2026</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>cusat-law-2026.html</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>cusat-mba-2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>cusat-mba-2026.html</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>cusat-mca-2026</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>cusat-mca-2026.html</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>cusat-placements-2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>cusat-placements-2026.html</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>cusat-science-marine-2026</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>cusat-science-marine-2026.html</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>iit-kanpur</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>iit-kanpur.html</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>siom-nashik</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>siom-nashik.html</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>sitm-pune</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>sitm-pune.html</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>2627701770d3c2525e8f70378fce09e9c1722e18</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
         <v>75</v>
       </c>
     </row>
@@ -1224,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1270,32 +2230,416 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 13:42:11</t>
+          <t>2026-09-14 14:57:56</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>cusat-admission-2026</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>cusat-admission-2026.html</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>cusat-btech-2026</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>cusat-btech-2026.html</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>cusat-campus-hostel</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>cusat-campus-hostel.html</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>cusat-fees-scholarships-2026</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>cusat-fees-scholarships-2026.html</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>cusat-kochi</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>cusat-kochi.html</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>cusat-law-2026</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>cusat-law-2026.html</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>cusat-mba-2026</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>cusat-mba-2026.html</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>cusat-mca-2026</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>cusat-mca-2026.html</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>cusat-placements-2026</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>cusat-placements-2026.html</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>cusat-science-marine-2026</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>cusat-science-marine-2026.html</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>iit-kanpur</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>iit-kanpur.html</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>siom-nashik</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>siom-nashik.html</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:56</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>sitm-pune</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>sitm-pune.html</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2627701770d3c2525e8f70378fce09e9c1722e18</t>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
         </is>
       </c>
     </row>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56 UTC</t>
+          <t>2026-09-14 15:00:56 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -1600,9 +1600,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1642,11 +1642,11 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>66f5dbdf2deac50e8f27c8342c6761b12f179882</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -2230,7 +2230,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2294,7 +2294,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2358,7 +2358,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2422,7 +2422,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2454,7 +2454,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2486,7 +2486,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2550,7 +2550,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2575,14 +2575,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>66f5dbdf2deac50e8f27c8342c6761b12f179882</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2614,7 +2614,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:56</t>
+          <t>2026-09-14 15:00:56</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56 UTC</t>
+          <t>2026-09-14 15:01:53 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2230,7 +2230,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2294,7 +2294,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2358,7 +2358,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2422,7 +2422,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2454,7 +2454,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2486,7 +2486,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2550,7 +2550,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2582,7 +2582,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2614,7 +2614,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:56</t>
+          <t>2026-09-14 15:01:53</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P14" headerRowCount="1">
-  <autoFilter ref="A1:P14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P15" headerRowCount="1">
+  <autoFilter ref="A1:P15"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,15 +580,15 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53 UTC</t>
+          <t>2026-09-14 16:18:36 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1572,27 +1572,27 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur</t>
+          <t>iit-kanpur-placements</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur.html</t>
+          <t>iit-kanpur-placements.html</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>IN QUEUE</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Awaiting audit</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1605,19 +1605,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1637,27 +1637,25 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Awaiting benchmark-level verification.</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>66f5dbdf2deac50e8f27c8342c6761b12f179882</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>90</v>
-      </c>
+          <t>804a35f87f30962853917dd88ed3c44e1d8f62b9</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik</t>
+          <t>iit-kanpur</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik.html</t>
+          <t>iit-kanpur.html</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1665,14 +1663,14 @@
           <t>Overview</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>IN QUEUE</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Awaiting audit</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1680,24 +1678,24 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1717,95 +1715,173 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Awaiting benchmark-level verification.</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>87</v>
-      </c>
+          <t>b9b7c08d3f2b4706056de67f43526c5319e0e342</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>siom-nashik</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>siom-nashik.html</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>sitm-pune</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>sitm-pune.html</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
         </is>
       </c>
-      <c r="P14" s="3" t="n">
+      <c r="P15" s="3" t="n">
         <v>75</v>
       </c>
     </row>
@@ -2184,7 +2260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2230,7 +2306,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2262,7 +2338,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2294,7 +2370,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2326,7 +2402,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2358,7 +2434,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2390,7 +2466,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2422,7 +2498,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2454,7 +2530,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2486,7 +2562,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2518,7 +2594,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2550,94 +2626,126 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur</t>
+          <t>iit-kanpur-placements</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur.html</t>
+          <t>iit-kanpur-placements.html</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>AUDITED</t>
+          <t>IN QUEUE</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>AUDITED – NO CHANGE</t>
+          <t>Awaiting audit</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>66f5dbdf2deac50e8f27c8342c6761b12f179882</t>
+          <t>804a35f87f30962853917dd88ed3c44e1d8f62b9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik</t>
+          <t>iit-kanpur</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik.html</t>
+          <t>iit-kanpur.html</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>AUDITED</t>
+          <t>IN QUEUE</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>AUDITED – NO CHANGE</t>
+          <t>Awaiting audit</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>b9b7c08d3f2b4706056de67f43526c5319e0e342</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 15:01:53</t>
+          <t>2026-09-14 16:18:36</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>siom-nashik</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>siom-nashik.html</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:18:36</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t>sitm-pune</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>sitm-pune.html</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P15" headerRowCount="1">
-  <autoFilter ref="A1:P15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P16" headerRowCount="1">
+  <autoFilter ref="A1:P16"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36 UTC</t>
+          <t>2026-09-14 16:38:17 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1883,6 +1883,86 @@
       </c>
       <c r="P15" s="3" t="n">
         <v>75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>top-mba-colleges-in-india</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>top-mba-colleges-in-india.html</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2260,7 +2340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2306,7 +2386,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2331,14 +2411,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2363,14 +2443,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2395,14 +2475,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2427,14 +2507,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2459,14 +2539,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2491,14 +2571,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2523,14 +2603,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2555,14 +2635,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2587,14 +2667,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2619,14 +2699,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2658,7 +2738,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2690,7 +2770,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2722,7 +2802,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:18:36</t>
+          <t>2026-09-14 16:38:17</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2748,6 +2828,38 @@
       <c r="F15" s="3" t="inlineStr">
         <is>
           <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:38:17</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>top-mba-colleges-in-india</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>top-mba-colleges-in-india.html</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
         </is>
       </c>
     </row>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P16" headerRowCount="1">
-  <autoFilter ref="A1:P16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P18" headerRowCount="1">
+  <autoFilter ref="A1:P18"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17 UTC</t>
+          <t>2026-09-14 16:53:56 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1728,12 +1728,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik</t>
+          <t>mba-college-fees</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik.html</t>
+          <t>mba-college-fees.html</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1756,9 +1756,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1798,27 +1798,27 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>sitm-pune</t>
+          <t>mba-colleges-by-exam</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>sitm-pune.html</t>
+          <t>mba-colleges-by-exam.html</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1836,9 +1836,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1878,90 +1878,250 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>siom-nashik</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>siom-nashik.html</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>sitm-pune</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>sitm-pune.html</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>top-mba-colleges-in-india</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>top-mba-colleges-in-india.html</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Course-specific</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
         </is>
       </c>
-      <c r="P16" s="3" t="n">
+      <c r="P18" s="3" t="n">
         <v>88</v>
       </c>
     </row>
@@ -2340,7 +2500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2386,7 +2546,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2411,14 +2571,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2443,14 +2603,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2475,14 +2635,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2507,14 +2667,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2539,14 +2699,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2571,14 +2731,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2603,14 +2763,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2635,14 +2795,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2667,14 +2827,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2699,14 +2859,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>3ea262439cc3c9d4c3979fdca30db1b7d0596298</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2738,7 +2898,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2770,17 +2930,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik</t>
+          <t>mba-college-fees</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik.html</t>
+          <t>mba-college-fees.html</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2795,24 +2955,24 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>sitm-pune</t>
+          <t>mba-colleges-by-exam</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>sitm-pune.html</t>
+          <t>mba-colleges-by-exam.html</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2827,37 +2987,101 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:38:17</t>
+          <t>2026-09-14 16:53:56</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>siom-nashik</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>siom-nashik.html</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:53:56</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>sitm-pune</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>sitm-pune.html</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:53:56</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>top-mba-colleges-in-india</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>top-mba-colleges-in-india.html</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P18" headerRowCount="1">
-  <autoFilter ref="A1:P18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P19" headerRowCount="1">
+  <autoFilter ref="A1:P19"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56 UTC</t>
+          <t>2026-09-14 18:53:41 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1761,19 +1761,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1841,19 +1841,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1888,17 +1888,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik</t>
+          <t>mba-colleges-by-location</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik.html</t>
+          <t>mba-colleges-by-location.html</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1916,24 +1916,24 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -1953,27 +1953,27 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 1 issue group(s)</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>44593444817ff5bdcd75b0b271e5cc3db6591cff</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>sitm-pune</t>
+          <t>siom-nashik</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>sitm-pune.html</t>
+          <t>siom-nashik.html</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2001,19 +2001,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2042,86 +2042,166 @@
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>sitm-pune</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>sitm-pune.html</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>top-mba-colleges-in-india</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>top-mba-colleges-in-india.html</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Course-specific</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
         </is>
       </c>
-      <c r="P18" s="3" t="n">
+      <c r="P19" s="3" t="n">
         <v>88</v>
       </c>
     </row>
@@ -2500,7 +2580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2546,7 +2626,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2571,14 +2651,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2603,14 +2683,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2635,14 +2715,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2667,14 +2747,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2699,14 +2779,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2731,14 +2811,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2763,14 +2843,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2795,14 +2875,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2827,14 +2907,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2859,14 +2939,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2898,7 +2978,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2930,7 +3010,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2962,7 +3042,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2994,17 +3074,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik</t>
+          <t>mba-colleges-by-location</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>siom-nashik.html</t>
+          <t>mba-colleges-by-location.html</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3019,24 +3099,24 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+          <t>44593444817ff5bdcd75b0b271e5cc3db6591cff</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>sitm-pune</t>
+          <t>siom-nashik</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>sitm-pune.html</t>
+          <t>siom-nashik.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3058,30 +3138,62 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:53:56</t>
+          <t>2026-09-14 18:53:41</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>sitm-pune</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>sitm-pune.html</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:53:41</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>top-mba-colleges-in-india</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>top-mba-colleges-in-india.html</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41 UTC</t>
+          <t>2026-09-14 22:17:47 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2626,7 +2626,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2658,7 +2658,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2818,7 +2818,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2882,7 +2882,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2946,7 +2946,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3042,7 +3042,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3138,7 +3138,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 18:53:41</t>
+          <t>2026-09-14 22:17:47</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47 UTC</t>
+          <t>2026-09-15 00:48:09 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2626,7 +2626,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2658,7 +2658,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2818,7 +2818,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2882,7 +2882,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2946,7 +2946,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3042,7 +3042,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3138,7 +3138,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 22:17:47</t>
+          <t>2026-09-15 00:48:09</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09 UTC</t>
+          <t>2026-09-15 05:55:05 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2626,7 +2626,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2658,7 +2658,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2818,7 +2818,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2882,7 +2882,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2946,7 +2946,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3042,7 +3042,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3138,7 +3138,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:48:09</t>
+          <t>2026-09-15 05:55:05</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05 UTC</t>
+          <t>2026-09-15 11:14:54 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 1 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>44593444817ff5bdcd75b0b271e5cc3db6591cff</t>
+          <t>5513862df5ae7fbad8da05f206286eafe5871f7f</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -2626,7 +2626,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2651,14 +2651,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2683,14 +2683,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2715,14 +2715,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2747,14 +2747,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2779,14 +2779,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2811,14 +2811,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2843,14 +2843,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2875,14 +2875,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2907,14 +2907,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2939,14 +2939,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>bc083c30aa02176f5fa5d6e6d9d7cbc41cdb6078</t>
+          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3042,7 +3042,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3099,14 +3099,14 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>44593444817ff5bdcd75b0b271e5cc3db6591cff</t>
+          <t>5513862df5ae7fbad8da05f206286eafe5871f7f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3138,7 +3138,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 05:55:05</t>
+          <t>2026-09-15 11:14:54</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54 UTC</t>
+          <t>2026-09-15 11:23:38 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1761,19 +1761,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1841,19 +1841,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1921,19 +1921,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -2001,19 +2001,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2081,19 +2081,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2161,19 +2161,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2626,7 +2626,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2658,7 +2658,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2818,7 +2818,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2882,7 +2882,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2946,7 +2946,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3042,7 +3042,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3138,7 +3138,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:14:54</t>
+          <t>2026-09-15 11:23:38</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38 UTC</t>
+          <t>2026-09-15 11:24:51 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2626,7 +2626,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2658,7 +2658,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2818,7 +2818,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2882,7 +2882,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2946,7 +2946,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3042,7 +3042,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3138,7 +3138,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:23:38</t>
+          <t>2026-09-15 11:24:51</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51 UTC</t>
+          <t>2026-09-15 11:26:55 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1958,11 +1958,11 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>5513862df5ae7fbad8da05f206286eafe5871f7f</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -2626,7 +2626,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2651,14 +2651,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2683,14 +2683,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2715,14 +2715,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2747,14 +2747,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2779,14 +2779,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2811,14 +2811,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2843,14 +2843,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2875,14 +2875,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2907,14 +2907,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2939,14 +2939,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>a1fd4589d4c16c2c06ffa075f8923b117eb4bf86</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3042,7 +3042,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3099,14 +3099,14 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>5513862df5ae7fbad8da05f206286eafe5871f7f</t>
+          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3138,7 +3138,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:24:51</t>
+          <t>2026-09-15 11:26:55</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55 UTC</t>
+          <t>2026-09-15 11:29:53 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2626,7 +2626,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2658,7 +2658,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2818,7 +2818,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2882,7 +2882,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2946,7 +2946,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3042,7 +3042,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3138,7 +3138,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26:55</t>
+          <t>2026-09-15 11:29:53</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P19" headerRowCount="1">
-  <autoFilter ref="A1:P19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P15" headerRowCount="1">
+  <autoFilter ref="A1:P15"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,15 +580,15 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53 UTC</t>
+          <t>2026-09-15 15:36:09 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1572,27 +1572,27 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur-placements</t>
+          <t>mba-college-fees</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur-placements.html</t>
+          <t>mba-college-fees.html</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>IN QUEUE</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Awaiting audit</t>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1637,40 +1637,42 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Awaiting benchmark-level verification.</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>804a35f87f30962853917dd88ed3c44e1d8f62b9</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="n"/>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur</t>
+          <t>mba-colleges-by-exam</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur.html</t>
+          <t>mba-colleges-by-exam.html</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>IN QUEUE</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Awaiting audit</t>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1715,30 +1717,32 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Awaiting benchmark-level verification.</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>b9b7c08d3f2b4706056de67f43526c5319e0e342</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees</t>
+          <t>mba-colleges-by-location</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees.html</t>
+          <t>mba-colleges-by-location.html</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1761,19 +1765,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1793,27 +1797,27 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>3a252e780f95f6c57d4f991043d75977b8ad6e51</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-exam</t>
+          <t>top-mba-colleges-in-india</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-exam.html</t>
+          <t>top-mba-colleges-in-india.html</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1841,19 +1845,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1873,335 +1877,15 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location.html</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>siom-nashik</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>siom-nashik.html</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 3 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>sitm-pune</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>sitm-pune.html</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>top-mba-colleges-in-india</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>top-mba-colleges-in-india.html</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 3 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n">
         <v>88</v>
       </c>
     </row>
@@ -2580,7 +2264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2626,7 +2310,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2651,14 +2335,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2683,14 +2367,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2715,14 +2399,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2747,14 +2431,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2779,14 +2463,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2811,14 +2495,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2843,14 +2527,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2875,14 +2559,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2907,14 +2591,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2939,88 +2623,88 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
+          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur-placements</t>
+          <t>mba-college-fees</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur-placements.html</t>
+          <t>mba-college-fees.html</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>IN QUEUE</t>
+          <t>AUDITED</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Awaiting audit</t>
+          <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>804a35f87f30962853917dd88ed3c44e1d8f62b9</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur</t>
+          <t>mba-colleges-by-exam</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>iit-kanpur.html</t>
+          <t>mba-colleges-by-exam.html</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>IN QUEUE</t>
+          <t>AUDITED</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Awaiting audit</t>
+          <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>b9b7c08d3f2b4706056de67f43526c5319e0e342</t>
+          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees</t>
+          <t>mba-colleges-by-location</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees.html</t>
+          <t>mba-colleges-by-location.html</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3035,24 +2719,24 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>3a252e780f95f6c57d4f991043d75977b8ad6e51</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 11:29:53</t>
+          <t>2026-09-15 15:36:09</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-exam</t>
+          <t>top-mba-colleges-in-india</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-exam.html</t>
+          <t>top-mba-colleges-in-india.html</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3066,134 +2750,6 @@
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:29:53</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location.html</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>4c910f9f1bd088bdc9f047e9cc174046dac787f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:29:53</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>siom-nashik</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>siom-nashik.html</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:29:53</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>sitm-pune</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>sitm-pune.html</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>79a0773a7c0ab48f6ceb7f8030ec9021c4ffc56e</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:29:53</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>top-mba-colleges-in-india</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>top-mba-colleges-in-india.html</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P15" headerRowCount="1">
-  <autoFilter ref="A1:P15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P23" headerRowCount="1">
+  <autoFilter ref="A1:P23"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,15 +580,15 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09 UTC</t>
+          <t>2026-09-15 16:08:00 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1605,19 +1605,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1812,80 +1812,716 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>mba-colleges-in-ahmedabad</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-ahmedabad.html</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-bengaluru</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-bengaluru.html</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-chennai</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-chennai.html</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>IN QUEUE</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Awaiting audit</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Awaiting benchmark-level verification.</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>a6485668ef67b87541887d89a9aa11bee38233fc</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-delhi-ncr</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-delhi-ncr.html</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-hyderabad</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-hyderabad.html</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>IN QUEUE</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Awaiting audit</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Awaiting benchmark-level verification.</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>1faf47950e15979374c1b86658692571d7b4e128</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-kolkata</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-kolkata.html</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-mumbai</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-mumbai.html</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-pune</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-pune.html</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>top-mba-colleges-in-india</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>top-mba-colleges-in-india.html</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Course-specific</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
         </is>
       </c>
-      <c r="P15" s="3" t="n">
+      <c r="P23" s="3" t="n">
         <v>88</v>
       </c>
     </row>
@@ -2264,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2310,7 +2946,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2335,14 +2971,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2367,14 +3003,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2399,14 +3035,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2431,14 +3067,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2463,14 +3099,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2495,14 +3131,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2527,14 +3163,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2559,14 +3195,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2591,14 +3227,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2623,14 +3259,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>a5a840f0bb43e7db4db431f159878cf51920f763</t>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2662,7 +3298,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2694,7 +3330,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2726,30 +3362,286 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:36:09</t>
+          <t>2026-09-15 16:08:00</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>mba-colleges-in-ahmedabad</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-ahmedabad.html</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:08:00</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-bengaluru</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-bengaluru.html</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:08:00</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-chennai</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-chennai.html</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>IN QUEUE</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Awaiting audit</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>a6485668ef67b87541887d89a9aa11bee38233fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:08:00</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-delhi-ncr</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-delhi-ncr.html</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:08:00</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-hyderabad</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-hyderabad.html</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>IN QUEUE</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Awaiting audit</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>1faf47950e15979374c1b86658692571d7b4e128</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:08:00</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-kolkata</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-kolkata.html</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:08:00</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-mumbai</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-mumbai.html</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:08:00</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-pune</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-pune.html</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:08:00</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
           <t>top-mba-colleges-in-india</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>top-mba-colleges-in-india.html</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -584,11 +584,11 @@
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00 UTC</t>
+          <t>2026-09-15 16:08:55 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -1985,14 +1985,14 @@
           <t>Course-specific</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>IN QUEUE</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Awaiting audit</t>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2037,15 +2037,17 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Awaiting benchmark-level verification.</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>a6485668ef67b87541887d89a9aa11bee38233fc</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n"/>
+          <t>11f095916b85de75d64b3a813f9a86d7f334745d</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -2143,14 +2145,14 @@
           <t>Course-specific</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>IN QUEUE</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Awaiting audit</t>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -2163,19 +2165,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2195,15 +2197,17 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Awaiting benchmark-level verification.</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>1faf47950e15979374c1b86658692571d7b4e128</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n"/>
+          <t>11f095916b85de75d64b3a813f9a86d7f334745d</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -2946,7 +2950,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2978,7 +2982,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3010,7 +3014,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3042,7 +3046,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3074,7 +3078,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3106,7 +3110,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3138,7 +3142,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3170,7 +3174,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3202,7 +3206,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3234,7 +3238,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3266,7 +3270,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3298,7 +3302,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3330,7 +3334,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3362,7 +3366,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3394,7 +3398,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3426,7 +3430,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3441,24 +3445,24 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>IN QUEUE</t>
+          <t>AUDITED</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Awaiting audit</t>
+          <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>a6485668ef67b87541887d89a9aa11bee38233fc</t>
+          <t>11f095916b85de75d64b3a813f9a86d7f334745d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3490,7 +3494,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3505,24 +3509,24 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>IN QUEUE</t>
+          <t>AUDITED</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Awaiting audit</t>
+          <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>1faf47950e15979374c1b86658692571d7b4e128</t>
+          <t>11f095916b85de75d64b3a813f9a86d7f334745d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3554,7 +3558,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3586,7 +3590,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3618,7 +3622,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:00</t>
+          <t>2026-09-15 16:08:55</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P23" headerRowCount="1">
-  <autoFilter ref="A1:P23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P20" headerRowCount="1">
+  <autoFilter ref="A1:P20"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55 UTC</t>
+          <t>2026-09-15 17:09:58 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1572,17 +1572,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees</t>
+          <t>mba-colleges-by-location</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees.html</t>
+          <t>mba-colleges-by-location.html</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1637,27 +1637,27 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>1ae1717b9673012730eac8139d98dd21b9c7fa79</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-exam</t>
+          <t>mba-colleges-in-ahmedabad</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-exam.html</t>
+          <t>mba-colleges-in-ahmedabad.html</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1722,22 +1722,22 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-location</t>
+          <t>mba-colleges-in-bengaluru</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-location.html</t>
+          <t>mba-colleges-in-bengaluru.html</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>3a252e780f95f6c57d4f991043d75977b8ad6e51</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-ahmedabad</t>
+          <t>mba-colleges-in-chennai</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-ahmedabad.html</t>
+          <t>mba-colleges-in-chennai.html</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-bengaluru</t>
+          <t>mba-colleges-in-delhi-ncr</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-bengaluru.html</t>
+          <t>mba-colleges-in-delhi-ncr.html</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1962,22 +1962,22 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-chennai</t>
+          <t>mba-colleges-in-hyderabad</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-chennai.html</t>
+          <t>mba-colleges-in-hyderabad.html</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>11f095916b85de75d64b3a813f9a86d7f334745d</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
@@ -2052,12 +2052,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-delhi-ncr</t>
+          <t>mba-colleges-in-kolkata</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-delhi-ncr.html</t>
+          <t>mba-colleges-in-kolkata.html</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2122,22 +2122,22 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-hyderabad</t>
+          <t>mba-colleges-in-mumbai</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-hyderabad.html</t>
+          <t>mba-colleges-in-mumbai.html</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>11f095916b85de75d64b3a813f9a86d7f334745d</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
@@ -2212,12 +2212,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-kolkata</t>
+          <t>mba-colleges-in-pune</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-kolkata.html</t>
+          <t>mba-colleges-in-pune.html</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2282,251 +2282,11 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-mumbai</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-mumbai.html</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n">
         <v>80</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-pune</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-pune.html</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>top-mba-colleges-in-india</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>top-mba-colleges-in-india.html</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 3 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2904,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2950,7 +2710,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2975,14 +2735,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3007,14 +2767,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3039,14 +2799,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3071,14 +2831,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3103,14 +2863,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3135,14 +2895,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3167,14 +2927,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3199,14 +2959,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3231,14 +2991,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3263,24 +3023,24 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees</t>
+          <t>mba-colleges-by-location</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees.html</t>
+          <t>mba-colleges-by-location.html</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -3295,24 +3055,24 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>1ae1717b9673012730eac8139d98dd21b9c7fa79</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-exam</t>
+          <t>mba-colleges-in-ahmedabad</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-exam.html</t>
+          <t>mba-colleges-in-ahmedabad.html</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -3327,24 +3087,24 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>ff2637fffee7ede07aad9dca86b48f46c61ac47e</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-location</t>
+          <t>mba-colleges-in-bengaluru</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-location.html</t>
+          <t>mba-colleges-in-bengaluru.html</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3359,24 +3119,24 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>3a252e780f95f6c57d4f991043d75977b8ad6e51</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-ahmedabad</t>
+          <t>mba-colleges-in-chennai</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-ahmedabad.html</t>
+          <t>mba-colleges-in-chennai.html</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3391,24 +3151,24 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-bengaluru</t>
+          <t>mba-colleges-in-delhi-ncr</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-bengaluru.html</t>
+          <t>mba-colleges-in-delhi-ncr.html</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3423,24 +3183,24 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-chennai</t>
+          <t>mba-colleges-in-hyderabad</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-chennai.html</t>
+          <t>mba-colleges-in-hyderabad.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3455,24 +3215,24 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>11f095916b85de75d64b3a813f9a86d7f334745d</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-delhi-ncr</t>
+          <t>mba-colleges-in-kolkata</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-delhi-ncr.html</t>
+          <t>mba-colleges-in-kolkata.html</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -3487,24 +3247,24 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-hyderabad</t>
+          <t>mba-colleges-in-mumbai</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-hyderabad.html</t>
+          <t>mba-colleges-in-mumbai.html</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3519,24 +3279,24 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>11f095916b85de75d64b3a813f9a86d7f334745d</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:55</t>
+          <t>2026-09-15 17:09:58</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-kolkata</t>
+          <t>mba-colleges-in-pune</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-kolkata.html</t>
+          <t>mba-colleges-in-pune.html</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3551,103 +3311,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15 16:08:55</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-mumbai</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-mumbai.html</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15 16:08:55</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-pune</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-pune.html</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>73b8a80c680ffd6de056ffd2c734259a5a7e4e06</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15 16:08:55</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>top-mba-colleges-in-india</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>top-mba-colleges-in-india.html</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>80bd6091c4c6518a7b8568a0d0278893569bd181</t>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58 UTC</t>
+          <t>2026-09-15 17:19:23 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>1ae1717b9673012730eac8139d98dd21b9c7fa79</t>
+          <t>f1d2002bc4604f4b99ba72eaf7d39aa85df89cf3</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
@@ -2710,7 +2710,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2742,7 +2742,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2774,7 +2774,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2806,7 +2806,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2838,7 +2838,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2870,7 +2870,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2966,7 +2966,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2998,7 +2998,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>1ae1717b9673012730eac8139d98dd21b9c7fa79</t>
+          <t>f1d2002bc4604f4b99ba72eaf7d39aa85df89cf3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3158,7 +3158,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:58</t>
+          <t>2026-09-15 17:19:23</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P20" headerRowCount="1">
-  <autoFilter ref="A1:P20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P22" headerRowCount="1">
+  <autoFilter ref="A1:P22"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23 UTC</t>
+          <t>2026-09-15 18:15:20 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1572,17 +1572,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-location</t>
+          <t>mba-college-comparison</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-location.html</t>
+          <t>mba-college-comparison.html</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>f1d2002bc4604f4b99ba72eaf7d39aa85df89cf3</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-ahmedabad</t>
+          <t>mba-college-fees</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-ahmedabad.html</t>
+          <t>mba-college-fees.html</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>4030b3ab60bf099621625ae33d8902a993a35728</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
@@ -1732,12 +1732,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-bengaluru</t>
+          <t>mba-colleges-by-location</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-bengaluru.html</t>
+          <t>mba-colleges-by-location.html</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-chennai</t>
+          <t>mba-colleges-in-ahmedabad</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-chennai.html</t>
+          <t>mba-colleges-in-ahmedabad.html</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1886,18 +1886,18 @@
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-delhi-ncr</t>
+          <t>mba-colleges-in-bengaluru</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-delhi-ncr.html</t>
+          <t>mba-colleges-in-bengaluru.html</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1966,18 +1966,18 @@
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-hyderabad</t>
+          <t>mba-colleges-in-chennai</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-hyderabad.html</t>
+          <t>mba-colleges-in-chennai.html</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2052,12 +2052,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-kolkata</t>
+          <t>mba-colleges-in-delhi-ncr</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-kolkata.html</t>
+          <t>mba-colleges-in-delhi-ncr.html</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2126,18 +2126,18 @@
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-mumbai</t>
+          <t>mba-colleges-in-hyderabad</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-mumbai.html</t>
+          <t>mba-colleges-in-hyderabad.html</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2212,80 +2212,240 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>mba-colleges-in-kolkata</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-kolkata.html</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-mumbai</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-mumbai.html</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>mba-colleges-in-pune</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>mba-colleges-in-pune.html</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Course-specific</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="O22" s="3" t="inlineStr">
         <is>
           <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
-      <c r="P20" s="3" t="n">
+      <c r="P22" s="3" t="n">
         <v>80</v>
       </c>
     </row>
@@ -2664,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2710,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2735,14 +2895,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2767,14 +2927,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2799,14 +2959,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2831,14 +2991,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2863,14 +3023,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2895,14 +3055,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2927,14 +3087,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2959,14 +3119,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2991,14 +3151,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3023,24 +3183,24 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-location</t>
+          <t>mba-college-comparison</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-by-location.html</t>
+          <t>mba-college-comparison.html</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -3055,24 +3215,24 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>f1d2002bc4604f4b99ba72eaf7d39aa85df89cf3</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-ahmedabad</t>
+          <t>mba-college-fees</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-ahmedabad.html</t>
+          <t>mba-college-fees.html</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -3087,24 +3247,24 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>4030b3ab60bf099621625ae33d8902a993a35728</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-bengaluru</t>
+          <t>mba-colleges-by-location</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-bengaluru.html</t>
+          <t>mba-colleges-by-location.html</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3119,24 +3279,24 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-chennai</t>
+          <t>mba-colleges-in-ahmedabad</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-chennai.html</t>
+          <t>mba-colleges-in-ahmedabad.html</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3158,17 +3318,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-delhi-ncr</t>
+          <t>mba-colleges-in-bengaluru</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-delhi-ncr.html</t>
+          <t>mba-colleges-in-bengaluru.html</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3190,17 +3350,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-hyderabad</t>
+          <t>mba-colleges-in-chennai</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-hyderabad.html</t>
+          <t>mba-colleges-in-chennai.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3222,17 +3382,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-kolkata</t>
+          <t>mba-colleges-in-delhi-ncr</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-kolkata.html</t>
+          <t>mba-colleges-in-delhi-ncr.html</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -3254,17 +3414,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-mumbai</t>
+          <t>mba-colleges-in-hyderabad</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>mba-colleges-in-mumbai.html</t>
+          <t>mba-colleges-in-hyderabad.html</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3286,30 +3446,94 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:19:23</t>
+          <t>2026-09-15 18:15:20</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>mba-colleges-in-kolkata</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-kolkata.html</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:15:20</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-mumbai</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>mba-colleges-in-mumbai.html</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:15:20</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>mba-colleges-in-pune</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>mba-colleges-in-pune.html</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20 UTC</t>
+          <t>2026-09-15 19:13:43 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1605,19 +1605,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2085,19 +2085,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2245,19 +2245,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -2325,19 +2325,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -2405,19 +2405,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2966,7 +2966,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2998,7 +2998,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3158,7 +3158,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:20</t>
+          <t>2026-09-15 19:13:43</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43 UTC</t>
+          <t>2026-09-15 22:17:50 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2966,7 +2966,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2998,7 +2998,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3158,7 +3158,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:13:43</t>
+          <t>2026-09-15 22:17:50</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50 UTC</t>
+          <t>2026-09-16 00:40:36 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2966,7 +2966,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2998,7 +2998,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3158,7 +3158,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:50</t>
+          <t>2026-09-16 00:40:36</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36 UTC</t>
+          <t>2026-09-16 05:18:33 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2966,7 +2966,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2998,7 +2998,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3158,7 +3158,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:40:36</t>
+          <t>2026-09-16 05:18:33</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33 UTC</t>
+          <t>2026-09-16 05:38:35 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1605,19 +1605,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1642,11 +1642,11 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>6f8edf04d0d70d9cb674b0e87bad73841f91e888</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2085,19 +2085,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2245,19 +2245,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -2325,19 +2325,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -2405,19 +2405,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2895,14 +2895,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3119,14 +3119,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>676f4dddd407415e952eac534266952ca3560106</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
+          <t>6f8edf04d0d70d9cb674b0e87bad73841f91e888</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:18:33</t>
+          <t>2026-09-16 05:38:35</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35 UTC</t>
+          <t>2026-09-16 06:26:10 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>6f8edf04d0d70d9cb674b0e87bad73841f91e888</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2895,14 +2895,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3119,14 +3119,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>676f4dddd407415e952eac534266952ca3560106</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>6f8edf04d0d70d9cb674b0e87bad73841f91e888</t>
+          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 05:38:35</t>
+          <t>2026-09-16 06:26:10</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10 UTC</t>
+          <t>2026-09-16 06:38:57 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2895,14 +2895,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3119,14 +3119,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>8f7c78521012167361b84a923f33dddc4ab1a1c1</t>
+          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:26:10</t>
+          <t>2026-09-16 06:38:57</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57 UTC</t>
+          <t>2026-09-16 10:11:59 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1605,19 +1605,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2085,19 +2085,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2245,19 +2245,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -2325,19 +2325,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -2405,19 +2405,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2895,14 +2895,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3119,14 +3119,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 06:38:57</t>
+          <t>2026-09-16 10:11:59</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59 UTC</t>
+          <t>2026-09-16 15:00:11 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2966,7 +2966,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2998,7 +2998,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3158,7 +3158,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:11:59</t>
+          <t>2026-09-16 15:00:11</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11 UTC</t>
+          <t>2026-09-16 15:53:13 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1605,19 +1605,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1637,16 +1637,16 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 1 issue group(s)</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>02c9fd8f94185fae6b42eab64a76d63a3114a7a2</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2085,19 +2085,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2245,19 +2245,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -2325,19 +2325,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -2405,19 +2405,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2895,14 +2895,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3119,14 +3119,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>db5c40ee04ccd48ef398fda68d82d0ed216b8f1e</t>
+          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>f6b7bc2ceb3c95c4d7e8bea8f03a6c325147d1c0</t>
+          <t>02c9fd8f94185fae6b42eab64a76d63a3114a7a2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:11</t>
+          <t>2026-09-16 15:53:13</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13 UTC</t>
+          <t>2026-09-16 16:10:10 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1637,16 +1637,16 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 1 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>02c9fd8f94185fae6b42eab64a76d63a3114a7a2</t>
+          <t>4ccb211c2ff66df2136642e90631173b140698f4</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2895,14 +2895,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3119,14 +3119,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>1f8384545695d0f41629e83f0c22ad2adba05fbb</t>
+          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>02c9fd8f94185fae6b42eab64a76d63a3114a7a2</t>
+          <t>4ccb211c2ff66df2136642e90631173b140698f4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:53:13</t>
+          <t>2026-09-16 16:10:10</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10 UTC</t>
+          <t>2026-09-16 16:37:43 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>4ccb211c2ff66df2136642e90631173b140698f4</t>
+          <t>74c3bd61d3d12945893bf8e3b2149cd22ba2e549</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
@@ -2870,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2895,14 +2895,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3119,14 +3119,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>f4a310206058d45244fcb184b3efc1ed3d62117b</t>
+          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>4ccb211c2ff66df2136642e90631173b140698f4</t>
+          <t>74c3bd61d3d12945893bf8e3b2149cd22ba2e549</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:10:10</t>
+          <t>2026-09-16 16:37:43</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P22" headerRowCount="1">
-  <autoFilter ref="A1:P22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P13" headerRowCount="1">
+  <autoFilter ref="A1:P13"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43 UTC</t>
+          <t>2026-09-16 17:54:38 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>74c3bd61d3d12945893bf8e3b2149cd22ba2e549</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
@@ -1652,17 +1652,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees</t>
+          <t>mba-colleges-by-location</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees.html</t>
+          <t>mba-colleges-by-location.html</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1717,736 +1717,16 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>4030b3ab60bf099621625ae33d8902a993a35728</t>
+          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location.html</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n">
         <v>90</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-ahmedabad</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-ahmedabad.html</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-bengaluru</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-bengaluru.html</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-chennai</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-chennai.html</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-delhi-ncr</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-delhi-ncr.html</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-hyderabad</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-hyderabad.html</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-kolkata</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-kolkata.html</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-mumbai</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-mumbai.html</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-pune</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-pune.html</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2870,7 +2150,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2895,14 +2175,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2927,14 +2207,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2959,14 +2239,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2991,14 +2271,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3023,14 +2303,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3055,14 +2335,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3087,14 +2367,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3119,14 +2399,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3151,14 +2431,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3183,14 +2463,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>0bcacc0e952df2cd2475444caabc58b6931e783c</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3215,24 +2495,24 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>74c3bd61d3d12945893bf8e3b2149cd22ba2e549</t>
+          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:37:43</t>
+          <t>2026-09-16 17:54:38</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees</t>
+          <t>mba-colleges-by-location</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>mba-college-fees.html</t>
+          <t>mba-colleges-by-location.html</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -3247,295 +2527,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>4030b3ab60bf099621625ae33d8902a993a35728</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16 16:37:43</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location.html</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
           <t>362d0afecb97f242e5a56407166014a163c32093</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16 16:37:43</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-ahmedabad</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-ahmedabad.html</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16 16:37:43</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-bengaluru</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-bengaluru.html</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16 16:37:43</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-chennai</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-chennai.html</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16 16:37:43</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-delhi-ncr</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-delhi-ncr.html</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16 16:37:43</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-hyderabad</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-hyderabad.html</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16 16:37:43</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-kolkata</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-kolkata.html</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16 16:37:43</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-mumbai</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-mumbai.html</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16 16:37:43</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-pune</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-in-pune.html</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>f2a7ce1ee2e3405e4b0fbca110ac808ed80fa991</t>
         </is>
       </c>
     </row>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P13" headerRowCount="1">
-  <autoFilter ref="A1:P13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P12" headerRowCount="1">
+  <autoFilter ref="A1:P12"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38 UTC</t>
+          <t>2026-09-16 18:49:59 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1605,19 +1605,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1646,86 +1646,6 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location.html</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Course-specific</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2104,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2150,7 +2070,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38</t>
+          <t>2026-09-16 18:49:59</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2182,7 +2102,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38</t>
+          <t>2026-09-16 18:49:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2214,7 +2134,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38</t>
+          <t>2026-09-16 18:49:59</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2246,7 +2166,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38</t>
+          <t>2026-09-16 18:49:59</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2278,7 +2198,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38</t>
+          <t>2026-09-16 18:49:59</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2310,7 +2230,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38</t>
+          <t>2026-09-16 18:49:59</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2342,7 +2262,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38</t>
+          <t>2026-09-16 18:49:59</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2374,7 +2294,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38</t>
+          <t>2026-09-16 18:49:59</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2406,7 +2326,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38</t>
+          <t>2026-09-16 18:49:59</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2438,7 +2358,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38</t>
+          <t>2026-09-16 18:49:59</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2470,7 +2390,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:54:38</t>
+          <t>2026-09-16 18:49:59</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2496,38 +2416,6 @@
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16 17:54:38</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>mba-colleges-by-location.html</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>362d0afecb97f242e5a56407166014a163c32093</t>
         </is>
       </c>
     </row>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59 UTC</t>
+          <t>2026-09-16 21:55:46 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2070,7 +2070,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59</t>
+          <t>2026-09-16 21:55:46</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59</t>
+          <t>2026-09-16 21:55:46</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59</t>
+          <t>2026-09-16 21:55:46</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2166,7 +2166,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59</t>
+          <t>2026-09-16 21:55:46</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2198,7 +2198,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59</t>
+          <t>2026-09-16 21:55:46</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2230,7 +2230,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59</t>
+          <t>2026-09-16 21:55:46</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59</t>
+          <t>2026-09-16 21:55:46</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2294,7 +2294,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59</t>
+          <t>2026-09-16 21:55:46</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59</t>
+          <t>2026-09-16 21:55:46</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2358,7 +2358,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59</t>
+          <t>2026-09-16 21:55:46</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 18:49:59</t>
+          <t>2026-09-16 21:55:46</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46 UTC</t>
+          <t>2026-09-17 00:10:10 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2070,7 +2070,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46</t>
+          <t>2026-09-17 00:10:10</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46</t>
+          <t>2026-09-17 00:10:10</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46</t>
+          <t>2026-09-17 00:10:10</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2166,7 +2166,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46</t>
+          <t>2026-09-17 00:10:10</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2198,7 +2198,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46</t>
+          <t>2026-09-17 00:10:10</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2230,7 +2230,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46</t>
+          <t>2026-09-17 00:10:10</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46</t>
+          <t>2026-09-17 00:10:10</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2294,7 +2294,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46</t>
+          <t>2026-09-17 00:10:10</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46</t>
+          <t>2026-09-17 00:10:10</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2358,7 +2358,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46</t>
+          <t>2026-09-17 00:10:10</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:46</t>
+          <t>2026-09-17 00:10:10</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10 UTC</t>
+          <t>2026-09-17 04:53:49 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2070,7 +2070,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10</t>
+          <t>2026-09-17 04:53:49</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10</t>
+          <t>2026-09-17 04:53:49</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10</t>
+          <t>2026-09-17 04:53:49</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2166,7 +2166,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10</t>
+          <t>2026-09-17 04:53:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2198,7 +2198,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10</t>
+          <t>2026-09-17 04:53:49</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2230,7 +2230,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10</t>
+          <t>2026-09-17 04:53:49</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10</t>
+          <t>2026-09-17 04:53:49</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2294,7 +2294,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10</t>
+          <t>2026-09-17 04:53:49</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10</t>
+          <t>2026-09-17 04:53:49</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2358,7 +2358,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10</t>
+          <t>2026-09-17 04:53:49</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10</t>
+          <t>2026-09-17 04:53:49</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P12" headerRowCount="1">
-  <autoFilter ref="A1:P12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P13" headerRowCount="1">
+  <autoFilter ref="A1:P13"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49 UTC</t>
+          <t>2026-09-17 09:51:30 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1572,80 +1572,160 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>iim-bangalore</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>iim-bangalore.html</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>e73523b355b97d09994e59bd58ec5da66840c682</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>mba-college-comparison</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>mba-college-comparison.html</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
-      <c r="P12" s="3" t="n">
+      <c r="P13" s="3" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2024,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2070,7 +2150,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49</t>
+          <t>2026-09-17 09:51:30</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2095,14 +2175,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49</t>
+          <t>2026-09-17 09:51:30</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2127,14 +2207,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49</t>
+          <t>2026-09-17 09:51:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2159,14 +2239,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49</t>
+          <t>2026-09-17 09:51:30</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2191,14 +2271,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49</t>
+          <t>2026-09-17 09:51:30</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2223,14 +2303,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49</t>
+          <t>2026-09-17 09:51:30</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2255,14 +2335,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49</t>
+          <t>2026-09-17 09:51:30</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2287,14 +2367,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49</t>
+          <t>2026-09-17 09:51:30</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2319,14 +2399,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49</t>
+          <t>2026-09-17 09:51:30</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2351,14 +2431,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49</t>
+          <t>2026-09-17 09:51:30</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2383,37 +2463,69 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 04:53:49</t>
+          <t>2026-09-17 09:51:30</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>iim-bangalore</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>iim-bangalore.html</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>e73523b355b97d09994e59bd58ec5da66840c682</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:51:30</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>mba-college-comparison</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>mba-college-comparison.html</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P13" headerRowCount="1">
-  <autoFilter ref="A1:P13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P14" headerRowCount="1">
+  <autoFilter ref="A1:P14"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30 UTC</t>
+          <t>2026-09-17 14:43:42 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1652,80 +1652,160 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>IIM Udaipur</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>iim-udaipur.html</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>6cadcf1d0213782ffbdb433921c85d48255e27de</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>mba-college-comparison</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>mba-college-comparison.html</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
-      <c r="P13" s="3" t="n">
+      <c r="P14" s="3" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2104,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2150,7 +2230,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2175,14 +2255,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2207,14 +2287,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2239,14 +2319,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2271,14 +2351,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2303,14 +2383,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2335,14 +2415,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2367,14 +2447,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2399,14 +2479,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2431,14 +2511,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2463,14 +2543,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>3c5e8ea8b490a472cab41bd486a1a773edaf95c5</t>
+          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2502,30 +2582,62 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 09:51:30</t>
+          <t>2026-09-17 14:43:42</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>IIM Udaipur</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>iim-udaipur.html</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>6cadcf1d0213782ffbdb433921c85d48255e27de</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:43:42</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>mba-college-comparison</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>mba-college-comparison.html</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>AUDITED</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>AUDITED – NO CHANGE</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P14" headerRowCount="1">
-  <autoFilter ref="A1:P14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P17" headerRowCount="1">
+  <autoFilter ref="A1:P17"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42 UTC</t>
+          <t>2026-09-17 16:08:40 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1605,19 +1605,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1652,12 +1652,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-kozhikode-mba</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-kozhikode-mba.html</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1680,24 +1680,24 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1717,95 +1717,335 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>6cadcf1d0213782ffbdb433921c85d48255e27de</t>
+          <t>74b9a872f4167ace9e6a789664bfba243a1330c3</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>iim-kozhikode-placements</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>iim-kozhikode-placements.html</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>74b9a872f4167ace9e6a789664bfba243a1330c3</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>iim-kozhikode</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>iim-kozhikode.html</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 4 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>IIM Udaipur</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>iim-udaipur.html</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>mba-college-comparison</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>mba-college-comparison.html</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
-      <c r="P14" s="3" t="n">
+      <c r="P17" s="3" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2184,7 +2424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2230,7 +2470,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2255,14 +2495,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2287,14 +2527,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2319,14 +2559,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2351,14 +2591,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2383,14 +2623,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2415,14 +2655,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2447,14 +2687,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2479,14 +2719,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2511,14 +2751,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2543,14 +2783,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>5b2e906815e2efd0b244057e56a16aefc5cfc1cf</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2582,17 +2822,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-kozhikode-mba</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-kozhikode-mba.html</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -2607,37 +2847,133 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>6cadcf1d0213782ffbdb433921c85d48255e27de</t>
+          <t>74b9a872f4167ace9e6a789664bfba243a1330c3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:43:42</t>
+          <t>2026-09-17 16:08:40</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>iim-kozhikode-placements</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>iim-kozhikode-placements.html</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>74b9a872f4167ace9e6a789664bfba243a1330c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:08:40</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>iim-kozhikode</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>iim-kozhikode.html</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:08:40</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>IIM Udaipur</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>iim-udaipur.html</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:08:40</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>mba-college-comparison</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>mba-college-comparison.html</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P17" headerRowCount="1">
-  <autoFilter ref="A1:P17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P20" headerRowCount="1">
+  <autoFilter ref="A1:P20"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40 UTC</t>
+          <t>2026-09-17 16:31:08 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>74b9a872f4167ace9e6a789664bfba243a1330c3</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>74b9a872f4167ace9e6a789664bfba243a1330c3</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
@@ -1972,80 +1972,320 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>iit-delhi-dms-mba</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba.html</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 4 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>4ffd56936858771cc4a50bad318981eaa2d34c92</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9a5333cf1e145f2e3af1c820c3750a47aea01df6</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms.html</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>mba-college-comparison</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>mba-college-comparison.html</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>
       </c>
-      <c r="P17" s="3" t="n">
+      <c r="P20" s="3" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2424,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2470,7 +2710,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2495,14 +2735,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2527,14 +2767,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2559,14 +2799,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2591,14 +2831,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2623,14 +2863,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2655,14 +2895,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2687,14 +2927,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2719,14 +2959,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2751,14 +2991,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2783,14 +3023,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>410e355b01613fc9503f330814432868978ebc2e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2822,7 +3062,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2847,14 +3087,14 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>74b9a872f4167ace9e6a789664bfba243a1330c3</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2879,14 +3119,14 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>74b9a872f4167ace9e6a789664bfba243a1330c3</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2918,7 +3158,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2950,30 +3190,126 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:08:40</t>
+          <t>2026-09-17 16:31:08</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>iit-delhi-dms-mba</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba.html</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>4ffd56936858771cc4a50bad318981eaa2d34c92</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:31:08</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>9a5333cf1e145f2e3af1c820c3750a47aea01df6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:31:08</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms.html</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:31:08</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
           <t>mba-college-comparison</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>mba-college-comparison.html</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P20" headerRowCount="1">
-  <autoFilter ref="A1:P20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P21" headerRowCount="1">
+  <autoFilter ref="A1:P21"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08 UTC</t>
+          <t>2026-09-17 18:36:48 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1605,19 +1605,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -1972,12 +1972,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2037,32 +2037,32 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 4 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>4ffd56936858771cc4a50bad318981eaa2d34c92</t>
+          <t>5eca4964124cd45ce8701383f48033a67dfe32d3</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -2085,19 +2085,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2122,27 +2122,27 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>9a5333cf1e145f2e3af1c820c3750a47aea01df6</t>
+          <t>a77ecd4eccb213381c2c10b9b17808e9b47c7f1d</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms</t>
+          <t>iit-delhi-dms-mba</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms.html</t>
+          <t>iit-delhi-dms-mba.html</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>57275ecc866356860e333d5441114cd310490a65</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
@@ -2212,80 +2212,160 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>mba-college-comparison</t>
+          <t>iit-delhi-dms-placements</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>mba-college-comparison.html</t>
+          <t>iit-delhi-dms-placements.html</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9a5333cf1e145f2e3af1c820c3750a47aea01df6</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms.html</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 2 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n">
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>3dcc89e8d4e15cc25825df352e7634d40624a60b</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2664,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2710,7 +2790,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2742,7 +2822,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2774,7 +2854,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2806,7 +2886,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2838,7 +2918,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2870,7 +2950,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2902,7 +2982,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2934,7 +3014,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2966,7 +3046,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2998,7 +3078,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3030,7 +3110,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3062,7 +3142,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3094,7 +3174,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3126,7 +3206,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3158,7 +3238,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3190,17 +3270,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3215,24 +3295,24 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>4ffd56936858771cc4a50bad318981eaa2d34c92</t>
+          <t>5eca4964124cd45ce8701383f48033a67dfe32d3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -3247,24 +3327,24 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>9a5333cf1e145f2e3af1c820c3750a47aea01df6</t>
+          <t>a77ecd4eccb213381c2c10b9b17808e9b47c7f1d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms</t>
+          <t>iit-delhi-dms-mba</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms.html</t>
+          <t>iit-delhi-dms-mba.html</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3279,24 +3359,24 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>57275ecc866356860e333d5441114cd310490a65</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:31:08</t>
+          <t>2026-09-17 18:36:48</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>mba-college-comparison</t>
+          <t>iit-delhi-dms-placements</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>mba-college-comparison.html</t>
+          <t>iit-delhi-dms-placements.html</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3311,7 +3391,39 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>07ca3d3894cc4c9900e266a0c85baffcfa3ec96b</t>
+          <t>9a5333cf1e145f2e3af1c820c3750a47aea01df6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 18:36:48</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms.html</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>3dcc89e8d4e15cc25825df352e7634d40624a60b</t>
         </is>
       </c>
     </row>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48 UTC</t>
+          <t>2026-09-17 21:47:23 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2790,7 +2790,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2822,7 +2822,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2854,7 +2854,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2950,7 +2950,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2982,7 +2982,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3014,7 +3014,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3046,7 +3046,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3110,7 +3110,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 18:36:48</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23 UTC</t>
+          <t>2026-09-17 23:56:10 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2790,7 +2790,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2822,7 +2822,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2854,7 +2854,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2950,7 +2950,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2982,7 +2982,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3014,7 +3014,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3046,7 +3046,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3110,7 +3110,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 23:56:10</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10 UTC</t>
+          <t>2026-09-18 03:45:24 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2790,7 +2790,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2822,7 +2822,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2854,7 +2854,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2950,7 +2950,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2982,7 +2982,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3014,7 +3014,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3046,7 +3046,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3110,7 +3110,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:56:10</t>
+          <t>2026-09-18 03:45:24</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24 UTC</t>
+          <t>2026-09-18 03:59:53 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1605,19 +1605,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>5eca4964124cd45ce8701383f48033a67dfe32d3</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
@@ -2085,19 +2085,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>a77ecd4eccb213381c2c10b9b17808e9b47c7f1d</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
@@ -2165,19 +2165,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>57275ecc866356860e333d5441114cd310490a65</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
@@ -2245,19 +2245,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>9a5333cf1e145f2e3af1c820c3750a47aea01df6</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
@@ -2325,19 +2325,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>3dcc89e8d4e15cc25825df352e7634d40624a60b</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
@@ -2790,7 +2790,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2815,14 +2815,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2847,14 +2847,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2879,14 +2879,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2943,14 +2943,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2975,14 +2975,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3007,14 +3007,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3039,14 +3039,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3071,14 +3071,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3103,14 +3103,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>410e355b01613fc9503f330814432868978ebc2e</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3295,14 +3295,14 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>5eca4964124cd45ce8701383f48033a67dfe32d3</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3327,14 +3327,14 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>a77ecd4eccb213381c2c10b9b17808e9b47c7f1d</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3359,14 +3359,14 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>57275ecc866356860e333d5441114cd310490a65</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3391,14 +3391,14 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>9a5333cf1e145f2e3af1c820c3750a47aea01df6</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:45:24</t>
+          <t>2026-09-18 03:59:53</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>3dcc89e8d4e15cc25825df352e7634d40624a60b</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53 UTC</t>
+          <t>2026-09-18 04:00:45 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2790,7 +2790,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2822,7 +2822,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2854,7 +2854,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2950,7 +2950,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2982,7 +2982,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3014,7 +3014,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3046,7 +3046,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3110,7 +3110,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 03:59:53</t>
+          <t>2026-09-18 04:00:45</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P21" headerRowCount="1">
-  <autoFilter ref="A1:P21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P20" headerRowCount="1">
+  <autoFilter ref="A1:P20"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45 UTC</t>
+          <t>2026-09-18 08:31:40 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1572,12 +1572,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>iim-bangalore</t>
+          <t>iim-kozhikode-mba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>iim-bangalore.html</t>
+          <t>iim-kozhikode-mba.html</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1600,24 +1600,24 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>e73523b355b97d09994e59bd58ec5da66840c682</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
@@ -1652,17 +1652,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Placement</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1726,23 +1726,23 @@
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1760,24 +1760,24 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1797,27 +1797,27 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 4 issue group(s)</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 4 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -1886,23 +1886,23 @@
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1920,24 +1920,24 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -1957,27 +1957,27 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2046,18 +2046,18 @@
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>iit-delhi-dms-mba</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iit-delhi-dms-mba.html</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2085,19 +2085,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2126,23 +2126,23 @@
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-placements</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-placements.html</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Placement</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2206,23 +2206,23 @@
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms.html</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -2245,19 +2245,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -2286,86 +2286,6 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms.html</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 3 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2744,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2790,7 +2710,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2815,14 +2735,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2847,14 +2767,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2879,14 +2799,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2911,14 +2831,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2943,14 +2863,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2975,14 +2895,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3007,14 +2927,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3039,14 +2959,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3071,14 +2991,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3103,24 +3023,24 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>iim-bangalore</t>
+          <t>iim-kozhikode-mba</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>iim-bangalore.html</t>
+          <t>iim-kozhikode-mba.html</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -3135,24 +3055,24 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>e73523b355b97d09994e59bd58ec5da66840c682</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -3174,17 +3094,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3199,24 +3119,24 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3238,17 +3158,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3263,24 +3183,24 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3302,17 +3222,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>iit-delhi-dms-mba</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iit-delhi-dms-mba.html</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -3334,17 +3254,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-placements</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-placements.html</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3366,17 +3286,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 04:00:45</t>
+          <t>2026-09-18 08:31:40</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms.html</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3390,38 +3310,6 @@
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18 04:00:45</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms.html</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40 UTC</t>
+          <t>2026-09-18 08:57:51 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1605,19 +1605,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -2005,19 +2005,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
@@ -2085,19 +2085,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
@@ -2245,19 +2245,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -2710,7 +2710,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2767,14 +2767,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2831,14 +2831,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2863,14 +2863,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2895,14 +2895,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>5160388a9f8771a6f36d924aaeee88dc32e3cfd5</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3158,7 +3158,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:31:40</t>
+          <t>2026-09-18 08:57:51</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51 UTC</t>
+          <t>2026-09-18 10:12:14 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -2710,7 +2710,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2767,14 +2767,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2831,14 +2831,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2863,14 +2863,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2895,14 +2895,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3158,7 +3158,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:57:51</t>
+          <t>2026-09-18 10:12:14</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P20" headerRowCount="1">
-  <autoFilter ref="A1:P20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P24" headerRowCount="1">
+  <autoFilter ref="A1:P24"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14 UTC</t>
+          <t>2026-09-18 13:17:03 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1572,12 +1572,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba</t>
+          <t>iim-bangalore-epgp</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba.html</t>
+          <t>iim-bangalore-epgp.html</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1600,9 +1600,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1642,27 +1642,27 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-bangalore-mba</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-bangalore-mba.html</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1722,22 +1722,22 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>iim-bangalore-pgpba</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-bangalore-pgpba.html</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1797,27 +1797,27 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 4 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-bangalore</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-bangalore.html</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1882,27 +1882,27 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>iim-kozhikode-mba</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iim-kozhikode-mba.html</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -1972,17 +1972,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Placement</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -2042,27 +2042,27 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -2080,9 +2080,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -2117,32 +2117,32 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 4 issue group(s)</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>c6fa9db08b4248ad5a723d51f30f4dc149af9e48</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -2160,9 +2160,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -2202,90 +2202,410 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>iit-delhi-dms-executive-mba</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-executive-mba.html</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba-telecom</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba-telecom.html</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 2 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba.html</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>iit-delhi-dms</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>iit-delhi-dms.html</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="O24" s="3" t="inlineStr">
         <is>
           <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
-      <c r="P20" s="3" t="n">
+      <c r="P24" s="3" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2664,7 +2984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2710,7 +3030,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2735,14 +3055,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2767,14 +3087,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2799,14 +3119,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2831,14 +3151,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2863,14 +3183,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2895,14 +3215,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2927,14 +3247,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2959,14 +3279,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2991,14 +3311,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3023,24 +3343,24 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>8412cd93205522e7dadff7a182b35696875b4a29</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba</t>
+          <t>iim-bangalore-epgp</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba.html</t>
+          <t>iim-bangalore-epgp.html</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -3055,24 +3375,24 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-bangalore-mba</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-bangalore-mba.html</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -3087,24 +3407,24 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>iim-bangalore-pgpba</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-bangalore-pgpba.html</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3119,24 +3439,24 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-bangalore</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-bangalore.html</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3151,24 +3471,24 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>iim-kozhikode-mba</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iim-kozhikode-mba.html</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3183,24 +3503,24 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3215,24 +3535,24 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -3247,24 +3567,24 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>c6fa9db08b4248ad5a723d51f30f4dc149af9e48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3279,37 +3599,165 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:12:14</t>
+          <t>2026-09-18 13:17:03</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>iit-delhi-dms-executive-mba</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-executive-mba.html</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:17:03</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba-telecom</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba-telecom.html</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:17:03</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba.html</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:17:03</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:17:03</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
           <t>iit-delhi-dms</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>iit-delhi-dms.html</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P24" headerRowCount="1">
-  <autoFilter ref="A1:P24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P25" headerRowCount="1">
+  <autoFilter ref="A1:P25"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03 UTC</t>
+          <t>2026-09-18 13:19:59 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1972,17 +1972,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-kozhikode-pgp-finance</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-kozhikode-pgp-finance.html</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -2000,9 +2000,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -2037,32 +2037,32 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>abb5a8b5858d6cfe3ad2635df708992b8596ddf6</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Placement</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -2080,9 +2080,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -2117,27 +2117,27 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 4 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>c6fa9db08b4248ad5a723d51f30f4dc149af9e48</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2197,32 +2197,32 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 4 issue group(s)</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>c6fa9db08b4248ad5a723d51f30f4dc149af9e48</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -2240,9 +2240,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -2277,27 +2277,27 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2366,18 +2366,18 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2437,32 +2437,32 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms-mba</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms-mba.html</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -2522,90 +2522,170 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
           <t>iit-delhi-dms</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>iit-delhi-dms.html</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
-      <c r="P24" s="3" t="n">
+      <c r="P25" s="3" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2984,7 +3064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3030,7 +3110,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3062,7 +3142,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3094,7 +3174,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3126,7 +3206,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3158,7 +3238,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3190,7 +3270,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3222,7 +3302,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3254,7 +3334,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3286,7 +3366,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3318,7 +3398,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3350,7 +3430,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3382,7 +3462,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3414,7 +3494,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3446,7 +3526,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3478,7 +3558,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3510,17 +3590,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-kozhikode-pgp-finance</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-kozhikode-pgp-finance.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3535,24 +3615,24 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>abb5a8b5858d6cfe3ad2635df708992b8596ddf6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -3567,24 +3647,24 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>c6fa9db08b4248ad5a723d51f30f4dc149af9e48</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3599,24 +3679,24 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>c6fa9db08b4248ad5a723d51f30f4dc149af9e48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3631,24 +3711,24 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -3670,17 +3750,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3695,24 +3775,24 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms-mba</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms-mba.html</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3727,37 +3807,69 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:17:03</t>
+          <t>2026-09-18 13:19:59</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:19:59</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>iit-delhi-dms</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>iit-delhi-dms.html</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P25" headerRowCount="1">
-  <autoFilter ref="A1:P25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P27" headerRowCount="1">
+  <autoFilter ref="A1:P27"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59 UTC</t>
+          <t>2026-09-18 13:32:46 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1972,12 +1972,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance</t>
+          <t>iim-kozhikode-pgp-bl</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance.html</t>
+          <t>iim-kozhikode-pgp-bl.html</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2037,32 +2037,32 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 4 issue group(s)</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>abb5a8b5858d6cfe3ad2635df708992b8596ddf6</t>
+          <t>042d1e184deb58a25b82e52cf9864f4d0f01976d</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-kozhikode-pgp-finance</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-kozhikode-pgp-finance.html</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -2080,9 +2080,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -2122,27 +2122,27 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>46c98d4bc2422b190774491517a6a88e0ba53895</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>iim-kozhikode-pgp-lsm</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-kozhikode-pgp-lsm.html</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -2197,32 +2197,32 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 4 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>c6fa9db08b4248ad5a723d51f30f4dc149af9e48</t>
+          <t>52a1c774ffd4dda2fbceb9f14376400ad59022cb</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Placement</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -2240,9 +2240,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -2277,32 +2277,32 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>0af6b039e3fff954ed447e3d81915e1537f78ac2</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -2320,9 +2320,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -2357,32 +2357,32 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>121b44523f65ef3c785752256e326e05710b207a</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -2400,9 +2400,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -2437,27 +2437,27 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2517,32 +2517,32 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2606,23 +2606,23 @@
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms</t>
+          <t>iit-delhi-dms-mba</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms.html</t>
+          <t>iit-delhi-dms-mba.html</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -2687,6 +2687,166 @@
       </c>
       <c r="P25" s="3" t="n">
         <v>90</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms.html</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>accfa0471472b7e41623f5be63b0f95534f66d91</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3064,7 +3224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3110,7 +3270,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3135,14 +3295,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3167,14 +3327,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3199,14 +3359,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3231,14 +3391,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3263,14 +3423,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3295,14 +3455,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3327,14 +3487,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3359,14 +3519,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3391,14 +3551,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3423,14 +3583,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>4bc60b7f77cdf19442a5d2bdff6348a8834ef267</t>
+          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3462,7 +3622,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3494,7 +3654,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3526,7 +3686,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3558,7 +3718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3590,17 +3750,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance</t>
+          <t>iim-kozhikode-pgp-bl</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance.html</t>
+          <t>iim-kozhikode-pgp-bl.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3615,24 +3775,24 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>abb5a8b5858d6cfe3ad2635df708992b8596ddf6</t>
+          <t>042d1e184deb58a25b82e52cf9864f4d0f01976d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-kozhikode-pgp-finance</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-kozhikode-pgp-finance.html</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -3647,24 +3807,24 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>46c98d4bc2422b190774491517a6a88e0ba53895</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>iim-kozhikode-pgp-lsm</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-kozhikode-pgp-lsm.html</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3679,24 +3839,24 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>c6fa9db08b4248ad5a723d51f30f4dc149af9e48</t>
+          <t>52a1c774ffd4dda2fbceb9f14376400ad59022cb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3711,24 +3871,24 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>0af6b039e3fff954ed447e3d81915e1537f78ac2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -3743,24 +3903,24 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>121b44523f65ef3c785752256e326e05710b207a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3775,24 +3935,24 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3807,24 +3967,24 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3846,32 +4006,96 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:19:59</t>
+          <t>2026-09-18 13:32:46</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>iit-delhi-dms-mba</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba.html</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:32:46</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:32:46</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>iit-delhi-dms</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>iit-delhi-dms.html</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>accfa0471472b7e41623f5be63b0f95534f66d91</t>
         </is>
       </c>
     </row>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46 UTC</t>
+          <t>2026-09-18 13:35:03 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>accfa0471472b7e41623f5be63b0f95534f66d91</t>
+          <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
         </is>
       </c>
       <c r="P27" s="3" t="n">
@@ -3270,7 +3270,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3878,7 +3878,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3942,7 +3942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3974,7 +3974,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4038,7 +4038,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4070,7 +4070,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:32:46</t>
+          <t>2026-09-18 13:35:03</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>accfa0471472b7e41623f5be63b0f95534f66d91</t>
+          <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
         </is>
       </c>
     </row>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P27" headerRowCount="1">
-  <autoFilter ref="A1:P27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P28" headerRowCount="1">
+  <autoFilter ref="A1:P28"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03 UTC</t>
+          <t>2026-09-18 13:41:27 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -2372,12 +2372,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-lucknow</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-lucknow.html</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2437,32 +2437,32 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -2480,9 +2480,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -2517,27 +2517,27 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2606,18 +2606,18 @@
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2677,32 +2677,32 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms-mba</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms-mba.html</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -2762,90 +2762,170 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>iit-delhi-dms</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>iit-delhi-dms.html</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O28" s="3" t="inlineStr">
         <is>
           <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
         </is>
       </c>
-      <c r="P27" s="3" t="n">
+      <c r="P28" s="3" t="n">
         <v>78</v>
       </c>
     </row>
@@ -3224,7 +3304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3270,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3295,14 +3375,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3327,14 +3407,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3359,14 +3439,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3391,14 +3471,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3423,14 +3503,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3455,14 +3535,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3487,14 +3567,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3519,14 +3599,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3551,14 +3631,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3583,14 +3663,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>7d50dc4e394381a444aace0b955055126f85c6e5</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3622,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3654,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3686,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3718,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3750,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3782,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3814,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3846,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3878,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3910,17 +3990,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-lucknow</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-lucknow.html</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3935,24 +4015,24 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3967,24 +4047,24 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -4006,17 +4086,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -4031,24 +4111,24 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms-mba</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms-mba.html</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -4063,37 +4143,69 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:35:03</t>
+          <t>2026-09-18 13:41:27</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:41:27</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
           <t>iit-delhi-dms</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>iit-delhi-dms.html</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27 UTC</t>
+          <t>2026-09-18 13:51:34 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>f2b87e89377307b8f4d3fe19dcf2150c8a4743e9</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>f2b87e89377307b8f4d3fe19dcf2150c8a4743e9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:27</t>
+          <t>2026-09-18 13:51:34</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P28" headerRowCount="1">
-  <autoFilter ref="A1:P28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P30" headerRowCount="1">
+  <autoFilter ref="A1:P30"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34 UTC</t>
+          <t>2026-09-18 15:40:19 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1892,12 +1892,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba</t>
+          <t>iim-calcutta</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba.html</t>
+          <t>iim-calcutta.html</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1920,9 +1920,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 1 issue group(s)</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>33c28e4f22ca12c37a93fb96a922a3e85fa3a924</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-bl</t>
+          <t>iim-kozhikode-mba</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-bl.html</t>
+          <t>iim-kozhikode-mba.html</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -2000,9 +2000,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -2037,27 +2037,27 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 4 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>042d1e184deb58a25b82e52cf9864f4d0f01976d</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance</t>
+          <t>iim-kozhikode-pgp-bl</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance.html</t>
+          <t>iim-kozhikode-pgp-bl.html</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2117,27 +2117,27 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 4 issue group(s)</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>46c98d4bc2422b190774491517a6a88e0ba53895</t>
+          <t>042d1e184deb58a25b82e52cf9864f4d0f01976d</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-lsm</t>
+          <t>iim-kozhikode-pgp-finance</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-lsm.html</t>
+          <t>iim-kozhikode-pgp-finance.html</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2197,32 +2197,32 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>52a1c774ffd4dda2fbceb9f14376400ad59022cb</t>
+          <t>46c98d4bc2422b190774491517a6a88e0ba53895</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-kozhikode-pgp-lsm</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-kozhikode-pgp-lsm.html</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -2240,9 +2240,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -2277,32 +2277,32 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>0af6b039e3fff954ed447e3d81915e1537f78ac2</t>
+          <t>52a1c774ffd4dda2fbceb9f14376400ad59022cb</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Placement</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -2320,9 +2320,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -2357,27 +2357,27 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>121b44523f65ef3c785752256e326e05710b207a</t>
+          <t>0af6b039e3fff954ed447e3d81915e1537f78ac2</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>iim-lucknow</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>iim-lucknow.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2437,27 +2437,27 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>f2b87e89377307b8f4d3fe19dcf2150c8a4743e9</t>
+          <t>121b44523f65ef3c785752256e326e05710b207a</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-lucknow</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-lucknow.html</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2517,32 +2517,32 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>343636b326bd127d8eb761b5b18db85ec69439bd</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>IIM Mumbai</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iim-mumbai.html</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -2560,9 +2560,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -2597,32 +2597,32 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 1 issue group(s)</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -2640,9 +2640,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -2677,27 +2677,27 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2757,32 +2757,32 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -2846,86 +2846,246 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>iit-delhi-dms-mba</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba.html</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Course-specific</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Content audit: 3 issue group(s)</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>iit-delhi-dms</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>iit-delhi-dms.html</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
         <is>
           <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
+      <c r="O30" s="3" t="inlineStr">
         <is>
           <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
         </is>
       </c>
-      <c r="P28" s="3" t="n">
+      <c r="P30" s="3" t="n">
         <v>78</v>
       </c>
     </row>
@@ -3304,7 +3464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3350,7 +3510,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3375,14 +3535,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3407,14 +3567,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3439,14 +3599,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3471,14 +3631,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3503,14 +3663,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3535,14 +3695,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3567,14 +3727,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3599,14 +3759,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3631,14 +3791,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3663,14 +3823,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>0f88b04d7f7c53bb1cf0411554d400ed640f4c11</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3862,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3894,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3926,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,17 +3958,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba</t>
+          <t>iim-calcutta</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba.html</t>
+          <t>iim-calcutta.html</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3823,24 +3983,24 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>33c28e4f22ca12c37a93fb96a922a3e85fa3a924</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-bl</t>
+          <t>iim-kozhikode-mba</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-bl.html</t>
+          <t>iim-kozhikode-mba.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3855,24 +4015,24 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>042d1e184deb58a25b82e52cf9864f4d0f01976d</t>
+          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance</t>
+          <t>iim-kozhikode-pgp-bl</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance.html</t>
+          <t>iim-kozhikode-pgp-bl.html</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -3887,24 +4047,24 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>46c98d4bc2422b190774491517a6a88e0ba53895</t>
+          <t>042d1e184deb58a25b82e52cf9864f4d0f01976d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-lsm</t>
+          <t>iim-kozhikode-pgp-finance</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-lsm.html</t>
+          <t>iim-kozhikode-pgp-finance.html</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3919,24 +4079,24 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>52a1c774ffd4dda2fbceb9f14376400ad59022cb</t>
+          <t>46c98d4bc2422b190774491517a6a88e0ba53895</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-kozhikode-pgp-lsm</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-kozhikode-pgp-lsm.html</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3951,24 +4111,24 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0af6b039e3fff954ed447e3d81915e1537f78ac2</t>
+          <t>52a1c774ffd4dda2fbceb9f14376400ad59022cb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -3983,24 +4143,24 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>121b44523f65ef3c785752256e326e05710b207a</t>
+          <t>0af6b039e3fff954ed447e3d81915e1537f78ac2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>iim-lucknow</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>iim-lucknow.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -4015,24 +4175,24 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>f2b87e89377307b8f4d3fe19dcf2150c8a4743e9</t>
+          <t>121b44523f65ef3c785752256e326e05710b207a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iim-lucknow</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iim-lucknow.html</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -4047,24 +4207,24 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>343636b326bd127d8eb761b5b18db85ec69439bd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>IIM Mumbai</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iim-mumbai.html</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -4079,24 +4239,24 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>IIM Udaipur</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iim-udaipur.html</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -4111,24 +4271,24 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -4143,24 +4303,24 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -4182,30 +4342,94 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:51:34</t>
+          <t>2026-09-18 15:40:19</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>iit-delhi-dms-mba</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-mba.html</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:40:19</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>iit-delhi-dms-placements.html</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:40:19</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
           <t>iit-delhi-dms</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>iit-delhi-dms.html</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>AUDITED – NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19 UTC</t>
+          <t>2026-09-18 15:42:29 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>33c28e4f22ca12c37a93fb96a922a3e85fa3a924</t>
+          <t>ff22928a16ad3c915f47af28ec18e611c01f971f</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -3510,7 +3510,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>33c28e4f22ca12c37a93fb96a922a3e85fa3a924</t>
+          <t>ff22928a16ad3c915f47af28ec18e611c01f971f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4214,7 +4214,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4278,7 +4278,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4310,7 +4310,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -4374,7 +4374,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:40:19</t>
+          <t>2026-09-18 15:42:29</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29 UTC</t>
+          <t>2026-09-18 15:45:34 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>ff22928a16ad3c915f47af28ec18e611c01f971f</t>
+          <t>cef2b27c4acc60765783eb2b476c5e06939a021d</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -3510,7 +3510,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3695,14 +3695,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3727,14 +3727,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3759,14 +3759,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3823,14 +3823,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>ff22928a16ad3c915f47af28ec18e611c01f971f</t>
+          <t>cef2b27c4acc60765783eb2b476c5e06939a021d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4214,7 +4214,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4278,7 +4278,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4310,7 +4310,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -4374,7 +4374,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:42:29</t>
+          <t>2026-09-18 15:45:34</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34 UTC</t>
+          <t>2026-09-18 15:46:43 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>cef2b27c4acc60765783eb2b476c5e06939a021d</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -3510,7 +3510,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3695,14 +3695,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3727,14 +3727,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3759,14 +3759,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3823,14 +3823,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>3064c2c39ede2d0f3bc530d589928ba65c2325e3</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>cef2b27c4acc60765783eb2b476c5e06939a021d</t>
+          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4214,7 +4214,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4278,7 +4278,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4310,7 +4310,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -4374,7 +4374,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:34</t>
+          <t>2026-09-18 15:46:43</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43 UTC</t>
+          <t>2026-09-18 15:47:38 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>642c70a724a76d859d85db984ad23c97cdff896b</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -3510,7 +3510,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>642c70a724a76d859d85db984ad23c97cdff896b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4214,7 +4214,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4278,7 +4278,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4310,7 +4310,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -4374,7 +4374,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:46:43</t>
+          <t>2026-09-18 15:47:38</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38 UTC</t>
+          <t>2026-09-18 15:50:27 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>642c70a724a76d859d85db984ad23c97cdff896b</t>
+          <t>cf829595705e98ce1ad2f74bb54c314e8a0d4c44</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -3510,7 +3510,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>642c70a724a76d859d85db984ad23c97cdff896b</t>
+          <t>cf829595705e98ce1ad2f74bb54c314e8a0d4c44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4214,7 +4214,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4278,7 +4278,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4310,7 +4310,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -4374,7 +4374,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:47:38</t>
+          <t>2026-09-18 15:50:27</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P30" headerRowCount="1">
-  <autoFilter ref="A1:P30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P28" headerRowCount="1">
+  <autoFilter ref="A1:P28"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27 UTC</t>
+          <t>2026-09-18 16:42:15 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1972,17 +1972,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba</t>
+          <t>iim-kozhikode-pgp-bl</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba.html</t>
+          <t>iim-kozhikode-pgp-bl.html</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -2000,9 +2000,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -2037,27 +2037,27 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 4 issue group(s)</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>042d1e184deb58a25b82e52cf9864f4d0f01976d</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-bl</t>
+          <t>iim-kozhikode-pgp-finance</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-bl.html</t>
+          <t>iim-kozhikode-pgp-finance.html</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2117,27 +2117,27 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 4 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>042d1e184deb58a25b82e52cf9864f4d0f01976d</t>
+          <t>46c98d4bc2422b190774491517a6a88e0ba53895</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance</t>
+          <t>iim-kozhikode-pgp-lsm</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance.html</t>
+          <t>iim-kozhikode-pgp-lsm.html</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2197,32 +2197,32 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>46c98d4bc2422b190774491517a6a88e0ba53895</t>
+          <t>52a1c774ffd4dda2fbceb9f14376400ad59022cb</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-lsm</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-lsm.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Placement</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -2240,9 +2240,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -2277,32 +2277,32 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>52a1c774ffd4dda2fbceb9f14376400ad59022cb</t>
+          <t>0af6b039e3fff954ed447e3d81915e1537f78ac2</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -2320,9 +2320,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -2357,27 +2357,27 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>0af6b039e3fff954ed447e3d81915e1537f78ac2</t>
+          <t>121b44523f65ef3c785752256e326e05710b207a</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>iim-lucknow</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-lucknow.html</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2437,27 +2437,27 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>121b44523f65ef3c785752256e326e05710b207a</t>
+          <t>343636b326bd127d8eb761b5b18db85ec69439bd</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>iim-lucknow</t>
+          <t>IIM Mumbai</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>iim-lucknow.html</t>
+          <t>iim-mumbai.html</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2517,32 +2517,32 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 1 issue group(s)</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>343636b326bd127d8eb761b5b18db85ec69439bd</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>IIM Mumbai</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>iim-mumbai.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -2560,9 +2560,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -2597,32 +2597,32 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 1 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Course-specific</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -2640,9 +2640,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -2677,27 +2677,27 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 3 issue group(s)</t>
+          <t>Content audit: 2 issue group(s)</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>iit-delhi-dms-mba</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iit-delhi-dms-mba.html</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2757,32 +2757,32 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>iit-delhi-dms-placements</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iit-delhi-dms-placements.html</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Placement</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 2 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -2846,23 +2846,23 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms.html</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -2922,170 +2922,10 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms-placements</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms-placements.html</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Placement</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 3 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms.html</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 3 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n">
         <v>78</v>
       </c>
     </row>
@@ -3464,7 +3304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3510,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3535,14 +3375,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3567,14 +3407,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3599,14 +3439,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3631,14 +3471,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3663,14 +3503,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3695,14 +3535,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3727,14 +3567,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3759,14 +3599,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3791,14 +3631,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3823,14 +3663,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>78f61052def800ef6088b6dca2d7d7c2725c2235</t>
+          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3862,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3894,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3926,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3958,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3990,17 +3830,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba</t>
+          <t>iim-kozhikode-pgp-bl</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-mba.html</t>
+          <t>iim-kozhikode-pgp-bl.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -4015,24 +3855,24 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>b1ab22bfe1d0c4c583f6cc76a84d84ab8b6481e4</t>
+          <t>042d1e184deb58a25b82e52cf9864f4d0f01976d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-bl</t>
+          <t>iim-kozhikode-pgp-finance</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-bl.html</t>
+          <t>iim-kozhikode-pgp-finance.html</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -4047,24 +3887,24 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>042d1e184deb58a25b82e52cf9864f4d0f01976d</t>
+          <t>46c98d4bc2422b190774491517a6a88e0ba53895</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance</t>
+          <t>iim-kozhikode-pgp-lsm</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-finance.html</t>
+          <t>iim-kozhikode-pgp-lsm.html</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -4079,24 +3919,24 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>46c98d4bc2422b190774491517a6a88e0ba53895</t>
+          <t>52a1c774ffd4dda2fbceb9f14376400ad59022cb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-lsm</t>
+          <t>iim-kozhikode-placements</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-pgp-lsm.html</t>
+          <t>iim-kozhikode-placements.html</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -4111,24 +3951,24 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>52a1c774ffd4dda2fbceb9f14376400ad59022cb</t>
+          <t>0af6b039e3fff954ed447e3d81915e1537f78ac2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements</t>
+          <t>iim-kozhikode</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode-placements.html</t>
+          <t>iim-kozhikode.html</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -4143,24 +3983,24 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>0af6b039e3fff954ed447e3d81915e1537f78ac2</t>
+          <t>121b44523f65ef3c785752256e326e05710b207a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode</t>
+          <t>iim-lucknow</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>iim-kozhikode.html</t>
+          <t>iim-lucknow.html</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -4175,24 +4015,24 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>121b44523f65ef3c785752256e326e05710b207a</t>
+          <t>343636b326bd127d8eb761b5b18db85ec69439bd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>iim-lucknow</t>
+          <t>IIM Mumbai</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>iim-lucknow.html</t>
+          <t>iim-mumbai.html</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -4207,24 +4047,24 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>343636b326bd127d8eb761b5b18db85ec69439bd</t>
+          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>IIM Mumbai</t>
+          <t>iit-delhi-dms-executive-mba</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>iim-mumbai.html</t>
+          <t>iit-delhi-dms-executive-mba.html</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -4239,24 +4079,24 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>8678dd6135e041f1fb009702b6ce883cf4075c74</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>IIM Udaipur</t>
+          <t>iit-delhi-dms-mba-telecom</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>iim-udaipur.html</t>
+          <t>iit-delhi-dms-mba-telecom.html</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -4271,24 +4111,24 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>814ae6c82f2752d39ca357db9c7ba1ac75ac16e8</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba</t>
+          <t>iit-delhi-dms-mba</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-executive-mba.html</t>
+          <t>iit-delhi-dms-mba.html</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -4303,24 +4143,24 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom</t>
+          <t>iit-delhi-dms-placements</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba-telecom.html</t>
+          <t>iit-delhi-dms-placements.html</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -4342,17 +4182,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:50:27</t>
+          <t>2026-09-18 16:42:15</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms.html</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4366,70 +4206,6 @@
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18 15:50:27</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms-placements</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms-placements.html</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18 15:50:27</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms.html</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15 UTC</t>
+          <t>2026-09-18 16:42:53 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:15</t>
+          <t>2026-09-18 16:42:53</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53 UTC</t>
+          <t>2026-09-18 16:44:57 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:42:53</t>
+          <t>2026-09-18 16:44:57</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57 UTC</t>
+          <t>2026-09-18 17:06:11 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1605,19 +1605,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2085,19 +2085,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2245,19 +2245,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -2325,19 +2325,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -2405,19 +2405,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -2485,19 +2485,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -2565,19 +2565,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -2645,19 +2645,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -2725,19 +2725,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -2805,19 +2805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -2885,19 +2885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 16:44:57</t>
+          <t>2026-09-18 17:06:11</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11 UTC</t>
+          <t>2026-09-18 19:36:55 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:06:11</t>
+          <t>2026-09-18 19:36:55</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55 UTC</t>
+          <t>2026-09-18 21:53:49 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:36:55</t>
+          <t>2026-09-18 21:53:49</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49 UTC</t>
+          <t>2026-09-18 23:54:49 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 21:53:49</t>
+          <t>2026-09-18 23:54:49</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49 UTC</t>
+          <t>2026-09-19 03:17:43 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1605,19 +1605,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2085,19 +2085,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2245,19 +2245,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -2325,19 +2325,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -2405,19 +2405,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -2485,19 +2485,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -2565,19 +2565,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -2645,19 +2645,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -2725,19 +2725,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -2805,19 +2805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -2885,19 +2885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>737d798ddaf13a718ed93a386a8662c37943e8ab</t>
+          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:54:49</t>
+          <t>2026-09-19 03:17:43</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43 UTC</t>
+          <t>2026-09-19 03:28:21 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1605,19 +1605,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2085,19 +2085,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2245,19 +2245,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -2325,19 +2325,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -2405,19 +2405,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -2485,19 +2485,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -2565,19 +2565,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -2645,19 +2645,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -2725,19 +2725,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -2805,19 +2805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -2885,19 +2885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>3569aa329b6d2e87bc4f17fe4d086766d129216a</t>
+          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:17:43</t>
+          <t>2026-09-19 03:28:21</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21 UTC</t>
+          <t>2026-09-19 03:30:08 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -805,19 +805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -885,19 +885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -965,19 +965,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1045,19 +1045,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1125,19 +1125,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1205,19 +1205,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1285,19 +1285,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1365,19 +1365,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1445,19 +1445,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1525,19 +1525,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -1605,19 +1605,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1685,19 +1685,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1765,19 +1765,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1845,19 +1845,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1925,19 +1925,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -2005,19 +2005,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2085,19 +2085,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -2165,19 +2165,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -2245,19 +2245,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -2325,19 +2325,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -2405,19 +2405,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -2485,19 +2485,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -2565,19 +2565,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -2645,19 +2645,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -2725,19 +2725,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -2805,19 +2805,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -2885,19 +2885,19 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>daa4adf560fed7945d17e1b5a2dc6de25a20f15c</t>
+          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:28:21</t>
+          <t>2026-09-19 03:30:08</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08 UTC</t>
+          <t>2026-09-19 03:34:34 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:30:08</t>
+          <t>2026-09-19 03:34:34</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34 UTC</t>
+          <t>2026-09-19 03:40:38 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>952e7d3675861e3ee1fd33a07500f498f457fe44</t>
+          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:34:34</t>
+          <t>2026-09-19 03:40:38</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38 UTC</t>
+          <t>2026-09-19 03:51:32 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>a6a1f3908cc70579470312b14ed5c39d46fe4f60</t>
+          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:40:38</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32 UTC</t>
+          <t>2026-09-19 03:52:31 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3350,7 +3350,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-19 03:52:31</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P28" headerRowCount="1">
-  <autoFilter ref="A1:P28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiveAuditQueue" displayName="LiveAuditQueue" ref="A1:P27" headerRowCount="1">
+  <autoFilter ref="A1:P27"/>
   <tableColumns count="16">
     <tableColumn id="1" name="College"/>
     <tableColumn id="2" name="Page"/>
@@ -580,11 +580,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31 UTC</t>
+          <t>2026-09-19 04:00:56 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2692,17 +2692,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-placements</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-placements.html</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Course-specific</t>
+          <t>Placement</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -2762,27 +2762,27 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms.html</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -2842,90 +2842,10 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
+          <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms.html</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>Content audit: 3 issue group(s)</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="n">
         <v>78</v>
       </c>
     </row>
@@ -3304,7 +3224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3350,7 +3270,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3382,7 +3302,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3414,7 +3334,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3446,7 +3366,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3478,7 +3398,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3510,7 +3430,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3542,7 +3462,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3574,7 +3494,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3606,7 +3526,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3638,7 +3558,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3670,7 +3590,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3702,7 +3622,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3734,7 +3654,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3766,7 +3686,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3798,7 +3718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3830,7 +3750,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3862,7 +3782,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3894,7 +3814,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3926,7 +3846,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3958,7 +3878,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3990,7 +3910,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4022,7 +3942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4054,7 +3974,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4086,7 +4006,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4118,17 +4038,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba</t>
+          <t>iit-delhi-dms-placements</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-mba.html</t>
+          <t>iit-delhi-dms-placements.html</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -4143,24 +4063,24 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>3c46c75a0518ec1263b599656bce5a7391cd6e99</t>
+          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 03:52:31</t>
+          <t>2026-09-19 04:00:56</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements</t>
+          <t>iit-delhi-dms</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>iit-delhi-dms-placements.html</t>
+          <t>iit-delhi-dms.html</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -4174,38 +4094,6 @@
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>b4fbcf22f140914724ffeecec924a952b6ed0092</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-19 03:52:31</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>iit-delhi-dms.html</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>AUDITED – NO CHANGE</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>8b2f16c20513a6d6cdcefabefb30223f7745c4da</t>
         </is>

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56 UTC</t>
+          <t>2026-09-19 04:05:25 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3270,7 +3270,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3878,7 +3878,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3942,7 +3942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3974,7 +3974,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4038,7 +4038,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4070,7 +4070,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:56</t>
+          <t>2026-09-19 04:05:25</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25 UTC</t>
+          <t>2026-09-19 05:48:06 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -3270,7 +3270,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3295,14 +3295,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3327,14 +3327,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3359,14 +3359,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3391,14 +3391,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3423,14 +3423,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3455,14 +3455,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3487,14 +3487,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3519,14 +3519,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3551,14 +3551,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3583,14 +3583,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>37a86e4ebb6fcb59e834de1a52cab36e3c910ba1</t>
+          <t>d47f86f718ac112c86d2b3255d10affca9f547ee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3878,7 +3878,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3942,7 +3942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3974,7 +3974,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4038,7 +4038,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4070,7 +4070,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 04:05:25</t>
+          <t>2026-09-19 05:48:06</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06 UTC</t>
+          <t>2026-09-19 05:48:50 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3270,7 +3270,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3878,7 +3878,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3942,7 +3942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3974,7 +3974,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4038,7 +4038,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4070,7 +4070,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 05:48:06</t>
+          <t>2026-09-19 05:48:50</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00 UTC</t>
+          <t>2026-10-08 20:50:22 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -53270,7 +53270,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -53302,7 +53302,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -53334,7 +53334,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -53366,7 +53366,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -53398,7 +53398,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -53430,7 +53430,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -53462,7 +53462,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -53494,7 +53494,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -53526,7 +53526,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -53558,7 +53558,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -53590,7 +53590,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -53622,7 +53622,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -53654,7 +53654,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -53686,7 +53686,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -53718,7 +53718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -53750,7 +53750,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -53782,7 +53782,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -53814,7 +53814,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -53846,7 +53846,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -53878,7 +53878,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -53910,7 +53910,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -53942,7 +53942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -53974,7 +53974,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -54006,7 +54006,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -54038,7 +54038,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -54070,7 +54070,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -54102,7 +54102,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -54134,7 +54134,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -54166,7 +54166,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -54198,7 +54198,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -54230,7 +54230,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -54262,7 +54262,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -54294,7 +54294,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -54326,7 +54326,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -54358,7 +54358,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -54390,7 +54390,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -54422,7 +54422,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -54454,7 +54454,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -54486,7 +54486,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -54518,7 +54518,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -54550,7 +54550,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -54582,7 +54582,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -54614,7 +54614,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -54646,7 +54646,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -54678,7 +54678,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -54710,7 +54710,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -54742,7 +54742,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -54774,7 +54774,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -54806,7 +54806,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -54838,7 +54838,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -54870,7 +54870,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -54902,7 +54902,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -54934,7 +54934,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -54966,7 +54966,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -54998,7 +54998,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -55030,7 +55030,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -55062,7 +55062,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -55094,7 +55094,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -55126,7 +55126,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -55158,7 +55158,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -55190,7 +55190,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -55222,7 +55222,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -55254,7 +55254,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -55286,7 +55286,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -55318,7 +55318,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -55350,7 +55350,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -55382,7 +55382,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -55414,7 +55414,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -55446,7 +55446,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -55478,7 +55478,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -55510,7 +55510,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -55542,7 +55542,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -55574,7 +55574,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -55606,7 +55606,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -55638,7 +55638,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -55670,7 +55670,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -55702,7 +55702,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -55734,7 +55734,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -55766,7 +55766,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -55798,7 +55798,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -55830,7 +55830,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -55862,7 +55862,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -55894,7 +55894,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -55926,7 +55926,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -55958,7 +55958,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -55990,7 +55990,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -56022,7 +56022,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -56054,7 +56054,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -56086,7 +56086,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -56118,7 +56118,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -56150,7 +56150,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -56182,7 +56182,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -56214,7 +56214,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -56246,7 +56246,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -56278,7 +56278,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -56310,7 +56310,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -56342,7 +56342,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -56374,7 +56374,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -56406,7 +56406,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -56438,7 +56438,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -56470,7 +56470,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -56502,7 +56502,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -56534,7 +56534,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -56566,7 +56566,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -56598,7 +56598,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -56630,7 +56630,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -56662,7 +56662,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -56694,7 +56694,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -56726,7 +56726,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -56758,7 +56758,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -56790,7 +56790,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -56822,7 +56822,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -56854,7 +56854,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -56886,7 +56886,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -56918,7 +56918,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -56950,7 +56950,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -56982,7 +56982,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -57014,7 +57014,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -57046,7 +57046,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -57078,7 +57078,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -57110,7 +57110,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -57142,7 +57142,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -57174,7 +57174,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -57206,7 +57206,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -57238,7 +57238,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -57270,7 +57270,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -57302,7 +57302,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -57334,7 +57334,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -57366,7 +57366,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -57398,7 +57398,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -57430,7 +57430,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -57462,7 +57462,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -57494,7 +57494,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -57526,7 +57526,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -57558,7 +57558,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -57590,7 +57590,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -57622,7 +57622,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -57654,7 +57654,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -57686,7 +57686,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -57718,7 +57718,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -57750,7 +57750,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -57782,7 +57782,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -57814,7 +57814,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -57846,7 +57846,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -57878,7 +57878,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -57910,7 +57910,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -57942,7 +57942,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -57974,7 +57974,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -58006,7 +58006,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -58038,7 +58038,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -58070,7 +58070,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -58102,7 +58102,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -58134,7 +58134,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -58166,7 +58166,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -58198,7 +58198,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -58230,7 +58230,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -58262,7 +58262,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -58294,7 +58294,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -58326,7 +58326,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -58358,7 +58358,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -58390,7 +58390,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -58422,7 +58422,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -58454,7 +58454,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -58486,7 +58486,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -58518,7 +58518,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -58550,7 +58550,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -58582,7 +58582,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -58614,7 +58614,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -58646,7 +58646,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -58678,7 +58678,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -58710,7 +58710,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -58742,7 +58742,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -58774,7 +58774,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -58806,7 +58806,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -58838,7 +58838,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -58870,7 +58870,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -58902,7 +58902,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -58934,7 +58934,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -58966,7 +58966,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -58998,7 +58998,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -59030,7 +59030,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -59062,7 +59062,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -59094,7 +59094,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -59126,7 +59126,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -59158,7 +59158,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -59190,7 +59190,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -59222,7 +59222,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -59254,7 +59254,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -59286,7 +59286,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -59318,7 +59318,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -59350,7 +59350,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -59382,7 +59382,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -59414,7 +59414,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -59446,7 +59446,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -59478,7 +59478,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -59510,7 +59510,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -59542,7 +59542,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -59574,7 +59574,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -59606,7 +59606,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -59638,7 +59638,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -59670,7 +59670,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -59702,7 +59702,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -59734,7 +59734,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -59766,7 +59766,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -59798,7 +59798,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -59830,7 +59830,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -59862,7 +59862,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -59894,7 +59894,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -59926,7 +59926,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -59958,7 +59958,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -59990,7 +59990,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -60022,7 +60022,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -60054,7 +60054,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -60086,7 +60086,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -60118,7 +60118,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -60150,7 +60150,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -60182,7 +60182,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -60214,7 +60214,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -60246,7 +60246,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -60278,7 +60278,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -60310,7 +60310,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -60342,7 +60342,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -60374,7 +60374,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -60406,7 +60406,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -60438,7 +60438,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -60470,7 +60470,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -60502,7 +60502,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -60534,7 +60534,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -60566,7 +60566,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -60598,7 +60598,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -60630,7 +60630,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -60662,7 +60662,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -60694,7 +60694,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -60726,7 +60726,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -60758,7 +60758,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -60790,7 +60790,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -60822,7 +60822,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -60854,7 +60854,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -60886,7 +60886,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -60918,7 +60918,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -60950,7 +60950,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -60982,7 +60982,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -61014,7 +61014,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -61046,7 +61046,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -61078,7 +61078,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -61110,7 +61110,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -61142,7 +61142,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -61174,7 +61174,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -61206,7 +61206,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -61238,7 +61238,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -61270,7 +61270,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -61302,7 +61302,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -61334,7 +61334,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -61366,7 +61366,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -61398,7 +61398,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -61430,7 +61430,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -61462,7 +61462,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -61494,7 +61494,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -61526,7 +61526,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -61558,7 +61558,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -61590,7 +61590,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -61622,7 +61622,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -61654,7 +61654,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -61686,7 +61686,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -61718,7 +61718,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -61750,7 +61750,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -61782,7 +61782,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -61814,7 +61814,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -61846,7 +61846,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -61878,7 +61878,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -61910,7 +61910,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -61942,7 +61942,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -61974,7 +61974,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -62006,7 +62006,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -62038,7 +62038,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -62070,7 +62070,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -62102,7 +62102,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -62134,7 +62134,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -62166,7 +62166,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -62198,7 +62198,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -62230,7 +62230,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -62262,7 +62262,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -62294,7 +62294,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -62326,7 +62326,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -62358,7 +62358,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -62390,7 +62390,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -62422,7 +62422,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -62454,7 +62454,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -62486,7 +62486,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -62518,7 +62518,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -62550,7 +62550,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -62582,7 +62582,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -62614,7 +62614,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -62646,7 +62646,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -62678,7 +62678,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -62710,7 +62710,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -62742,7 +62742,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -62774,7 +62774,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -62806,7 +62806,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -62838,7 +62838,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
@@ -62870,7 +62870,7 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
@@ -62902,7 +62902,7 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
@@ -62934,7 +62934,7 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -62966,7 +62966,7 @@
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
@@ -62998,7 +62998,7 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -63030,7 +63030,7 @@
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
@@ -63062,7 +63062,7 @@
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
@@ -63094,7 +63094,7 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
@@ -63126,7 +63126,7 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
@@ -63158,7 +63158,7 @@
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
@@ -63190,7 +63190,7 @@
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -63222,7 +63222,7 @@
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B313" s="3" t="inlineStr">
@@ -63254,7 +63254,7 @@
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
@@ -63286,7 +63286,7 @@
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
@@ -63318,7 +63318,7 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
@@ -63350,7 +63350,7 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B317" s="3" t="inlineStr">
@@ -63382,7 +63382,7 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
@@ -63414,7 +63414,7 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
@@ -63446,7 +63446,7 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
@@ -63478,7 +63478,7 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
@@ -63510,7 +63510,7 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
@@ -63542,7 +63542,7 @@
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B323" s="3" t="inlineStr">
@@ -63574,7 +63574,7 @@
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
@@ -63606,7 +63606,7 @@
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B325" s="3" t="inlineStr">
@@ -63638,7 +63638,7 @@
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
@@ -63670,7 +63670,7 @@
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B327" s="3" t="inlineStr">
@@ -63702,7 +63702,7 @@
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
@@ -63734,7 +63734,7 @@
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B329" s="3" t="inlineStr">
@@ -63766,7 +63766,7 @@
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
@@ -63798,7 +63798,7 @@
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B331" s="3" t="inlineStr">
@@ -63830,7 +63830,7 @@
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
@@ -63862,7 +63862,7 @@
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B333" s="3" t="inlineStr">
@@ -63894,7 +63894,7 @@
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
@@ -63926,7 +63926,7 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B335" s="3" t="inlineStr">
@@ -63958,7 +63958,7 @@
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
@@ -63990,7 +63990,7 @@
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B337" s="3" t="inlineStr">
@@ -64022,7 +64022,7 @@
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
@@ -64054,7 +64054,7 @@
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B339" s="3" t="inlineStr">
@@ -64086,7 +64086,7 @@
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
@@ -64118,7 +64118,7 @@
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B341" s="3" t="inlineStr">
@@ -64150,7 +64150,7 @@
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
@@ -64182,7 +64182,7 @@
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B343" s="3" t="inlineStr">
@@ -64214,7 +64214,7 @@
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
@@ -64246,7 +64246,7 @@
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B345" s="3" t="inlineStr">
@@ -64278,7 +64278,7 @@
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
@@ -64310,7 +64310,7 @@
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B347" s="3" t="inlineStr">
@@ -64342,7 +64342,7 @@
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
@@ -64374,7 +64374,7 @@
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B349" s="3" t="inlineStr">
@@ -64406,7 +64406,7 @@
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
@@ -64438,7 +64438,7 @@
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B351" s="3" t="inlineStr">
@@ -64470,7 +64470,7 @@
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
@@ -64502,7 +64502,7 @@
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B353" s="3" t="inlineStr">
@@ -64534,7 +64534,7 @@
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
@@ -64566,7 +64566,7 @@
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B355" s="3" t="inlineStr">
@@ -64598,7 +64598,7 @@
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
@@ -64630,7 +64630,7 @@
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B357" s="3" t="inlineStr">
@@ -64662,7 +64662,7 @@
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
@@ -64694,7 +64694,7 @@
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B359" s="3" t="inlineStr">
@@ -64726,7 +64726,7 @@
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
@@ -64758,7 +64758,7 @@
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B361" s="3" t="inlineStr">
@@ -64790,7 +64790,7 @@
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
@@ -64822,7 +64822,7 @@
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B363" s="3" t="inlineStr">
@@ -64854,7 +64854,7 @@
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
@@ -64886,7 +64886,7 @@
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B365" s="3" t="inlineStr">
@@ -64918,7 +64918,7 @@
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
@@ -64950,7 +64950,7 @@
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B367" s="3" t="inlineStr">
@@ -64982,7 +64982,7 @@
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
@@ -65014,7 +65014,7 @@
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B369" s="3" t="inlineStr">
@@ -65046,7 +65046,7 @@
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
@@ -65078,7 +65078,7 @@
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B371" s="3" t="inlineStr">
@@ -65110,7 +65110,7 @@
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
@@ -65142,7 +65142,7 @@
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B373" s="3" t="inlineStr">
@@ -65174,7 +65174,7 @@
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
@@ -65206,7 +65206,7 @@
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B375" s="3" t="inlineStr">
@@ -65238,7 +65238,7 @@
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
@@ -65270,7 +65270,7 @@
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B377" s="3" t="inlineStr">
@@ -65302,7 +65302,7 @@
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
@@ -65334,7 +65334,7 @@
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B379" s="3" t="inlineStr">
@@ -65366,7 +65366,7 @@
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
@@ -65398,7 +65398,7 @@
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B381" s="3" t="inlineStr">
@@ -65430,7 +65430,7 @@
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
@@ -65462,7 +65462,7 @@
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B383" s="3" t="inlineStr">
@@ -65494,7 +65494,7 @@
     <row r="384">
       <c r="A384" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
@@ -65526,7 +65526,7 @@
     <row r="385">
       <c r="A385" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B385" s="3" t="inlineStr">
@@ -65558,7 +65558,7 @@
     <row r="386">
       <c r="A386" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
@@ -65590,7 +65590,7 @@
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B387" s="3" t="inlineStr">
@@ -65622,7 +65622,7 @@
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
@@ -65654,7 +65654,7 @@
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B389" s="3" t="inlineStr">
@@ -65686,7 +65686,7 @@
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
@@ -65718,7 +65718,7 @@
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B391" s="3" t="inlineStr">
@@ -65750,7 +65750,7 @@
     <row r="392">
       <c r="A392" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
@@ -65782,7 +65782,7 @@
     <row r="393">
       <c r="A393" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B393" s="3" t="inlineStr">
@@ -65814,7 +65814,7 @@
     <row r="394">
       <c r="A394" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
@@ -65846,7 +65846,7 @@
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B395" s="3" t="inlineStr">
@@ -65878,7 +65878,7 @@
     <row r="396">
       <c r="A396" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
@@ -65910,7 +65910,7 @@
     <row r="397">
       <c r="A397" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B397" s="3" t="inlineStr">
@@ -65942,7 +65942,7 @@
     <row r="398">
       <c r="A398" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
@@ -65974,7 +65974,7 @@
     <row r="399">
       <c r="A399" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B399" s="3" t="inlineStr">
@@ -66006,7 +66006,7 @@
     <row r="400">
       <c r="A400" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
@@ -66038,7 +66038,7 @@
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B401" s="3" t="inlineStr">
@@ -66070,7 +66070,7 @@
     <row r="402">
       <c r="A402" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
@@ -66102,7 +66102,7 @@
     <row r="403">
       <c r="A403" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B403" s="3" t="inlineStr">
@@ -66134,7 +66134,7 @@
     <row r="404">
       <c r="A404" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
@@ -66166,7 +66166,7 @@
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B405" s="3" t="inlineStr">
@@ -66198,7 +66198,7 @@
     <row r="406">
       <c r="A406" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
@@ -66230,7 +66230,7 @@
     <row r="407">
       <c r="A407" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B407" s="3" t="inlineStr">
@@ -66262,7 +66262,7 @@
     <row r="408">
       <c r="A408" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
@@ -66294,7 +66294,7 @@
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B409" s="3" t="inlineStr">
@@ -66326,7 +66326,7 @@
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
@@ -66358,7 +66358,7 @@
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B411" s="3" t="inlineStr">
@@ -66390,7 +66390,7 @@
     <row r="412">
       <c r="A412" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
@@ -66422,7 +66422,7 @@
     <row r="413">
       <c r="A413" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B413" s="3" t="inlineStr">
@@ -66454,7 +66454,7 @@
     <row r="414">
       <c r="A414" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
@@ -66486,7 +66486,7 @@
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B415" s="3" t="inlineStr">
@@ -66518,7 +66518,7 @@
     <row r="416">
       <c r="A416" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B416" s="3" t="inlineStr">
@@ -66550,7 +66550,7 @@
     <row r="417">
       <c r="A417" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B417" s="3" t="inlineStr">
@@ -66582,7 +66582,7 @@
     <row r="418">
       <c r="A418" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -66614,7 +66614,7 @@
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B419" s="3" t="inlineStr">
@@ -66646,7 +66646,7 @@
     <row r="420">
       <c r="A420" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
@@ -66678,7 +66678,7 @@
     <row r="421">
       <c r="A421" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B421" s="3" t="inlineStr">
@@ -66710,7 +66710,7 @@
     <row r="422">
       <c r="A422" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B422" s="3" t="inlineStr">
@@ -66742,7 +66742,7 @@
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B423" s="3" t="inlineStr">
@@ -66774,7 +66774,7 @@
     <row r="424">
       <c r="A424" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
@@ -66806,7 +66806,7 @@
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B425" s="3" t="inlineStr">
@@ -66838,7 +66838,7 @@
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
@@ -66870,7 +66870,7 @@
     <row r="427">
       <c r="A427" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B427" s="3" t="inlineStr">
@@ -66902,7 +66902,7 @@
     <row r="428">
       <c r="A428" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
@@ -66934,7 +66934,7 @@
     <row r="429">
       <c r="A429" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B429" s="3" t="inlineStr">
@@ -66966,7 +66966,7 @@
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
@@ -66998,7 +66998,7 @@
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B431" s="3" t="inlineStr">
@@ -67030,7 +67030,7 @@
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
@@ -67062,7 +67062,7 @@
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B433" s="3" t="inlineStr">
@@ -67094,7 +67094,7 @@
     <row r="434">
       <c r="A434" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
@@ -67126,7 +67126,7 @@
     <row r="435">
       <c r="A435" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B435" s="3" t="inlineStr">
@@ -67158,7 +67158,7 @@
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
@@ -67190,7 +67190,7 @@
     <row r="437">
       <c r="A437" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B437" s="3" t="inlineStr">
@@ -67222,7 +67222,7 @@
     <row r="438">
       <c r="A438" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
@@ -67254,7 +67254,7 @@
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B439" s="3" t="inlineStr">
@@ -67286,7 +67286,7 @@
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -67318,7 +67318,7 @@
     <row r="441">
       <c r="A441" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B441" s="3" t="inlineStr">
@@ -67350,7 +67350,7 @@
     <row r="442">
       <c r="A442" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -67382,7 +67382,7 @@
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B443" s="3" t="inlineStr">
@@ -67414,7 +67414,7 @@
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
@@ -67446,7 +67446,7 @@
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B445" s="3" t="inlineStr">
@@ -67478,7 +67478,7 @@
     <row r="446">
       <c r="A446" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
@@ -67510,7 +67510,7 @@
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B447" s="3" t="inlineStr">
@@ -67542,7 +67542,7 @@
     <row r="448">
       <c r="A448" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
@@ -67574,7 +67574,7 @@
     <row r="449">
       <c r="A449" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B449" s="3" t="inlineStr">
@@ -67606,7 +67606,7 @@
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
@@ -67638,7 +67638,7 @@
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B451" s="3" t="inlineStr">
@@ -67670,7 +67670,7 @@
     <row r="452">
       <c r="A452" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
@@ -67702,7 +67702,7 @@
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B453" s="3" t="inlineStr">
@@ -67734,7 +67734,7 @@
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
@@ -67766,7 +67766,7 @@
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B455" s="3" t="inlineStr">
@@ -67798,7 +67798,7 @@
     <row r="456">
       <c r="A456" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
@@ -67830,7 +67830,7 @@
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B457" s="3" t="inlineStr">
@@ -67862,7 +67862,7 @@
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
@@ -67894,7 +67894,7 @@
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B459" s="3" t="inlineStr">
@@ -67926,7 +67926,7 @@
     <row r="460">
       <c r="A460" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
@@ -67958,7 +67958,7 @@
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B461" s="3" t="inlineStr">
@@ -67990,7 +67990,7 @@
     <row r="462">
       <c r="A462" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
@@ -68022,7 +68022,7 @@
     <row r="463">
       <c r="A463" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B463" s="3" t="inlineStr">
@@ -68054,7 +68054,7 @@
     <row r="464">
       <c r="A464" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B464" s="3" t="inlineStr">
@@ -68086,7 +68086,7 @@
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B465" s="3" t="inlineStr">
@@ -68118,7 +68118,7 @@
     <row r="466">
       <c r="A466" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
@@ -68150,7 +68150,7 @@
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B467" s="3" t="inlineStr">
@@ -68182,7 +68182,7 @@
     <row r="468">
       <c r="A468" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
@@ -68214,7 +68214,7 @@
     <row r="469">
       <c r="A469" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B469" s="3" t="inlineStr">
@@ -68246,7 +68246,7 @@
     <row r="470">
       <c r="A470" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
@@ -68278,7 +68278,7 @@
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B471" s="3" t="inlineStr">
@@ -68310,7 +68310,7 @@
     <row r="472">
       <c r="A472" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B472" s="3" t="inlineStr">
@@ -68342,7 +68342,7 @@
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B473" s="3" t="inlineStr">
@@ -68374,7 +68374,7 @@
     <row r="474">
       <c r="A474" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B474" s="3" t="inlineStr">
@@ -68406,7 +68406,7 @@
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B475" s="3" t="inlineStr">
@@ -68438,7 +68438,7 @@
     <row r="476">
       <c r="A476" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B476" s="3" t="inlineStr">
@@ -68470,7 +68470,7 @@
     <row r="477">
       <c r="A477" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B477" s="3" t="inlineStr">
@@ -68502,7 +68502,7 @@
     <row r="478">
       <c r="A478" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B478" s="3" t="inlineStr">
@@ -68534,7 +68534,7 @@
     <row r="479">
       <c r="A479" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B479" s="3" t="inlineStr">
@@ -68566,7 +68566,7 @@
     <row r="480">
       <c r="A480" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B480" s="3" t="inlineStr">
@@ -68598,7 +68598,7 @@
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B481" s="3" t="inlineStr">
@@ -68630,7 +68630,7 @@
     <row r="482">
       <c r="A482" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B482" s="3" t="inlineStr">
@@ -68662,7 +68662,7 @@
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B483" s="3" t="inlineStr">
@@ -68694,7 +68694,7 @@
     <row r="484">
       <c r="A484" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
@@ -68726,7 +68726,7 @@
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B485" s="3" t="inlineStr">
@@ -68758,7 +68758,7 @@
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B486" s="3" t="inlineStr">
@@ -68790,7 +68790,7 @@
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B487" s="3" t="inlineStr">
@@ -68822,7 +68822,7 @@
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B488" s="3" t="inlineStr">
@@ -68854,7 +68854,7 @@
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B489" s="3" t="inlineStr">
@@ -68886,7 +68886,7 @@
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B490" s="3" t="inlineStr">
@@ -68918,7 +68918,7 @@
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B491" s="3" t="inlineStr">
@@ -68950,7 +68950,7 @@
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B492" s="3" t="inlineStr">
@@ -68982,7 +68982,7 @@
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B493" s="3" t="inlineStr">
@@ -69014,7 +69014,7 @@
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B494" s="3" t="inlineStr">
@@ -69046,7 +69046,7 @@
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B495" s="3" t="inlineStr">
@@ -69078,7 +69078,7 @@
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B496" s="3" t="inlineStr">
@@ -69110,7 +69110,7 @@
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B497" s="3" t="inlineStr">
@@ -69142,7 +69142,7 @@
     <row r="498">
       <c r="A498" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B498" s="3" t="inlineStr">
@@ -69174,7 +69174,7 @@
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B499" s="3" t="inlineStr">
@@ -69206,7 +69206,7 @@
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B500" s="3" t="inlineStr">
@@ -69238,7 +69238,7 @@
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B501" s="3" t="inlineStr">
@@ -69270,7 +69270,7 @@
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B502" s="3" t="inlineStr">
@@ -69302,7 +69302,7 @@
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B503" s="3" t="inlineStr">
@@ -69334,7 +69334,7 @@
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B504" s="3" t="inlineStr">
@@ -69366,7 +69366,7 @@
     <row r="505">
       <c r="A505" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B505" s="3" t="inlineStr">
@@ -69398,7 +69398,7 @@
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B506" s="3" t="inlineStr">
@@ -69430,7 +69430,7 @@
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B507" s="3" t="inlineStr">
@@ -69462,7 +69462,7 @@
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B508" s="3" t="inlineStr">
@@ -69494,7 +69494,7 @@
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B509" s="3" t="inlineStr">
@@ -69526,7 +69526,7 @@
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B510" s="3" t="inlineStr">
@@ -69558,7 +69558,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B511" s="3" t="inlineStr">
@@ -69590,7 +69590,7 @@
     <row r="512">
       <c r="A512" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B512" s="3" t="inlineStr">
@@ -69622,7 +69622,7 @@
     <row r="513">
       <c r="A513" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B513" s="3" t="inlineStr">
@@ -69654,7 +69654,7 @@
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B514" s="3" t="inlineStr">
@@ -69686,7 +69686,7 @@
     <row r="515">
       <c r="A515" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B515" s="3" t="inlineStr">
@@ -69718,7 +69718,7 @@
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B516" s="3" t="inlineStr">
@@ -69750,7 +69750,7 @@
     <row r="517">
       <c r="A517" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B517" s="3" t="inlineStr">
@@ -69782,7 +69782,7 @@
     <row r="518">
       <c r="A518" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B518" s="3" t="inlineStr">
@@ -69814,7 +69814,7 @@
     <row r="519">
       <c r="A519" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B519" s="3" t="inlineStr">
@@ -69846,7 +69846,7 @@
     <row r="520">
       <c r="A520" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B520" s="3" t="inlineStr">
@@ -69878,7 +69878,7 @@
     <row r="521">
       <c r="A521" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B521" s="3" t="inlineStr">
@@ -69910,7 +69910,7 @@
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B522" s="3" t="inlineStr">
@@ -69942,7 +69942,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B523" s="3" t="inlineStr">
@@ -69974,7 +69974,7 @@
     <row r="524">
       <c r="A524" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B524" s="3" t="inlineStr">
@@ -70006,7 +70006,7 @@
     <row r="525">
       <c r="A525" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B525" s="3" t="inlineStr">
@@ -70038,7 +70038,7 @@
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B526" s="3" t="inlineStr">
@@ -70070,7 +70070,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B527" s="3" t="inlineStr">
@@ -70102,7 +70102,7 @@
     <row r="528">
       <c r="A528" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B528" s="3" t="inlineStr">
@@ -70134,7 +70134,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B529" s="3" t="inlineStr">
@@ -70166,7 +70166,7 @@
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B530" s="3" t="inlineStr">
@@ -70198,7 +70198,7 @@
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B531" s="3" t="inlineStr">
@@ -70230,7 +70230,7 @@
     <row r="532">
       <c r="A532" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B532" s="3" t="inlineStr">
@@ -70262,7 +70262,7 @@
     <row r="533">
       <c r="A533" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B533" s="3" t="inlineStr">
@@ -70294,7 +70294,7 @@
     <row r="534">
       <c r="A534" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B534" s="3" t="inlineStr">
@@ -70326,7 +70326,7 @@
     <row r="535">
       <c r="A535" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B535" s="3" t="inlineStr">
@@ -70358,7 +70358,7 @@
     <row r="536">
       <c r="A536" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B536" s="3" t="inlineStr">
@@ -70390,7 +70390,7 @@
     <row r="537">
       <c r="A537" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B537" s="3" t="inlineStr">
@@ -70422,7 +70422,7 @@
     <row r="538">
       <c r="A538" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B538" s="3" t="inlineStr">
@@ -70454,7 +70454,7 @@
     <row r="539">
       <c r="A539" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B539" s="3" t="inlineStr">
@@ -70486,7 +70486,7 @@
     <row r="540">
       <c r="A540" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B540" s="3" t="inlineStr">
@@ -70518,7 +70518,7 @@
     <row r="541">
       <c r="A541" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B541" s="3" t="inlineStr">
@@ -70550,7 +70550,7 @@
     <row r="542">
       <c r="A542" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B542" s="3" t="inlineStr">
@@ -70582,7 +70582,7 @@
     <row r="543">
       <c r="A543" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B543" s="3" t="inlineStr">
@@ -70614,7 +70614,7 @@
     <row r="544">
       <c r="A544" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B544" s="3" t="inlineStr">
@@ -70646,7 +70646,7 @@
     <row r="545">
       <c r="A545" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B545" s="3" t="inlineStr">
@@ -70678,7 +70678,7 @@
     <row r="546">
       <c r="A546" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B546" s="3" t="inlineStr">
@@ -70710,7 +70710,7 @@
     <row r="547">
       <c r="A547" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B547" s="3" t="inlineStr">
@@ -70742,7 +70742,7 @@
     <row r="548">
       <c r="A548" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B548" s="3" t="inlineStr">
@@ -70774,7 +70774,7 @@
     <row r="549">
       <c r="A549" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B549" s="3" t="inlineStr">
@@ -70806,7 +70806,7 @@
     <row r="550">
       <c r="A550" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B550" s="3" t="inlineStr">
@@ -70838,7 +70838,7 @@
     <row r="551">
       <c r="A551" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B551" s="3" t="inlineStr">
@@ -70870,7 +70870,7 @@
     <row r="552">
       <c r="A552" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B552" s="3" t="inlineStr">
@@ -70902,7 +70902,7 @@
     <row r="553">
       <c r="A553" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B553" s="3" t="inlineStr">
@@ -70934,7 +70934,7 @@
     <row r="554">
       <c r="A554" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B554" s="3" t="inlineStr">
@@ -70966,7 +70966,7 @@
     <row r="555">
       <c r="A555" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B555" s="3" t="inlineStr">
@@ -70998,7 +70998,7 @@
     <row r="556">
       <c r="A556" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B556" s="3" t="inlineStr">
@@ -71030,7 +71030,7 @@
     <row r="557">
       <c r="A557" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B557" s="3" t="inlineStr">
@@ -71062,7 +71062,7 @@
     <row r="558">
       <c r="A558" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B558" s="3" t="inlineStr">
@@ -71094,7 +71094,7 @@
     <row r="559">
       <c r="A559" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B559" s="3" t="inlineStr">
@@ -71126,7 +71126,7 @@
     <row r="560">
       <c r="A560" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B560" s="3" t="inlineStr">
@@ -71158,7 +71158,7 @@
     <row r="561">
       <c r="A561" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B561" s="3" t="inlineStr">
@@ -71190,7 +71190,7 @@
     <row r="562">
       <c r="A562" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B562" s="3" t="inlineStr">
@@ -71222,7 +71222,7 @@
     <row r="563">
       <c r="A563" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B563" s="3" t="inlineStr">
@@ -71254,7 +71254,7 @@
     <row r="564">
       <c r="A564" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B564" s="3" t="inlineStr">
@@ -71286,7 +71286,7 @@
     <row r="565">
       <c r="A565" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B565" s="3" t="inlineStr">
@@ -71318,7 +71318,7 @@
     <row r="566">
       <c r="A566" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B566" s="3" t="inlineStr">
@@ -71350,7 +71350,7 @@
     <row r="567">
       <c r="A567" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B567" s="3" t="inlineStr">
@@ -71382,7 +71382,7 @@
     <row r="568">
       <c r="A568" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B568" s="3" t="inlineStr">
@@ -71414,7 +71414,7 @@
     <row r="569">
       <c r="A569" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B569" s="3" t="inlineStr">
@@ -71446,7 +71446,7 @@
     <row r="570">
       <c r="A570" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B570" s="3" t="inlineStr">
@@ -71478,7 +71478,7 @@
     <row r="571">
       <c r="A571" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B571" s="3" t="inlineStr">
@@ -71510,7 +71510,7 @@
     <row r="572">
       <c r="A572" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B572" s="3" t="inlineStr">
@@ -71542,7 +71542,7 @@
     <row r="573">
       <c r="A573" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B573" s="3" t="inlineStr">
@@ -71574,7 +71574,7 @@
     <row r="574">
       <c r="A574" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B574" s="3" t="inlineStr">
@@ -71606,7 +71606,7 @@
     <row r="575">
       <c r="A575" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B575" s="3" t="inlineStr">
@@ -71638,7 +71638,7 @@
     <row r="576">
       <c r="A576" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B576" s="3" t="inlineStr">
@@ -71670,7 +71670,7 @@
     <row r="577">
       <c r="A577" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B577" s="3" t="inlineStr">
@@ -71702,7 +71702,7 @@
     <row r="578">
       <c r="A578" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B578" s="3" t="inlineStr">
@@ -71734,7 +71734,7 @@
     <row r="579">
       <c r="A579" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B579" s="3" t="inlineStr">
@@ -71766,7 +71766,7 @@
     <row r="580">
       <c r="A580" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B580" s="3" t="inlineStr">
@@ -71798,7 +71798,7 @@
     <row r="581">
       <c r="A581" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B581" s="3" t="inlineStr">
@@ -71830,7 +71830,7 @@
     <row r="582">
       <c r="A582" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B582" s="3" t="inlineStr">
@@ -71862,7 +71862,7 @@
     <row r="583">
       <c r="A583" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B583" s="3" t="inlineStr">
@@ -71894,7 +71894,7 @@
     <row r="584">
       <c r="A584" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B584" s="3" t="inlineStr">
@@ -71926,7 +71926,7 @@
     <row r="585">
       <c r="A585" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B585" s="3" t="inlineStr">
@@ -71958,7 +71958,7 @@
     <row r="586">
       <c r="A586" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B586" s="3" t="inlineStr">
@@ -71990,7 +71990,7 @@
     <row r="587">
       <c r="A587" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B587" s="3" t="inlineStr">
@@ -72022,7 +72022,7 @@
     <row r="588">
       <c r="A588" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B588" s="3" t="inlineStr">
@@ -72054,7 +72054,7 @@
     <row r="589">
       <c r="A589" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B589" s="3" t="inlineStr">
@@ -72086,7 +72086,7 @@
     <row r="590">
       <c r="A590" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B590" s="3" t="inlineStr">
@@ -72118,7 +72118,7 @@
     <row r="591">
       <c r="A591" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B591" s="3" t="inlineStr">
@@ -72150,7 +72150,7 @@
     <row r="592">
       <c r="A592" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B592" s="3" t="inlineStr">
@@ -72182,7 +72182,7 @@
     <row r="593">
       <c r="A593" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B593" s="3" t="inlineStr">
@@ -72214,7 +72214,7 @@
     <row r="594">
       <c r="A594" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B594" s="3" t="inlineStr">
@@ -72246,7 +72246,7 @@
     <row r="595">
       <c r="A595" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B595" s="3" t="inlineStr">
@@ -72278,7 +72278,7 @@
     <row r="596">
       <c r="A596" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B596" s="3" t="inlineStr">
@@ -72310,7 +72310,7 @@
     <row r="597">
       <c r="A597" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B597" s="3" t="inlineStr">
@@ -72342,7 +72342,7 @@
     <row r="598">
       <c r="A598" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B598" s="3" t="inlineStr">
@@ -72374,7 +72374,7 @@
     <row r="599">
       <c r="A599" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B599" s="3" t="inlineStr">
@@ -72406,7 +72406,7 @@
     <row r="600">
       <c r="A600" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B600" s="3" t="inlineStr">
@@ -72438,7 +72438,7 @@
     <row r="601">
       <c r="A601" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B601" s="3" t="inlineStr">
@@ -72470,7 +72470,7 @@
     <row r="602">
       <c r="A602" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B602" s="3" t="inlineStr">
@@ -72502,7 +72502,7 @@
     <row r="603">
       <c r="A603" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B603" s="3" t="inlineStr">
@@ -72534,7 +72534,7 @@
     <row r="604">
       <c r="A604" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B604" s="3" t="inlineStr">
@@ -72566,7 +72566,7 @@
     <row r="605">
       <c r="A605" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B605" s="3" t="inlineStr">
@@ -72598,7 +72598,7 @@
     <row r="606">
       <c r="A606" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B606" s="3" t="inlineStr">
@@ -72630,7 +72630,7 @@
     <row r="607">
       <c r="A607" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B607" s="3" t="inlineStr">
@@ -72662,7 +72662,7 @@
     <row r="608">
       <c r="A608" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B608" s="3" t="inlineStr">
@@ -72694,7 +72694,7 @@
     <row r="609">
       <c r="A609" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B609" s="3" t="inlineStr">
@@ -72726,7 +72726,7 @@
     <row r="610">
       <c r="A610" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B610" s="3" t="inlineStr">
@@ -72758,7 +72758,7 @@
     <row r="611">
       <c r="A611" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B611" s="3" t="inlineStr">
@@ -72790,7 +72790,7 @@
     <row r="612">
       <c r="A612" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B612" s="3" t="inlineStr">
@@ -72822,7 +72822,7 @@
     <row r="613">
       <c r="A613" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B613" s="3" t="inlineStr">
@@ -72854,7 +72854,7 @@
     <row r="614">
       <c r="A614" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B614" s="3" t="inlineStr">
@@ -72886,7 +72886,7 @@
     <row r="615">
       <c r="A615" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B615" s="3" t="inlineStr">
@@ -72918,7 +72918,7 @@
     <row r="616">
       <c r="A616" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B616" s="3" t="inlineStr">
@@ -72950,7 +72950,7 @@
     <row r="617">
       <c r="A617" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B617" s="3" t="inlineStr">
@@ -72982,7 +72982,7 @@
     <row r="618">
       <c r="A618" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B618" s="3" t="inlineStr">
@@ -73014,7 +73014,7 @@
     <row r="619">
       <c r="A619" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B619" s="3" t="inlineStr">
@@ -73046,7 +73046,7 @@
     <row r="620">
       <c r="A620" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B620" s="3" t="inlineStr">
@@ -73078,7 +73078,7 @@
     <row r="621">
       <c r="A621" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B621" s="3" t="inlineStr">
@@ -73110,7 +73110,7 @@
     <row r="622">
       <c r="A622" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B622" s="3" t="inlineStr">
@@ -73142,7 +73142,7 @@
     <row r="623">
       <c r="A623" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B623" s="3" t="inlineStr">
@@ -73174,7 +73174,7 @@
     <row r="624">
       <c r="A624" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B624" s="3" t="inlineStr">
@@ -73206,7 +73206,7 @@
     <row r="625">
       <c r="A625" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B625" s="3" t="inlineStr">
@@ -73238,7 +73238,7 @@
     <row r="626">
       <c r="A626" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B626" s="3" t="inlineStr">
@@ -73270,7 +73270,7 @@
     <row r="627">
       <c r="A627" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B627" s="3" t="inlineStr">
@@ -73302,7 +73302,7 @@
     <row r="628">
       <c r="A628" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B628" s="3" t="inlineStr">
@@ -73334,7 +73334,7 @@
     <row r="629">
       <c r="A629" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B629" s="3" t="inlineStr">
@@ -73366,7 +73366,7 @@
     <row r="630">
       <c r="A630" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B630" s="3" t="inlineStr">
@@ -73398,7 +73398,7 @@
     <row r="631">
       <c r="A631" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B631" s="3" t="inlineStr">
@@ -73430,7 +73430,7 @@
     <row r="632">
       <c r="A632" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B632" s="3" t="inlineStr">
@@ -73462,7 +73462,7 @@
     <row r="633">
       <c r="A633" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B633" s="3" t="inlineStr">
@@ -73494,7 +73494,7 @@
     <row r="634">
       <c r="A634" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B634" s="3" t="inlineStr">
@@ -73526,7 +73526,7 @@
     <row r="635">
       <c r="A635" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B635" s="3" t="inlineStr">
@@ -73558,7 +73558,7 @@
     <row r="636">
       <c r="A636" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B636" s="3" t="inlineStr">
@@ -73590,7 +73590,7 @@
     <row r="637">
       <c r="A637" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B637" s="3" t="inlineStr">
@@ -73622,7 +73622,7 @@
     <row r="638">
       <c r="A638" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B638" s="3" t="inlineStr">
@@ -73654,7 +73654,7 @@
     <row r="639">
       <c r="A639" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B639" s="3" t="inlineStr">
@@ -73686,7 +73686,7 @@
     <row r="640">
       <c r="A640" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B640" s="3" t="inlineStr">
@@ -73718,7 +73718,7 @@
     <row r="641">
       <c r="A641" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B641" s="3" t="inlineStr">
@@ -73750,7 +73750,7 @@
     <row r="642">
       <c r="A642" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B642" s="3" t="inlineStr">
@@ -73782,7 +73782,7 @@
     <row r="643">
       <c r="A643" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B643" s="3" t="inlineStr">
@@ -73814,7 +73814,7 @@
     <row r="644">
       <c r="A644" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B644" s="3" t="inlineStr">
@@ -73846,7 +73846,7 @@
     <row r="645">
       <c r="A645" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B645" s="3" t="inlineStr">
@@ -73878,7 +73878,7 @@
     <row r="646">
       <c r="A646" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B646" s="3" t="inlineStr">
@@ -73910,7 +73910,7 @@
     <row r="647">
       <c r="A647" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B647" s="3" t="inlineStr">
@@ -73942,7 +73942,7 @@
     <row r="648">
       <c r="A648" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B648" s="3" t="inlineStr">
@@ -73974,7 +73974,7 @@
     <row r="649">
       <c r="A649" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B649" s="3" t="inlineStr">
@@ -74006,7 +74006,7 @@
     <row r="650">
       <c r="A650" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B650" s="3" t="inlineStr">
@@ -74038,7 +74038,7 @@
     <row r="651">
       <c r="A651" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B651" s="3" t="inlineStr">
@@ -74070,7 +74070,7 @@
     <row r="652">
       <c r="A652" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:38:00</t>
+          <t>2026-10-08 20:50:22</t>
         </is>
       </c>
       <c r="B652" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22 UTC</t>
+          <t>2026-10-09 01:01:45 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -53270,7 +53270,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -53302,7 +53302,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -53334,7 +53334,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -53366,7 +53366,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -53398,7 +53398,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -53430,7 +53430,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -53462,7 +53462,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -53494,7 +53494,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -53526,7 +53526,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -53558,7 +53558,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -53590,7 +53590,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -53622,7 +53622,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -53654,7 +53654,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -53686,7 +53686,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -53718,7 +53718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -53750,7 +53750,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -53782,7 +53782,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -53814,7 +53814,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -53846,7 +53846,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -53878,7 +53878,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -53910,7 +53910,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -53942,7 +53942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -53974,7 +53974,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -54006,7 +54006,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -54038,7 +54038,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -54070,7 +54070,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -54102,7 +54102,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -54134,7 +54134,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -54166,7 +54166,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -54198,7 +54198,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -54230,7 +54230,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -54262,7 +54262,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -54294,7 +54294,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -54326,7 +54326,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -54358,7 +54358,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -54390,7 +54390,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -54422,7 +54422,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -54454,7 +54454,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -54486,7 +54486,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -54518,7 +54518,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -54550,7 +54550,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -54582,7 +54582,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -54614,7 +54614,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -54646,7 +54646,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -54678,7 +54678,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -54710,7 +54710,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -54742,7 +54742,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -54774,7 +54774,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -54806,7 +54806,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -54838,7 +54838,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -54870,7 +54870,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -54902,7 +54902,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -54934,7 +54934,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -54966,7 +54966,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -54998,7 +54998,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -55030,7 +55030,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -55062,7 +55062,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -55094,7 +55094,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -55126,7 +55126,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -55158,7 +55158,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -55190,7 +55190,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -55222,7 +55222,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -55254,7 +55254,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -55286,7 +55286,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -55318,7 +55318,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -55350,7 +55350,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -55382,7 +55382,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -55414,7 +55414,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -55446,7 +55446,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -55478,7 +55478,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -55510,7 +55510,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -55542,7 +55542,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -55574,7 +55574,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -55606,7 +55606,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -55638,7 +55638,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -55670,7 +55670,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -55702,7 +55702,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -55734,7 +55734,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -55766,7 +55766,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -55798,7 +55798,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -55830,7 +55830,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -55862,7 +55862,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -55894,7 +55894,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -55926,7 +55926,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -55958,7 +55958,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -55990,7 +55990,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -56022,7 +56022,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -56054,7 +56054,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -56086,7 +56086,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -56118,7 +56118,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -56150,7 +56150,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -56182,7 +56182,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -56214,7 +56214,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -56246,7 +56246,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -56278,7 +56278,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -56310,7 +56310,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -56342,7 +56342,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -56374,7 +56374,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -56406,7 +56406,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -56438,7 +56438,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -56470,7 +56470,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -56502,7 +56502,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -56534,7 +56534,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -56566,7 +56566,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -56598,7 +56598,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -56630,7 +56630,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -56662,7 +56662,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -56694,7 +56694,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -56726,7 +56726,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -56758,7 +56758,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -56790,7 +56790,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -56822,7 +56822,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -56854,7 +56854,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -56886,7 +56886,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -56918,7 +56918,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -56950,7 +56950,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -56982,7 +56982,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -57014,7 +57014,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -57046,7 +57046,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -57078,7 +57078,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -57110,7 +57110,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -57142,7 +57142,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -57174,7 +57174,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -57206,7 +57206,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -57238,7 +57238,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -57270,7 +57270,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -57302,7 +57302,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -57334,7 +57334,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -57366,7 +57366,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -57398,7 +57398,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -57430,7 +57430,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -57462,7 +57462,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -57494,7 +57494,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -57526,7 +57526,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -57558,7 +57558,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -57590,7 +57590,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -57622,7 +57622,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -57654,7 +57654,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -57686,7 +57686,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -57718,7 +57718,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -57750,7 +57750,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -57782,7 +57782,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -57814,7 +57814,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -57846,7 +57846,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -57878,7 +57878,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -57910,7 +57910,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -57942,7 +57942,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -57974,7 +57974,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -58006,7 +58006,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -58038,7 +58038,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -58070,7 +58070,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -58102,7 +58102,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -58134,7 +58134,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -58166,7 +58166,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -58198,7 +58198,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -58230,7 +58230,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -58262,7 +58262,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -58294,7 +58294,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -58326,7 +58326,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -58358,7 +58358,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -58390,7 +58390,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -58422,7 +58422,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -58454,7 +58454,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -58486,7 +58486,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -58518,7 +58518,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -58550,7 +58550,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -58582,7 +58582,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -58614,7 +58614,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -58646,7 +58646,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -58678,7 +58678,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -58710,7 +58710,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -58742,7 +58742,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -58774,7 +58774,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -58806,7 +58806,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -58838,7 +58838,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -58870,7 +58870,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -58902,7 +58902,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -58934,7 +58934,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -58966,7 +58966,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -58998,7 +58998,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -59030,7 +59030,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -59062,7 +59062,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -59094,7 +59094,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -59126,7 +59126,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -59158,7 +59158,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -59190,7 +59190,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -59222,7 +59222,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -59254,7 +59254,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -59286,7 +59286,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -59318,7 +59318,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -59350,7 +59350,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -59382,7 +59382,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -59414,7 +59414,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -59446,7 +59446,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -59478,7 +59478,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -59510,7 +59510,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -59542,7 +59542,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -59574,7 +59574,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -59606,7 +59606,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -59638,7 +59638,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -59670,7 +59670,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -59702,7 +59702,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -59734,7 +59734,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -59766,7 +59766,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -59798,7 +59798,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -59830,7 +59830,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -59862,7 +59862,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -59894,7 +59894,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -59926,7 +59926,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -59958,7 +59958,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -59990,7 +59990,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -60022,7 +60022,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -60054,7 +60054,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -60086,7 +60086,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -60118,7 +60118,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -60150,7 +60150,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -60182,7 +60182,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -60214,7 +60214,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -60246,7 +60246,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -60278,7 +60278,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -60310,7 +60310,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -60342,7 +60342,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -60374,7 +60374,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -60406,7 +60406,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -60438,7 +60438,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -60470,7 +60470,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -60502,7 +60502,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -60534,7 +60534,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -60566,7 +60566,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -60598,7 +60598,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -60630,7 +60630,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -60662,7 +60662,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -60694,7 +60694,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -60726,7 +60726,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -60758,7 +60758,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -60790,7 +60790,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -60822,7 +60822,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -60854,7 +60854,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -60886,7 +60886,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -60918,7 +60918,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -60950,7 +60950,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -60982,7 +60982,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -61014,7 +61014,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -61046,7 +61046,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -61078,7 +61078,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -61110,7 +61110,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -61142,7 +61142,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -61174,7 +61174,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -61206,7 +61206,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -61238,7 +61238,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -61270,7 +61270,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -61302,7 +61302,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -61334,7 +61334,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -61366,7 +61366,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -61398,7 +61398,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -61430,7 +61430,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -61462,7 +61462,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -61494,7 +61494,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -61526,7 +61526,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -61558,7 +61558,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -61590,7 +61590,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -61622,7 +61622,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -61654,7 +61654,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -61686,7 +61686,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -61718,7 +61718,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -61750,7 +61750,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -61782,7 +61782,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -61814,7 +61814,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -61846,7 +61846,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -61878,7 +61878,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -61910,7 +61910,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -61942,7 +61942,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -61974,7 +61974,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -62006,7 +62006,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -62038,7 +62038,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -62070,7 +62070,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -62102,7 +62102,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -62134,7 +62134,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -62166,7 +62166,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -62198,7 +62198,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -62230,7 +62230,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -62262,7 +62262,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -62294,7 +62294,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -62326,7 +62326,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -62358,7 +62358,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -62390,7 +62390,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -62422,7 +62422,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -62454,7 +62454,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -62486,7 +62486,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -62518,7 +62518,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -62550,7 +62550,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -62582,7 +62582,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -62614,7 +62614,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -62646,7 +62646,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -62678,7 +62678,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -62710,7 +62710,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -62742,7 +62742,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -62774,7 +62774,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -62806,7 +62806,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -62838,7 +62838,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
@@ -62870,7 +62870,7 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
@@ -62902,7 +62902,7 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
@@ -62934,7 +62934,7 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -62966,7 +62966,7 @@
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
@@ -62998,7 +62998,7 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -63030,7 +63030,7 @@
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
@@ -63062,7 +63062,7 @@
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
@@ -63094,7 +63094,7 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
@@ -63126,7 +63126,7 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
@@ -63158,7 +63158,7 @@
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
@@ -63190,7 +63190,7 @@
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -63222,7 +63222,7 @@
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B313" s="3" t="inlineStr">
@@ -63254,7 +63254,7 @@
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
@@ -63286,7 +63286,7 @@
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
@@ -63318,7 +63318,7 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
@@ -63350,7 +63350,7 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B317" s="3" t="inlineStr">
@@ -63382,7 +63382,7 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
@@ -63414,7 +63414,7 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
@@ -63446,7 +63446,7 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
@@ -63478,7 +63478,7 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
@@ -63510,7 +63510,7 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
@@ -63542,7 +63542,7 @@
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B323" s="3" t="inlineStr">
@@ -63574,7 +63574,7 @@
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
@@ -63606,7 +63606,7 @@
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B325" s="3" t="inlineStr">
@@ -63638,7 +63638,7 @@
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
@@ -63670,7 +63670,7 @@
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B327" s="3" t="inlineStr">
@@ -63702,7 +63702,7 @@
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
@@ -63734,7 +63734,7 @@
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B329" s="3" t="inlineStr">
@@ -63766,7 +63766,7 @@
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
@@ -63798,7 +63798,7 @@
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B331" s="3" t="inlineStr">
@@ -63830,7 +63830,7 @@
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
@@ -63862,7 +63862,7 @@
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B333" s="3" t="inlineStr">
@@ -63894,7 +63894,7 @@
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
@@ -63926,7 +63926,7 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B335" s="3" t="inlineStr">
@@ -63958,7 +63958,7 @@
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
@@ -63990,7 +63990,7 @@
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B337" s="3" t="inlineStr">
@@ -64022,7 +64022,7 @@
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
@@ -64054,7 +64054,7 @@
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B339" s="3" t="inlineStr">
@@ -64086,7 +64086,7 @@
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
@@ -64118,7 +64118,7 @@
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B341" s="3" t="inlineStr">
@@ -64150,7 +64150,7 @@
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
@@ -64182,7 +64182,7 @@
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B343" s="3" t="inlineStr">
@@ -64214,7 +64214,7 @@
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
@@ -64246,7 +64246,7 @@
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B345" s="3" t="inlineStr">
@@ -64278,7 +64278,7 @@
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
@@ -64310,7 +64310,7 @@
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B347" s="3" t="inlineStr">
@@ -64342,7 +64342,7 @@
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
@@ -64374,7 +64374,7 @@
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B349" s="3" t="inlineStr">
@@ -64406,7 +64406,7 @@
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
@@ -64438,7 +64438,7 @@
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B351" s="3" t="inlineStr">
@@ -64470,7 +64470,7 @@
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
@@ -64502,7 +64502,7 @@
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B353" s="3" t="inlineStr">
@@ -64534,7 +64534,7 @@
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
@@ -64566,7 +64566,7 @@
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B355" s="3" t="inlineStr">
@@ -64598,7 +64598,7 @@
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
@@ -64630,7 +64630,7 @@
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B357" s="3" t="inlineStr">
@@ -64662,7 +64662,7 @@
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
@@ -64694,7 +64694,7 @@
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B359" s="3" t="inlineStr">
@@ -64726,7 +64726,7 @@
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
@@ -64758,7 +64758,7 @@
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B361" s="3" t="inlineStr">
@@ -64790,7 +64790,7 @@
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
@@ -64822,7 +64822,7 @@
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B363" s="3" t="inlineStr">
@@ -64854,7 +64854,7 @@
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
@@ -64886,7 +64886,7 @@
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B365" s="3" t="inlineStr">
@@ -64918,7 +64918,7 @@
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
@@ -64950,7 +64950,7 @@
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B367" s="3" t="inlineStr">
@@ -64982,7 +64982,7 @@
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
@@ -65014,7 +65014,7 @@
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B369" s="3" t="inlineStr">
@@ -65046,7 +65046,7 @@
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
@@ -65078,7 +65078,7 @@
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B371" s="3" t="inlineStr">
@@ -65110,7 +65110,7 @@
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
@@ -65142,7 +65142,7 @@
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B373" s="3" t="inlineStr">
@@ -65174,7 +65174,7 @@
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
@@ -65206,7 +65206,7 @@
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B375" s="3" t="inlineStr">
@@ -65238,7 +65238,7 @@
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
@@ -65270,7 +65270,7 @@
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B377" s="3" t="inlineStr">
@@ -65302,7 +65302,7 @@
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
@@ -65334,7 +65334,7 @@
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B379" s="3" t="inlineStr">
@@ -65366,7 +65366,7 @@
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
@@ -65398,7 +65398,7 @@
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B381" s="3" t="inlineStr">
@@ -65430,7 +65430,7 @@
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
@@ -65462,7 +65462,7 @@
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B383" s="3" t="inlineStr">
@@ -65494,7 +65494,7 @@
     <row r="384">
       <c r="A384" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
@@ -65526,7 +65526,7 @@
     <row r="385">
       <c r="A385" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B385" s="3" t="inlineStr">
@@ -65558,7 +65558,7 @@
     <row r="386">
       <c r="A386" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
@@ -65590,7 +65590,7 @@
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B387" s="3" t="inlineStr">
@@ -65622,7 +65622,7 @@
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
@@ -65654,7 +65654,7 @@
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B389" s="3" t="inlineStr">
@@ -65686,7 +65686,7 @@
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
@@ -65718,7 +65718,7 @@
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B391" s="3" t="inlineStr">
@@ -65750,7 +65750,7 @@
     <row r="392">
       <c r="A392" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
@@ -65782,7 +65782,7 @@
     <row r="393">
       <c r="A393" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B393" s="3" t="inlineStr">
@@ -65814,7 +65814,7 @@
     <row r="394">
       <c r="A394" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
@@ -65846,7 +65846,7 @@
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B395" s="3" t="inlineStr">
@@ -65878,7 +65878,7 @@
     <row r="396">
       <c r="A396" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
@@ -65910,7 +65910,7 @@
     <row r="397">
       <c r="A397" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B397" s="3" t="inlineStr">
@@ -65942,7 +65942,7 @@
     <row r="398">
       <c r="A398" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
@@ -65974,7 +65974,7 @@
     <row r="399">
       <c r="A399" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B399" s="3" t="inlineStr">
@@ -66006,7 +66006,7 @@
     <row r="400">
       <c r="A400" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
@@ -66038,7 +66038,7 @@
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B401" s="3" t="inlineStr">
@@ -66070,7 +66070,7 @@
     <row r="402">
       <c r="A402" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
@@ -66102,7 +66102,7 @@
     <row r="403">
       <c r="A403" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B403" s="3" t="inlineStr">
@@ -66134,7 +66134,7 @@
     <row r="404">
       <c r="A404" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
@@ -66166,7 +66166,7 @@
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B405" s="3" t="inlineStr">
@@ -66198,7 +66198,7 @@
     <row r="406">
       <c r="A406" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
@@ -66230,7 +66230,7 @@
     <row r="407">
       <c r="A407" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B407" s="3" t="inlineStr">
@@ -66262,7 +66262,7 @@
     <row r="408">
       <c r="A408" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
@@ -66294,7 +66294,7 @@
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B409" s="3" t="inlineStr">
@@ -66326,7 +66326,7 @@
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
@@ -66358,7 +66358,7 @@
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B411" s="3" t="inlineStr">
@@ -66390,7 +66390,7 @@
     <row r="412">
       <c r="A412" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
@@ -66422,7 +66422,7 @@
     <row r="413">
       <c r="A413" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B413" s="3" t="inlineStr">
@@ -66454,7 +66454,7 @@
     <row r="414">
       <c r="A414" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
@@ -66486,7 +66486,7 @@
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B415" s="3" t="inlineStr">
@@ -66518,7 +66518,7 @@
     <row r="416">
       <c r="A416" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B416" s="3" t="inlineStr">
@@ -66550,7 +66550,7 @@
     <row r="417">
       <c r="A417" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B417" s="3" t="inlineStr">
@@ -66582,7 +66582,7 @@
     <row r="418">
       <c r="A418" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -66614,7 +66614,7 @@
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B419" s="3" t="inlineStr">
@@ -66646,7 +66646,7 @@
     <row r="420">
       <c r="A420" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
@@ -66678,7 +66678,7 @@
     <row r="421">
       <c r="A421" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B421" s="3" t="inlineStr">
@@ -66710,7 +66710,7 @@
     <row r="422">
       <c r="A422" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B422" s="3" t="inlineStr">
@@ -66742,7 +66742,7 @@
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B423" s="3" t="inlineStr">
@@ -66774,7 +66774,7 @@
     <row r="424">
       <c r="A424" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
@@ -66806,7 +66806,7 @@
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B425" s="3" t="inlineStr">
@@ -66838,7 +66838,7 @@
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
@@ -66870,7 +66870,7 @@
     <row r="427">
       <c r="A427" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B427" s="3" t="inlineStr">
@@ -66902,7 +66902,7 @@
     <row r="428">
       <c r="A428" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
@@ -66934,7 +66934,7 @@
     <row r="429">
       <c r="A429" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B429" s="3" t="inlineStr">
@@ -66966,7 +66966,7 @@
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
@@ -66998,7 +66998,7 @@
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B431" s="3" t="inlineStr">
@@ -67030,7 +67030,7 @@
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
@@ -67062,7 +67062,7 @@
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B433" s="3" t="inlineStr">
@@ -67094,7 +67094,7 @@
     <row r="434">
       <c r="A434" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
@@ -67126,7 +67126,7 @@
     <row r="435">
       <c r="A435" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B435" s="3" t="inlineStr">
@@ -67158,7 +67158,7 @@
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
@@ -67190,7 +67190,7 @@
     <row r="437">
       <c r="A437" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B437" s="3" t="inlineStr">
@@ -67222,7 +67222,7 @@
     <row r="438">
       <c r="A438" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
@@ -67254,7 +67254,7 @@
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B439" s="3" t="inlineStr">
@@ -67286,7 +67286,7 @@
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -67318,7 +67318,7 @@
     <row r="441">
       <c r="A441" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B441" s="3" t="inlineStr">
@@ -67350,7 +67350,7 @@
     <row r="442">
       <c r="A442" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -67382,7 +67382,7 @@
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B443" s="3" t="inlineStr">
@@ -67414,7 +67414,7 @@
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
@@ -67446,7 +67446,7 @@
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B445" s="3" t="inlineStr">
@@ -67478,7 +67478,7 @@
     <row r="446">
       <c r="A446" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
@@ -67510,7 +67510,7 @@
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B447" s="3" t="inlineStr">
@@ -67542,7 +67542,7 @@
     <row r="448">
       <c r="A448" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
@@ -67574,7 +67574,7 @@
     <row r="449">
       <c r="A449" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B449" s="3" t="inlineStr">
@@ -67606,7 +67606,7 @@
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
@@ -67638,7 +67638,7 @@
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B451" s="3" t="inlineStr">
@@ -67670,7 +67670,7 @@
     <row r="452">
       <c r="A452" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
@@ -67702,7 +67702,7 @@
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B453" s="3" t="inlineStr">
@@ -67734,7 +67734,7 @@
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
@@ -67766,7 +67766,7 @@
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B455" s="3" t="inlineStr">
@@ -67798,7 +67798,7 @@
     <row r="456">
       <c r="A456" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
@@ -67830,7 +67830,7 @@
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B457" s="3" t="inlineStr">
@@ -67862,7 +67862,7 @@
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
@@ -67894,7 +67894,7 @@
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B459" s="3" t="inlineStr">
@@ -67926,7 +67926,7 @@
     <row r="460">
       <c r="A460" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
@@ -67958,7 +67958,7 @@
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B461" s="3" t="inlineStr">
@@ -67990,7 +67990,7 @@
     <row r="462">
       <c r="A462" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
@@ -68022,7 +68022,7 @@
     <row r="463">
       <c r="A463" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B463" s="3" t="inlineStr">
@@ -68054,7 +68054,7 @@
     <row r="464">
       <c r="A464" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B464" s="3" t="inlineStr">
@@ -68086,7 +68086,7 @@
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B465" s="3" t="inlineStr">
@@ -68118,7 +68118,7 @@
     <row r="466">
       <c r="A466" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
@@ -68150,7 +68150,7 @@
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B467" s="3" t="inlineStr">
@@ -68182,7 +68182,7 @@
     <row r="468">
       <c r="A468" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
@@ -68214,7 +68214,7 @@
     <row r="469">
       <c r="A469" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B469" s="3" t="inlineStr">
@@ -68246,7 +68246,7 @@
     <row r="470">
       <c r="A470" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
@@ -68278,7 +68278,7 @@
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B471" s="3" t="inlineStr">
@@ -68310,7 +68310,7 @@
     <row r="472">
       <c r="A472" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B472" s="3" t="inlineStr">
@@ -68342,7 +68342,7 @@
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B473" s="3" t="inlineStr">
@@ -68374,7 +68374,7 @@
     <row r="474">
       <c r="A474" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B474" s="3" t="inlineStr">
@@ -68406,7 +68406,7 @@
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B475" s="3" t="inlineStr">
@@ -68438,7 +68438,7 @@
     <row r="476">
       <c r="A476" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B476" s="3" t="inlineStr">
@@ -68470,7 +68470,7 @@
     <row r="477">
       <c r="A477" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B477" s="3" t="inlineStr">
@@ -68502,7 +68502,7 @@
     <row r="478">
       <c r="A478" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B478" s="3" t="inlineStr">
@@ -68534,7 +68534,7 @@
     <row r="479">
       <c r="A479" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B479" s="3" t="inlineStr">
@@ -68566,7 +68566,7 @@
     <row r="480">
       <c r="A480" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B480" s="3" t="inlineStr">
@@ -68598,7 +68598,7 @@
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B481" s="3" t="inlineStr">
@@ -68630,7 +68630,7 @@
     <row r="482">
       <c r="A482" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B482" s="3" t="inlineStr">
@@ -68662,7 +68662,7 @@
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B483" s="3" t="inlineStr">
@@ -68694,7 +68694,7 @@
     <row r="484">
       <c r="A484" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
@@ -68726,7 +68726,7 @@
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B485" s="3" t="inlineStr">
@@ -68758,7 +68758,7 @@
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B486" s="3" t="inlineStr">
@@ -68790,7 +68790,7 @@
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B487" s="3" t="inlineStr">
@@ -68822,7 +68822,7 @@
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B488" s="3" t="inlineStr">
@@ -68854,7 +68854,7 @@
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B489" s="3" t="inlineStr">
@@ -68886,7 +68886,7 @@
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B490" s="3" t="inlineStr">
@@ -68918,7 +68918,7 @@
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B491" s="3" t="inlineStr">
@@ -68950,7 +68950,7 @@
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B492" s="3" t="inlineStr">
@@ -68982,7 +68982,7 @@
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B493" s="3" t="inlineStr">
@@ -69014,7 +69014,7 @@
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B494" s="3" t="inlineStr">
@@ -69046,7 +69046,7 @@
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B495" s="3" t="inlineStr">
@@ -69078,7 +69078,7 @@
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B496" s="3" t="inlineStr">
@@ -69110,7 +69110,7 @@
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B497" s="3" t="inlineStr">
@@ -69142,7 +69142,7 @@
     <row r="498">
       <c r="A498" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B498" s="3" t="inlineStr">
@@ -69174,7 +69174,7 @@
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B499" s="3" t="inlineStr">
@@ -69206,7 +69206,7 @@
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B500" s="3" t="inlineStr">
@@ -69238,7 +69238,7 @@
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B501" s="3" t="inlineStr">
@@ -69270,7 +69270,7 @@
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B502" s="3" t="inlineStr">
@@ -69302,7 +69302,7 @@
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B503" s="3" t="inlineStr">
@@ -69334,7 +69334,7 @@
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B504" s="3" t="inlineStr">
@@ -69366,7 +69366,7 @@
     <row r="505">
       <c r="A505" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B505" s="3" t="inlineStr">
@@ -69398,7 +69398,7 @@
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B506" s="3" t="inlineStr">
@@ -69430,7 +69430,7 @@
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B507" s="3" t="inlineStr">
@@ -69462,7 +69462,7 @@
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B508" s="3" t="inlineStr">
@@ -69494,7 +69494,7 @@
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B509" s="3" t="inlineStr">
@@ -69526,7 +69526,7 @@
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B510" s="3" t="inlineStr">
@@ -69558,7 +69558,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B511" s="3" t="inlineStr">
@@ -69590,7 +69590,7 @@
     <row r="512">
       <c r="A512" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B512" s="3" t="inlineStr">
@@ -69622,7 +69622,7 @@
     <row r="513">
       <c r="A513" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B513" s="3" t="inlineStr">
@@ -69654,7 +69654,7 @@
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B514" s="3" t="inlineStr">
@@ -69686,7 +69686,7 @@
     <row r="515">
       <c r="A515" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B515" s="3" t="inlineStr">
@@ -69718,7 +69718,7 @@
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B516" s="3" t="inlineStr">
@@ -69750,7 +69750,7 @@
     <row r="517">
       <c r="A517" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B517" s="3" t="inlineStr">
@@ -69782,7 +69782,7 @@
     <row r="518">
       <c r="A518" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B518" s="3" t="inlineStr">
@@ -69814,7 +69814,7 @@
     <row r="519">
       <c r="A519" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B519" s="3" t="inlineStr">
@@ -69846,7 +69846,7 @@
     <row r="520">
       <c r="A520" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B520" s="3" t="inlineStr">
@@ -69878,7 +69878,7 @@
     <row r="521">
       <c r="A521" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B521" s="3" t="inlineStr">
@@ -69910,7 +69910,7 @@
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B522" s="3" t="inlineStr">
@@ -69942,7 +69942,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B523" s="3" t="inlineStr">
@@ -69974,7 +69974,7 @@
     <row r="524">
       <c r="A524" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B524" s="3" t="inlineStr">
@@ -70006,7 +70006,7 @@
     <row r="525">
       <c r="A525" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B525" s="3" t="inlineStr">
@@ -70038,7 +70038,7 @@
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B526" s="3" t="inlineStr">
@@ -70070,7 +70070,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B527" s="3" t="inlineStr">
@@ -70102,7 +70102,7 @@
     <row r="528">
       <c r="A528" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B528" s="3" t="inlineStr">
@@ -70134,7 +70134,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B529" s="3" t="inlineStr">
@@ -70166,7 +70166,7 @@
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B530" s="3" t="inlineStr">
@@ -70198,7 +70198,7 @@
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B531" s="3" t="inlineStr">
@@ -70230,7 +70230,7 @@
     <row r="532">
       <c r="A532" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B532" s="3" t="inlineStr">
@@ -70262,7 +70262,7 @@
     <row r="533">
       <c r="A533" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B533" s="3" t="inlineStr">
@@ -70294,7 +70294,7 @@
     <row r="534">
       <c r="A534" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B534" s="3" t="inlineStr">
@@ -70326,7 +70326,7 @@
     <row r="535">
       <c r="A535" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B535" s="3" t="inlineStr">
@@ -70358,7 +70358,7 @@
     <row r="536">
       <c r="A536" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B536" s="3" t="inlineStr">
@@ -70390,7 +70390,7 @@
     <row r="537">
       <c r="A537" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B537" s="3" t="inlineStr">
@@ -70422,7 +70422,7 @@
     <row r="538">
       <c r="A538" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B538" s="3" t="inlineStr">
@@ -70454,7 +70454,7 @@
     <row r="539">
       <c r="A539" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B539" s="3" t="inlineStr">
@@ -70486,7 +70486,7 @@
     <row r="540">
       <c r="A540" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B540" s="3" t="inlineStr">
@@ -70518,7 +70518,7 @@
     <row r="541">
       <c r="A541" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B541" s="3" t="inlineStr">
@@ -70550,7 +70550,7 @@
     <row r="542">
       <c r="A542" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B542" s="3" t="inlineStr">
@@ -70582,7 +70582,7 @@
     <row r="543">
       <c r="A543" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B543" s="3" t="inlineStr">
@@ -70614,7 +70614,7 @@
     <row r="544">
       <c r="A544" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B544" s="3" t="inlineStr">
@@ -70646,7 +70646,7 @@
     <row r="545">
       <c r="A545" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B545" s="3" t="inlineStr">
@@ -70678,7 +70678,7 @@
     <row r="546">
       <c r="A546" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B546" s="3" t="inlineStr">
@@ -70710,7 +70710,7 @@
     <row r="547">
       <c r="A547" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B547" s="3" t="inlineStr">
@@ -70742,7 +70742,7 @@
     <row r="548">
       <c r="A548" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B548" s="3" t="inlineStr">
@@ -70774,7 +70774,7 @@
     <row r="549">
       <c r="A549" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B549" s="3" t="inlineStr">
@@ -70806,7 +70806,7 @@
     <row r="550">
       <c r="A550" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B550" s="3" t="inlineStr">
@@ -70838,7 +70838,7 @@
     <row r="551">
       <c r="A551" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B551" s="3" t="inlineStr">
@@ -70870,7 +70870,7 @@
     <row r="552">
       <c r="A552" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B552" s="3" t="inlineStr">
@@ -70902,7 +70902,7 @@
     <row r="553">
       <c r="A553" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B553" s="3" t="inlineStr">
@@ -70934,7 +70934,7 @@
     <row r="554">
       <c r="A554" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B554" s="3" t="inlineStr">
@@ -70966,7 +70966,7 @@
     <row r="555">
       <c r="A555" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B555" s="3" t="inlineStr">
@@ -70998,7 +70998,7 @@
     <row r="556">
       <c r="A556" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B556" s="3" t="inlineStr">
@@ -71030,7 +71030,7 @@
     <row r="557">
       <c r="A557" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B557" s="3" t="inlineStr">
@@ -71062,7 +71062,7 @@
     <row r="558">
       <c r="A558" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B558" s="3" t="inlineStr">
@@ -71094,7 +71094,7 @@
     <row r="559">
       <c r="A559" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B559" s="3" t="inlineStr">
@@ -71126,7 +71126,7 @@
     <row r="560">
       <c r="A560" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B560" s="3" t="inlineStr">
@@ -71158,7 +71158,7 @@
     <row r="561">
       <c r="A561" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B561" s="3" t="inlineStr">
@@ -71190,7 +71190,7 @@
     <row r="562">
       <c r="A562" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B562" s="3" t="inlineStr">
@@ -71222,7 +71222,7 @@
     <row r="563">
       <c r="A563" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B563" s="3" t="inlineStr">
@@ -71254,7 +71254,7 @@
     <row r="564">
       <c r="A564" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B564" s="3" t="inlineStr">
@@ -71286,7 +71286,7 @@
     <row r="565">
       <c r="A565" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B565" s="3" t="inlineStr">
@@ -71318,7 +71318,7 @@
     <row r="566">
       <c r="A566" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B566" s="3" t="inlineStr">
@@ -71350,7 +71350,7 @@
     <row r="567">
       <c r="A567" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B567" s="3" t="inlineStr">
@@ -71382,7 +71382,7 @@
     <row r="568">
       <c r="A568" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B568" s="3" t="inlineStr">
@@ -71414,7 +71414,7 @@
     <row r="569">
       <c r="A569" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B569" s="3" t="inlineStr">
@@ -71446,7 +71446,7 @@
     <row r="570">
       <c r="A570" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B570" s="3" t="inlineStr">
@@ -71478,7 +71478,7 @@
     <row r="571">
       <c r="A571" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B571" s="3" t="inlineStr">
@@ -71510,7 +71510,7 @@
     <row r="572">
       <c r="A572" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B572" s="3" t="inlineStr">
@@ -71542,7 +71542,7 @@
     <row r="573">
       <c r="A573" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B573" s="3" t="inlineStr">
@@ -71574,7 +71574,7 @@
     <row r="574">
       <c r="A574" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B574" s="3" t="inlineStr">
@@ -71606,7 +71606,7 @@
     <row r="575">
       <c r="A575" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B575" s="3" t="inlineStr">
@@ -71638,7 +71638,7 @@
     <row r="576">
       <c r="A576" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B576" s="3" t="inlineStr">
@@ -71670,7 +71670,7 @@
     <row r="577">
       <c r="A577" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B577" s="3" t="inlineStr">
@@ -71702,7 +71702,7 @@
     <row r="578">
       <c r="A578" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B578" s="3" t="inlineStr">
@@ -71734,7 +71734,7 @@
     <row r="579">
       <c r="A579" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B579" s="3" t="inlineStr">
@@ -71766,7 +71766,7 @@
     <row r="580">
       <c r="A580" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B580" s="3" t="inlineStr">
@@ -71798,7 +71798,7 @@
     <row r="581">
       <c r="A581" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B581" s="3" t="inlineStr">
@@ -71830,7 +71830,7 @@
     <row r="582">
       <c r="A582" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B582" s="3" t="inlineStr">
@@ -71862,7 +71862,7 @@
     <row r="583">
       <c r="A583" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B583" s="3" t="inlineStr">
@@ -71894,7 +71894,7 @@
     <row r="584">
       <c r="A584" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B584" s="3" t="inlineStr">
@@ -71926,7 +71926,7 @@
     <row r="585">
       <c r="A585" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B585" s="3" t="inlineStr">
@@ -71958,7 +71958,7 @@
     <row r="586">
       <c r="A586" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B586" s="3" t="inlineStr">
@@ -71990,7 +71990,7 @@
     <row r="587">
       <c r="A587" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B587" s="3" t="inlineStr">
@@ -72022,7 +72022,7 @@
     <row r="588">
       <c r="A588" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B588" s="3" t="inlineStr">
@@ -72054,7 +72054,7 @@
     <row r="589">
       <c r="A589" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B589" s="3" t="inlineStr">
@@ -72086,7 +72086,7 @@
     <row r="590">
       <c r="A590" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B590" s="3" t="inlineStr">
@@ -72118,7 +72118,7 @@
     <row r="591">
       <c r="A591" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B591" s="3" t="inlineStr">
@@ -72150,7 +72150,7 @@
     <row r="592">
       <c r="A592" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B592" s="3" t="inlineStr">
@@ -72182,7 +72182,7 @@
     <row r="593">
       <c r="A593" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B593" s="3" t="inlineStr">
@@ -72214,7 +72214,7 @@
     <row r="594">
       <c r="A594" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B594" s="3" t="inlineStr">
@@ -72246,7 +72246,7 @@
     <row r="595">
       <c r="A595" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B595" s="3" t="inlineStr">
@@ -72278,7 +72278,7 @@
     <row r="596">
       <c r="A596" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B596" s="3" t="inlineStr">
@@ -72310,7 +72310,7 @@
     <row r="597">
       <c r="A597" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B597" s="3" t="inlineStr">
@@ -72342,7 +72342,7 @@
     <row r="598">
       <c r="A598" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B598" s="3" t="inlineStr">
@@ -72374,7 +72374,7 @@
     <row r="599">
       <c r="A599" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B599" s="3" t="inlineStr">
@@ -72406,7 +72406,7 @@
     <row r="600">
       <c r="A600" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B600" s="3" t="inlineStr">
@@ -72438,7 +72438,7 @@
     <row r="601">
       <c r="A601" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B601" s="3" t="inlineStr">
@@ -72470,7 +72470,7 @@
     <row r="602">
       <c r="A602" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B602" s="3" t="inlineStr">
@@ -72502,7 +72502,7 @@
     <row r="603">
       <c r="A603" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B603" s="3" t="inlineStr">
@@ -72534,7 +72534,7 @@
     <row r="604">
       <c r="A604" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B604" s="3" t="inlineStr">
@@ -72566,7 +72566,7 @@
     <row r="605">
       <c r="A605" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B605" s="3" t="inlineStr">
@@ -72598,7 +72598,7 @@
     <row r="606">
       <c r="A606" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B606" s="3" t="inlineStr">
@@ -72630,7 +72630,7 @@
     <row r="607">
       <c r="A607" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B607" s="3" t="inlineStr">
@@ -72662,7 +72662,7 @@
     <row r="608">
       <c r="A608" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B608" s="3" t="inlineStr">
@@ -72694,7 +72694,7 @@
     <row r="609">
       <c r="A609" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B609" s="3" t="inlineStr">
@@ -72726,7 +72726,7 @@
     <row r="610">
       <c r="A610" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B610" s="3" t="inlineStr">
@@ -72758,7 +72758,7 @@
     <row r="611">
       <c r="A611" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B611" s="3" t="inlineStr">
@@ -72790,7 +72790,7 @@
     <row r="612">
       <c r="A612" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B612" s="3" t="inlineStr">
@@ -72822,7 +72822,7 @@
     <row r="613">
       <c r="A613" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B613" s="3" t="inlineStr">
@@ -72854,7 +72854,7 @@
     <row r="614">
       <c r="A614" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B614" s="3" t="inlineStr">
@@ -72886,7 +72886,7 @@
     <row r="615">
       <c r="A615" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B615" s="3" t="inlineStr">
@@ -72918,7 +72918,7 @@
     <row r="616">
       <c r="A616" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B616" s="3" t="inlineStr">
@@ -72950,7 +72950,7 @@
     <row r="617">
       <c r="A617" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B617" s="3" t="inlineStr">
@@ -72982,7 +72982,7 @@
     <row r="618">
       <c r="A618" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B618" s="3" t="inlineStr">
@@ -73014,7 +73014,7 @@
     <row r="619">
       <c r="A619" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B619" s="3" t="inlineStr">
@@ -73046,7 +73046,7 @@
     <row r="620">
       <c r="A620" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B620" s="3" t="inlineStr">
@@ -73078,7 +73078,7 @@
     <row r="621">
       <c r="A621" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B621" s="3" t="inlineStr">
@@ -73110,7 +73110,7 @@
     <row r="622">
       <c r="A622" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B622" s="3" t="inlineStr">
@@ -73142,7 +73142,7 @@
     <row r="623">
       <c r="A623" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B623" s="3" t="inlineStr">
@@ -73174,7 +73174,7 @@
     <row r="624">
       <c r="A624" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B624" s="3" t="inlineStr">
@@ -73206,7 +73206,7 @@
     <row r="625">
       <c r="A625" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B625" s="3" t="inlineStr">
@@ -73238,7 +73238,7 @@
     <row r="626">
       <c r="A626" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B626" s="3" t="inlineStr">
@@ -73270,7 +73270,7 @@
     <row r="627">
       <c r="A627" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B627" s="3" t="inlineStr">
@@ -73302,7 +73302,7 @@
     <row r="628">
       <c r="A628" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B628" s="3" t="inlineStr">
@@ -73334,7 +73334,7 @@
     <row r="629">
       <c r="A629" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B629" s="3" t="inlineStr">
@@ -73366,7 +73366,7 @@
     <row r="630">
       <c r="A630" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B630" s="3" t="inlineStr">
@@ -73398,7 +73398,7 @@
     <row r="631">
       <c r="A631" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B631" s="3" t="inlineStr">
@@ -73430,7 +73430,7 @@
     <row r="632">
       <c r="A632" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B632" s="3" t="inlineStr">
@@ -73462,7 +73462,7 @@
     <row r="633">
       <c r="A633" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B633" s="3" t="inlineStr">
@@ -73494,7 +73494,7 @@
     <row r="634">
       <c r="A634" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B634" s="3" t="inlineStr">
@@ -73526,7 +73526,7 @@
     <row r="635">
       <c r="A635" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B635" s="3" t="inlineStr">
@@ -73558,7 +73558,7 @@
     <row r="636">
       <c r="A636" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B636" s="3" t="inlineStr">
@@ -73590,7 +73590,7 @@
     <row r="637">
       <c r="A637" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B637" s="3" t="inlineStr">
@@ -73622,7 +73622,7 @@
     <row r="638">
       <c r="A638" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B638" s="3" t="inlineStr">
@@ -73654,7 +73654,7 @@
     <row r="639">
       <c r="A639" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B639" s="3" t="inlineStr">
@@ -73686,7 +73686,7 @@
     <row r="640">
       <c r="A640" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B640" s="3" t="inlineStr">
@@ -73718,7 +73718,7 @@
     <row r="641">
       <c r="A641" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B641" s="3" t="inlineStr">
@@ -73750,7 +73750,7 @@
     <row r="642">
       <c r="A642" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B642" s="3" t="inlineStr">
@@ -73782,7 +73782,7 @@
     <row r="643">
       <c r="A643" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B643" s="3" t="inlineStr">
@@ -73814,7 +73814,7 @@
     <row r="644">
       <c r="A644" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B644" s="3" t="inlineStr">
@@ -73846,7 +73846,7 @@
     <row r="645">
       <c r="A645" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B645" s="3" t="inlineStr">
@@ -73878,7 +73878,7 @@
     <row r="646">
       <c r="A646" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B646" s="3" t="inlineStr">
@@ -73910,7 +73910,7 @@
     <row r="647">
       <c r="A647" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B647" s="3" t="inlineStr">
@@ -73942,7 +73942,7 @@
     <row r="648">
       <c r="A648" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B648" s="3" t="inlineStr">
@@ -73974,7 +73974,7 @@
     <row r="649">
       <c r="A649" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B649" s="3" t="inlineStr">
@@ -74006,7 +74006,7 @@
     <row r="650">
       <c r="A650" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B650" s="3" t="inlineStr">
@@ -74038,7 +74038,7 @@
     <row r="651">
       <c r="A651" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B651" s="3" t="inlineStr">
@@ -74070,7 +74070,7 @@
     <row r="652">
       <c r="A652" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 20:50:22</t>
+          <t>2026-10-09 01:01:45</t>
         </is>
       </c>
       <c r="B652" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45 UTC</t>
+          <t>2026-10-09 07:24:49 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -53270,7 +53270,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -53302,7 +53302,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -53334,7 +53334,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -53366,7 +53366,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -53398,7 +53398,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -53430,7 +53430,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -53462,7 +53462,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -53494,7 +53494,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -53526,7 +53526,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -53558,7 +53558,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -53590,7 +53590,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -53622,7 +53622,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -53654,7 +53654,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -53686,7 +53686,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -53718,7 +53718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -53750,7 +53750,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -53782,7 +53782,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -53814,7 +53814,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -53846,7 +53846,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -53878,7 +53878,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -53910,7 +53910,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -53942,7 +53942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -53974,7 +53974,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -54006,7 +54006,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -54038,7 +54038,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -54070,7 +54070,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -54102,7 +54102,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -54134,7 +54134,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -54166,7 +54166,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -54198,7 +54198,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -54230,7 +54230,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -54262,7 +54262,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -54294,7 +54294,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -54326,7 +54326,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -54358,7 +54358,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -54390,7 +54390,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -54422,7 +54422,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -54454,7 +54454,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -54486,7 +54486,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -54518,7 +54518,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -54550,7 +54550,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -54582,7 +54582,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -54614,7 +54614,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -54646,7 +54646,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -54678,7 +54678,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -54710,7 +54710,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -54742,7 +54742,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -54774,7 +54774,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -54806,7 +54806,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -54838,7 +54838,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -54870,7 +54870,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -54902,7 +54902,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -54934,7 +54934,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -54966,7 +54966,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -54998,7 +54998,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -55030,7 +55030,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -55062,7 +55062,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -55094,7 +55094,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -55126,7 +55126,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -55158,7 +55158,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -55190,7 +55190,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -55222,7 +55222,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -55254,7 +55254,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -55286,7 +55286,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -55318,7 +55318,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -55350,7 +55350,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -55382,7 +55382,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -55414,7 +55414,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -55446,7 +55446,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -55478,7 +55478,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -55510,7 +55510,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -55542,7 +55542,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -55574,7 +55574,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -55606,7 +55606,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -55638,7 +55638,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -55670,7 +55670,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -55702,7 +55702,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -55734,7 +55734,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -55766,7 +55766,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -55798,7 +55798,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -55830,7 +55830,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -55862,7 +55862,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -55894,7 +55894,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -55926,7 +55926,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -55958,7 +55958,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -55990,7 +55990,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -56022,7 +56022,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -56054,7 +56054,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -56086,7 +56086,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -56118,7 +56118,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -56150,7 +56150,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -56182,7 +56182,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -56214,7 +56214,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -56246,7 +56246,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -56278,7 +56278,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -56310,7 +56310,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -56342,7 +56342,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -56374,7 +56374,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -56406,7 +56406,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -56438,7 +56438,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -56470,7 +56470,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -56502,7 +56502,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -56534,7 +56534,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -56566,7 +56566,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -56598,7 +56598,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -56630,7 +56630,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -56662,7 +56662,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -56694,7 +56694,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -56726,7 +56726,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -56758,7 +56758,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -56790,7 +56790,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -56822,7 +56822,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -56854,7 +56854,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -56886,7 +56886,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -56918,7 +56918,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -56950,7 +56950,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -56982,7 +56982,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -57014,7 +57014,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -57046,7 +57046,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -57078,7 +57078,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -57110,7 +57110,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -57142,7 +57142,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -57174,7 +57174,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -57206,7 +57206,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -57238,7 +57238,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -57270,7 +57270,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -57302,7 +57302,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -57334,7 +57334,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -57366,7 +57366,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -57398,7 +57398,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -57430,7 +57430,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -57462,7 +57462,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -57494,7 +57494,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -57526,7 +57526,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -57558,7 +57558,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -57590,7 +57590,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -57622,7 +57622,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -57654,7 +57654,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -57686,7 +57686,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -57718,7 +57718,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -57750,7 +57750,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -57782,7 +57782,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -57814,7 +57814,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -57846,7 +57846,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -57878,7 +57878,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -57910,7 +57910,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -57942,7 +57942,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -57974,7 +57974,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -58006,7 +58006,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -58038,7 +58038,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -58070,7 +58070,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -58102,7 +58102,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -58134,7 +58134,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -58166,7 +58166,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -58198,7 +58198,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -58230,7 +58230,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -58262,7 +58262,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -58294,7 +58294,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -58326,7 +58326,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -58358,7 +58358,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -58390,7 +58390,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -58422,7 +58422,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -58454,7 +58454,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -58486,7 +58486,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -58518,7 +58518,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -58550,7 +58550,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -58582,7 +58582,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -58614,7 +58614,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -58646,7 +58646,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -58678,7 +58678,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -58710,7 +58710,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -58742,7 +58742,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -58774,7 +58774,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -58806,7 +58806,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -58838,7 +58838,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -58870,7 +58870,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -58902,7 +58902,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -58934,7 +58934,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -58966,7 +58966,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -58998,7 +58998,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -59030,7 +59030,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -59062,7 +59062,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -59094,7 +59094,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -59126,7 +59126,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -59158,7 +59158,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -59190,7 +59190,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -59222,7 +59222,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -59254,7 +59254,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -59286,7 +59286,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -59318,7 +59318,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -59350,7 +59350,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -59382,7 +59382,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -59414,7 +59414,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -59446,7 +59446,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -59478,7 +59478,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -59510,7 +59510,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -59542,7 +59542,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -59574,7 +59574,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -59606,7 +59606,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -59638,7 +59638,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -59670,7 +59670,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -59702,7 +59702,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -59734,7 +59734,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -59766,7 +59766,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -59798,7 +59798,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -59830,7 +59830,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -59862,7 +59862,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -59894,7 +59894,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -59926,7 +59926,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -59958,7 +59958,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -59990,7 +59990,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -60022,7 +60022,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -60054,7 +60054,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -60086,7 +60086,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -60118,7 +60118,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -60150,7 +60150,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -60182,7 +60182,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -60214,7 +60214,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -60246,7 +60246,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -60278,7 +60278,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -60310,7 +60310,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -60342,7 +60342,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -60374,7 +60374,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -60406,7 +60406,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -60438,7 +60438,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -60470,7 +60470,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -60502,7 +60502,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -60534,7 +60534,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -60566,7 +60566,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -60598,7 +60598,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -60630,7 +60630,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -60662,7 +60662,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -60694,7 +60694,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -60726,7 +60726,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -60758,7 +60758,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -60790,7 +60790,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -60822,7 +60822,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -60854,7 +60854,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -60886,7 +60886,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -60918,7 +60918,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -60950,7 +60950,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -60982,7 +60982,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -61014,7 +61014,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -61046,7 +61046,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -61078,7 +61078,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -61110,7 +61110,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -61142,7 +61142,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -61174,7 +61174,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -61206,7 +61206,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -61238,7 +61238,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -61270,7 +61270,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -61302,7 +61302,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -61334,7 +61334,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -61366,7 +61366,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -61398,7 +61398,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -61430,7 +61430,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -61462,7 +61462,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -61494,7 +61494,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -61526,7 +61526,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -61558,7 +61558,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -61590,7 +61590,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -61622,7 +61622,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -61654,7 +61654,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -61686,7 +61686,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -61718,7 +61718,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -61750,7 +61750,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -61782,7 +61782,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -61814,7 +61814,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -61846,7 +61846,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -61878,7 +61878,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -61910,7 +61910,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -61942,7 +61942,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -61974,7 +61974,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -62006,7 +62006,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -62038,7 +62038,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -62070,7 +62070,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -62102,7 +62102,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -62134,7 +62134,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -62166,7 +62166,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -62198,7 +62198,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -62230,7 +62230,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -62262,7 +62262,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -62294,7 +62294,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -62326,7 +62326,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -62358,7 +62358,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -62390,7 +62390,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -62422,7 +62422,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -62454,7 +62454,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -62486,7 +62486,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -62518,7 +62518,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -62550,7 +62550,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -62582,7 +62582,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -62614,7 +62614,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -62646,7 +62646,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -62678,7 +62678,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -62710,7 +62710,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -62742,7 +62742,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -62774,7 +62774,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -62806,7 +62806,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -62838,7 +62838,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
@@ -62870,7 +62870,7 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
@@ -62902,7 +62902,7 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
@@ -62934,7 +62934,7 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -62966,7 +62966,7 @@
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
@@ -62998,7 +62998,7 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -63030,7 +63030,7 @@
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
@@ -63062,7 +63062,7 @@
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
@@ -63094,7 +63094,7 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
@@ -63126,7 +63126,7 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
@@ -63158,7 +63158,7 @@
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
@@ -63190,7 +63190,7 @@
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -63222,7 +63222,7 @@
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B313" s="3" t="inlineStr">
@@ -63254,7 +63254,7 @@
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
@@ -63286,7 +63286,7 @@
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
@@ -63318,7 +63318,7 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
@@ -63350,7 +63350,7 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B317" s="3" t="inlineStr">
@@ -63382,7 +63382,7 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
@@ -63414,7 +63414,7 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
@@ -63446,7 +63446,7 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
@@ -63478,7 +63478,7 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
@@ -63510,7 +63510,7 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
@@ -63542,7 +63542,7 @@
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B323" s="3" t="inlineStr">
@@ -63574,7 +63574,7 @@
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
@@ -63606,7 +63606,7 @@
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B325" s="3" t="inlineStr">
@@ -63638,7 +63638,7 @@
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
@@ -63670,7 +63670,7 @@
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B327" s="3" t="inlineStr">
@@ -63702,7 +63702,7 @@
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
@@ -63734,7 +63734,7 @@
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B329" s="3" t="inlineStr">
@@ -63766,7 +63766,7 @@
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
@@ -63798,7 +63798,7 @@
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B331" s="3" t="inlineStr">
@@ -63830,7 +63830,7 @@
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
@@ -63862,7 +63862,7 @@
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B333" s="3" t="inlineStr">
@@ -63894,7 +63894,7 @@
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
@@ -63926,7 +63926,7 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B335" s="3" t="inlineStr">
@@ -63958,7 +63958,7 @@
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
@@ -63990,7 +63990,7 @@
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B337" s="3" t="inlineStr">
@@ -64022,7 +64022,7 @@
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
@@ -64054,7 +64054,7 @@
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B339" s="3" t="inlineStr">
@@ -64086,7 +64086,7 @@
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
@@ -64118,7 +64118,7 @@
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B341" s="3" t="inlineStr">
@@ -64150,7 +64150,7 @@
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
@@ -64182,7 +64182,7 @@
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B343" s="3" t="inlineStr">
@@ -64214,7 +64214,7 @@
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
@@ -64246,7 +64246,7 @@
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B345" s="3" t="inlineStr">
@@ -64278,7 +64278,7 @@
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
@@ -64310,7 +64310,7 @@
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B347" s="3" t="inlineStr">
@@ -64342,7 +64342,7 @@
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
@@ -64374,7 +64374,7 @@
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B349" s="3" t="inlineStr">
@@ -64406,7 +64406,7 @@
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
@@ -64438,7 +64438,7 @@
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B351" s="3" t="inlineStr">
@@ -64470,7 +64470,7 @@
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
@@ -64502,7 +64502,7 @@
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B353" s="3" t="inlineStr">
@@ -64534,7 +64534,7 @@
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
@@ -64566,7 +64566,7 @@
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B355" s="3" t="inlineStr">
@@ -64598,7 +64598,7 @@
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
@@ -64630,7 +64630,7 @@
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B357" s="3" t="inlineStr">
@@ -64662,7 +64662,7 @@
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
@@ -64694,7 +64694,7 @@
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B359" s="3" t="inlineStr">
@@ -64726,7 +64726,7 @@
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
@@ -64758,7 +64758,7 @@
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B361" s="3" t="inlineStr">
@@ -64790,7 +64790,7 @@
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
@@ -64822,7 +64822,7 @@
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B363" s="3" t="inlineStr">
@@ -64854,7 +64854,7 @@
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
@@ -64886,7 +64886,7 @@
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B365" s="3" t="inlineStr">
@@ -64918,7 +64918,7 @@
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
@@ -64950,7 +64950,7 @@
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B367" s="3" t="inlineStr">
@@ -64982,7 +64982,7 @@
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
@@ -65014,7 +65014,7 @@
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B369" s="3" t="inlineStr">
@@ -65046,7 +65046,7 @@
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
@@ -65078,7 +65078,7 @@
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B371" s="3" t="inlineStr">
@@ -65110,7 +65110,7 @@
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
@@ -65142,7 +65142,7 @@
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B373" s="3" t="inlineStr">
@@ -65174,7 +65174,7 @@
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
@@ -65206,7 +65206,7 @@
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B375" s="3" t="inlineStr">
@@ -65238,7 +65238,7 @@
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
@@ -65270,7 +65270,7 @@
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B377" s="3" t="inlineStr">
@@ -65302,7 +65302,7 @@
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
@@ -65334,7 +65334,7 @@
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B379" s="3" t="inlineStr">
@@ -65366,7 +65366,7 @@
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
@@ -65398,7 +65398,7 @@
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B381" s="3" t="inlineStr">
@@ -65430,7 +65430,7 @@
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
@@ -65462,7 +65462,7 @@
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B383" s="3" t="inlineStr">
@@ -65494,7 +65494,7 @@
     <row r="384">
       <c r="A384" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
@@ -65526,7 +65526,7 @@
     <row r="385">
       <c r="A385" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B385" s="3" t="inlineStr">
@@ -65558,7 +65558,7 @@
     <row r="386">
       <c r="A386" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
@@ -65590,7 +65590,7 @@
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B387" s="3" t="inlineStr">
@@ -65622,7 +65622,7 @@
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
@@ -65654,7 +65654,7 @@
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B389" s="3" t="inlineStr">
@@ -65686,7 +65686,7 @@
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
@@ -65718,7 +65718,7 @@
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B391" s="3" t="inlineStr">
@@ -65750,7 +65750,7 @@
     <row r="392">
       <c r="A392" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
@@ -65782,7 +65782,7 @@
     <row r="393">
       <c r="A393" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B393" s="3" t="inlineStr">
@@ -65814,7 +65814,7 @@
     <row r="394">
       <c r="A394" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
@@ -65846,7 +65846,7 @@
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B395" s="3" t="inlineStr">
@@ -65878,7 +65878,7 @@
     <row r="396">
       <c r="A396" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
@@ -65910,7 +65910,7 @@
     <row r="397">
       <c r="A397" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B397" s="3" t="inlineStr">
@@ -65942,7 +65942,7 @@
     <row r="398">
       <c r="A398" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
@@ -65974,7 +65974,7 @@
     <row r="399">
       <c r="A399" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B399" s="3" t="inlineStr">
@@ -66006,7 +66006,7 @@
     <row r="400">
       <c r="A400" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
@@ -66038,7 +66038,7 @@
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B401" s="3" t="inlineStr">
@@ -66070,7 +66070,7 @@
     <row r="402">
       <c r="A402" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
@@ -66102,7 +66102,7 @@
     <row r="403">
       <c r="A403" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B403" s="3" t="inlineStr">
@@ -66134,7 +66134,7 @@
     <row r="404">
       <c r="A404" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
@@ -66166,7 +66166,7 @@
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B405" s="3" t="inlineStr">
@@ -66198,7 +66198,7 @@
     <row r="406">
       <c r="A406" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
@@ -66230,7 +66230,7 @@
     <row r="407">
       <c r="A407" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B407" s="3" t="inlineStr">
@@ -66262,7 +66262,7 @@
     <row r="408">
       <c r="A408" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
@@ -66294,7 +66294,7 @@
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B409" s="3" t="inlineStr">
@@ -66326,7 +66326,7 @@
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
@@ -66358,7 +66358,7 @@
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B411" s="3" t="inlineStr">
@@ -66390,7 +66390,7 @@
     <row r="412">
       <c r="A412" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
@@ -66422,7 +66422,7 @@
     <row r="413">
       <c r="A413" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B413" s="3" t="inlineStr">
@@ -66454,7 +66454,7 @@
     <row r="414">
       <c r="A414" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
@@ -66486,7 +66486,7 @@
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B415" s="3" t="inlineStr">
@@ -66518,7 +66518,7 @@
     <row r="416">
       <c r="A416" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B416" s="3" t="inlineStr">
@@ -66550,7 +66550,7 @@
     <row r="417">
       <c r="A417" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B417" s="3" t="inlineStr">
@@ -66582,7 +66582,7 @@
     <row r="418">
       <c r="A418" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -66614,7 +66614,7 @@
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B419" s="3" t="inlineStr">
@@ -66646,7 +66646,7 @@
     <row r="420">
       <c r="A420" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
@@ -66678,7 +66678,7 @@
     <row r="421">
       <c r="A421" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B421" s="3" t="inlineStr">
@@ -66710,7 +66710,7 @@
     <row r="422">
       <c r="A422" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B422" s="3" t="inlineStr">
@@ -66742,7 +66742,7 @@
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B423" s="3" t="inlineStr">
@@ -66774,7 +66774,7 @@
     <row r="424">
       <c r="A424" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
@@ -66806,7 +66806,7 @@
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B425" s="3" t="inlineStr">
@@ -66838,7 +66838,7 @@
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
@@ -66870,7 +66870,7 @@
     <row r="427">
       <c r="A427" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B427" s="3" t="inlineStr">
@@ -66902,7 +66902,7 @@
     <row r="428">
       <c r="A428" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
@@ -66934,7 +66934,7 @@
     <row r="429">
       <c r="A429" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B429" s="3" t="inlineStr">
@@ -66966,7 +66966,7 @@
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
@@ -66998,7 +66998,7 @@
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B431" s="3" t="inlineStr">
@@ -67030,7 +67030,7 @@
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
@@ -67062,7 +67062,7 @@
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B433" s="3" t="inlineStr">
@@ -67094,7 +67094,7 @@
     <row r="434">
       <c r="A434" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
@@ -67126,7 +67126,7 @@
     <row r="435">
       <c r="A435" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B435" s="3" t="inlineStr">
@@ -67158,7 +67158,7 @@
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
@@ -67190,7 +67190,7 @@
     <row r="437">
       <c r="A437" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B437" s="3" t="inlineStr">
@@ -67222,7 +67222,7 @@
     <row r="438">
       <c r="A438" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
@@ -67254,7 +67254,7 @@
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B439" s="3" t="inlineStr">
@@ -67286,7 +67286,7 @@
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -67318,7 +67318,7 @@
     <row r="441">
       <c r="A441" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B441" s="3" t="inlineStr">
@@ -67350,7 +67350,7 @@
     <row r="442">
       <c r="A442" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -67382,7 +67382,7 @@
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B443" s="3" t="inlineStr">
@@ -67414,7 +67414,7 @@
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
@@ -67446,7 +67446,7 @@
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B445" s="3" t="inlineStr">
@@ -67478,7 +67478,7 @@
     <row r="446">
       <c r="A446" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
@@ -67510,7 +67510,7 @@
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B447" s="3" t="inlineStr">
@@ -67542,7 +67542,7 @@
     <row r="448">
       <c r="A448" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
@@ -67574,7 +67574,7 @@
     <row r="449">
       <c r="A449" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B449" s="3" t="inlineStr">
@@ -67606,7 +67606,7 @@
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
@@ -67638,7 +67638,7 @@
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B451" s="3" t="inlineStr">
@@ -67670,7 +67670,7 @@
     <row r="452">
       <c r="A452" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
@@ -67702,7 +67702,7 @@
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B453" s="3" t="inlineStr">
@@ -67734,7 +67734,7 @@
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
@@ -67766,7 +67766,7 @@
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B455" s="3" t="inlineStr">
@@ -67798,7 +67798,7 @@
     <row r="456">
       <c r="A456" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
@@ -67830,7 +67830,7 @@
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B457" s="3" t="inlineStr">
@@ -67862,7 +67862,7 @@
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
@@ -67894,7 +67894,7 @@
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B459" s="3" t="inlineStr">
@@ -67926,7 +67926,7 @@
     <row r="460">
       <c r="A460" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
@@ -67958,7 +67958,7 @@
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B461" s="3" t="inlineStr">
@@ -67990,7 +67990,7 @@
     <row r="462">
       <c r="A462" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
@@ -68022,7 +68022,7 @@
     <row r="463">
       <c r="A463" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B463" s="3" t="inlineStr">
@@ -68054,7 +68054,7 @@
     <row r="464">
       <c r="A464" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B464" s="3" t="inlineStr">
@@ -68086,7 +68086,7 @@
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B465" s="3" t="inlineStr">
@@ -68118,7 +68118,7 @@
     <row r="466">
       <c r="A466" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
@@ -68150,7 +68150,7 @@
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B467" s="3" t="inlineStr">
@@ -68182,7 +68182,7 @@
     <row r="468">
       <c r="A468" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
@@ -68214,7 +68214,7 @@
     <row r="469">
       <c r="A469" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B469" s="3" t="inlineStr">
@@ -68246,7 +68246,7 @@
     <row r="470">
       <c r="A470" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
@@ -68278,7 +68278,7 @@
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B471" s="3" t="inlineStr">
@@ -68310,7 +68310,7 @@
     <row r="472">
       <c r="A472" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B472" s="3" t="inlineStr">
@@ -68342,7 +68342,7 @@
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B473" s="3" t="inlineStr">
@@ -68374,7 +68374,7 @@
     <row r="474">
       <c r="A474" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B474" s="3" t="inlineStr">
@@ -68406,7 +68406,7 @@
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B475" s="3" t="inlineStr">
@@ -68438,7 +68438,7 @@
     <row r="476">
       <c r="A476" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B476" s="3" t="inlineStr">
@@ -68470,7 +68470,7 @@
     <row r="477">
       <c r="A477" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B477" s="3" t="inlineStr">
@@ -68502,7 +68502,7 @@
     <row r="478">
       <c r="A478" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B478" s="3" t="inlineStr">
@@ -68534,7 +68534,7 @@
     <row r="479">
       <c r="A479" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B479" s="3" t="inlineStr">
@@ -68566,7 +68566,7 @@
     <row r="480">
       <c r="A480" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B480" s="3" t="inlineStr">
@@ -68598,7 +68598,7 @@
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B481" s="3" t="inlineStr">
@@ -68630,7 +68630,7 @@
     <row r="482">
       <c r="A482" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B482" s="3" t="inlineStr">
@@ -68662,7 +68662,7 @@
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B483" s="3" t="inlineStr">
@@ -68694,7 +68694,7 @@
     <row r="484">
       <c r="A484" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
@@ -68726,7 +68726,7 @@
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B485" s="3" t="inlineStr">
@@ -68758,7 +68758,7 @@
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B486" s="3" t="inlineStr">
@@ -68790,7 +68790,7 @@
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B487" s="3" t="inlineStr">
@@ -68822,7 +68822,7 @@
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B488" s="3" t="inlineStr">
@@ -68854,7 +68854,7 @@
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B489" s="3" t="inlineStr">
@@ -68886,7 +68886,7 @@
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B490" s="3" t="inlineStr">
@@ -68918,7 +68918,7 @@
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B491" s="3" t="inlineStr">
@@ -68950,7 +68950,7 @@
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B492" s="3" t="inlineStr">
@@ -68982,7 +68982,7 @@
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B493" s="3" t="inlineStr">
@@ -69014,7 +69014,7 @@
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B494" s="3" t="inlineStr">
@@ -69046,7 +69046,7 @@
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B495" s="3" t="inlineStr">
@@ -69078,7 +69078,7 @@
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B496" s="3" t="inlineStr">
@@ -69110,7 +69110,7 @@
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B497" s="3" t="inlineStr">
@@ -69142,7 +69142,7 @@
     <row r="498">
       <c r="A498" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B498" s="3" t="inlineStr">
@@ -69174,7 +69174,7 @@
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B499" s="3" t="inlineStr">
@@ -69206,7 +69206,7 @@
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B500" s="3" t="inlineStr">
@@ -69238,7 +69238,7 @@
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B501" s="3" t="inlineStr">
@@ -69270,7 +69270,7 @@
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B502" s="3" t="inlineStr">
@@ -69302,7 +69302,7 @@
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B503" s="3" t="inlineStr">
@@ -69334,7 +69334,7 @@
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B504" s="3" t="inlineStr">
@@ -69366,7 +69366,7 @@
     <row r="505">
       <c r="A505" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B505" s="3" t="inlineStr">
@@ -69398,7 +69398,7 @@
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B506" s="3" t="inlineStr">
@@ -69430,7 +69430,7 @@
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B507" s="3" t="inlineStr">
@@ -69462,7 +69462,7 @@
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B508" s="3" t="inlineStr">
@@ -69494,7 +69494,7 @@
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B509" s="3" t="inlineStr">
@@ -69526,7 +69526,7 @@
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B510" s="3" t="inlineStr">
@@ -69558,7 +69558,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B511" s="3" t="inlineStr">
@@ -69590,7 +69590,7 @@
     <row r="512">
       <c r="A512" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B512" s="3" t="inlineStr">
@@ -69622,7 +69622,7 @@
     <row r="513">
       <c r="A513" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B513" s="3" t="inlineStr">
@@ -69654,7 +69654,7 @@
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B514" s="3" t="inlineStr">
@@ -69686,7 +69686,7 @@
     <row r="515">
       <c r="A515" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B515" s="3" t="inlineStr">
@@ -69718,7 +69718,7 @@
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B516" s="3" t="inlineStr">
@@ -69750,7 +69750,7 @@
     <row r="517">
       <c r="A517" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B517" s="3" t="inlineStr">
@@ -69782,7 +69782,7 @@
     <row r="518">
       <c r="A518" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B518" s="3" t="inlineStr">
@@ -69814,7 +69814,7 @@
     <row r="519">
       <c r="A519" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B519" s="3" t="inlineStr">
@@ -69846,7 +69846,7 @@
     <row r="520">
       <c r="A520" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B520" s="3" t="inlineStr">
@@ -69878,7 +69878,7 @@
     <row r="521">
       <c r="A521" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B521" s="3" t="inlineStr">
@@ -69910,7 +69910,7 @@
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B522" s="3" t="inlineStr">
@@ -69942,7 +69942,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B523" s="3" t="inlineStr">
@@ -69974,7 +69974,7 @@
     <row r="524">
       <c r="A524" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B524" s="3" t="inlineStr">
@@ -70006,7 +70006,7 @@
     <row r="525">
       <c r="A525" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B525" s="3" t="inlineStr">
@@ -70038,7 +70038,7 @@
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B526" s="3" t="inlineStr">
@@ -70070,7 +70070,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B527" s="3" t="inlineStr">
@@ -70102,7 +70102,7 @@
     <row r="528">
       <c r="A528" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B528" s="3" t="inlineStr">
@@ -70134,7 +70134,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B529" s="3" t="inlineStr">
@@ -70166,7 +70166,7 @@
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B530" s="3" t="inlineStr">
@@ -70198,7 +70198,7 @@
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B531" s="3" t="inlineStr">
@@ -70230,7 +70230,7 @@
     <row r="532">
       <c r="A532" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B532" s="3" t="inlineStr">
@@ -70262,7 +70262,7 @@
     <row r="533">
       <c r="A533" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B533" s="3" t="inlineStr">
@@ -70294,7 +70294,7 @@
     <row r="534">
       <c r="A534" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B534" s="3" t="inlineStr">
@@ -70326,7 +70326,7 @@
     <row r="535">
       <c r="A535" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B535" s="3" t="inlineStr">
@@ -70358,7 +70358,7 @@
     <row r="536">
       <c r="A536" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B536" s="3" t="inlineStr">
@@ -70390,7 +70390,7 @@
     <row r="537">
       <c r="A537" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B537" s="3" t="inlineStr">
@@ -70422,7 +70422,7 @@
     <row r="538">
       <c r="A538" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B538" s="3" t="inlineStr">
@@ -70454,7 +70454,7 @@
     <row r="539">
       <c r="A539" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B539" s="3" t="inlineStr">
@@ -70486,7 +70486,7 @@
     <row r="540">
       <c r="A540" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B540" s="3" t="inlineStr">
@@ -70518,7 +70518,7 @@
     <row r="541">
       <c r="A541" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B541" s="3" t="inlineStr">
@@ -70550,7 +70550,7 @@
     <row r="542">
       <c r="A542" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B542" s="3" t="inlineStr">
@@ -70582,7 +70582,7 @@
     <row r="543">
       <c r="A543" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B543" s="3" t="inlineStr">
@@ -70614,7 +70614,7 @@
     <row r="544">
       <c r="A544" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B544" s="3" t="inlineStr">
@@ -70646,7 +70646,7 @@
     <row r="545">
       <c r="A545" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B545" s="3" t="inlineStr">
@@ -70678,7 +70678,7 @@
     <row r="546">
       <c r="A546" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B546" s="3" t="inlineStr">
@@ -70710,7 +70710,7 @@
     <row r="547">
       <c r="A547" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B547" s="3" t="inlineStr">
@@ -70742,7 +70742,7 @@
     <row r="548">
       <c r="A548" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B548" s="3" t="inlineStr">
@@ -70774,7 +70774,7 @@
     <row r="549">
       <c r="A549" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B549" s="3" t="inlineStr">
@@ -70806,7 +70806,7 @@
     <row r="550">
       <c r="A550" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B550" s="3" t="inlineStr">
@@ -70838,7 +70838,7 @@
     <row r="551">
       <c r="A551" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B551" s="3" t="inlineStr">
@@ -70870,7 +70870,7 @@
     <row r="552">
       <c r="A552" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B552" s="3" t="inlineStr">
@@ -70902,7 +70902,7 @@
     <row r="553">
       <c r="A553" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B553" s="3" t="inlineStr">
@@ -70934,7 +70934,7 @@
     <row r="554">
       <c r="A554" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B554" s="3" t="inlineStr">
@@ -70966,7 +70966,7 @@
     <row r="555">
       <c r="A555" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B555" s="3" t="inlineStr">
@@ -70998,7 +70998,7 @@
     <row r="556">
       <c r="A556" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B556" s="3" t="inlineStr">
@@ -71030,7 +71030,7 @@
     <row r="557">
       <c r="A557" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B557" s="3" t="inlineStr">
@@ -71062,7 +71062,7 @@
     <row r="558">
       <c r="A558" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B558" s="3" t="inlineStr">
@@ -71094,7 +71094,7 @@
     <row r="559">
       <c r="A559" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B559" s="3" t="inlineStr">
@@ -71126,7 +71126,7 @@
     <row r="560">
       <c r="A560" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B560" s="3" t="inlineStr">
@@ -71158,7 +71158,7 @@
     <row r="561">
       <c r="A561" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B561" s="3" t="inlineStr">
@@ -71190,7 +71190,7 @@
     <row r="562">
       <c r="A562" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B562" s="3" t="inlineStr">
@@ -71222,7 +71222,7 @@
     <row r="563">
       <c r="A563" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B563" s="3" t="inlineStr">
@@ -71254,7 +71254,7 @@
     <row r="564">
       <c r="A564" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B564" s="3" t="inlineStr">
@@ -71286,7 +71286,7 @@
     <row r="565">
       <c r="A565" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B565" s="3" t="inlineStr">
@@ -71318,7 +71318,7 @@
     <row r="566">
       <c r="A566" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B566" s="3" t="inlineStr">
@@ -71350,7 +71350,7 @@
     <row r="567">
       <c r="A567" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B567" s="3" t="inlineStr">
@@ -71382,7 +71382,7 @@
     <row r="568">
       <c r="A568" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B568" s="3" t="inlineStr">
@@ -71414,7 +71414,7 @@
     <row r="569">
       <c r="A569" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B569" s="3" t="inlineStr">
@@ -71446,7 +71446,7 @@
     <row r="570">
       <c r="A570" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B570" s="3" t="inlineStr">
@@ -71478,7 +71478,7 @@
     <row r="571">
       <c r="A571" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B571" s="3" t="inlineStr">
@@ -71510,7 +71510,7 @@
     <row r="572">
       <c r="A572" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B572" s="3" t="inlineStr">
@@ -71542,7 +71542,7 @@
     <row r="573">
       <c r="A573" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B573" s="3" t="inlineStr">
@@ -71574,7 +71574,7 @@
     <row r="574">
       <c r="A574" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B574" s="3" t="inlineStr">
@@ -71606,7 +71606,7 @@
     <row r="575">
       <c r="A575" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B575" s="3" t="inlineStr">
@@ -71638,7 +71638,7 @@
     <row r="576">
       <c r="A576" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B576" s="3" t="inlineStr">
@@ -71670,7 +71670,7 @@
     <row r="577">
       <c r="A577" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B577" s="3" t="inlineStr">
@@ -71702,7 +71702,7 @@
     <row r="578">
       <c r="A578" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B578" s="3" t="inlineStr">
@@ -71734,7 +71734,7 @@
     <row r="579">
       <c r="A579" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B579" s="3" t="inlineStr">
@@ -71766,7 +71766,7 @@
     <row r="580">
       <c r="A580" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B580" s="3" t="inlineStr">
@@ -71798,7 +71798,7 @@
     <row r="581">
       <c r="A581" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B581" s="3" t="inlineStr">
@@ -71830,7 +71830,7 @@
     <row r="582">
       <c r="A582" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B582" s="3" t="inlineStr">
@@ -71862,7 +71862,7 @@
     <row r="583">
       <c r="A583" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B583" s="3" t="inlineStr">
@@ -71894,7 +71894,7 @@
     <row r="584">
       <c r="A584" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B584" s="3" t="inlineStr">
@@ -71926,7 +71926,7 @@
     <row r="585">
       <c r="A585" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B585" s="3" t="inlineStr">
@@ -71958,7 +71958,7 @@
     <row r="586">
       <c r="A586" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B586" s="3" t="inlineStr">
@@ -71990,7 +71990,7 @@
     <row r="587">
       <c r="A587" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B587" s="3" t="inlineStr">
@@ -72022,7 +72022,7 @@
     <row r="588">
       <c r="A588" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B588" s="3" t="inlineStr">
@@ -72054,7 +72054,7 @@
     <row r="589">
       <c r="A589" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B589" s="3" t="inlineStr">
@@ -72086,7 +72086,7 @@
     <row r="590">
       <c r="A590" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B590" s="3" t="inlineStr">
@@ -72118,7 +72118,7 @@
     <row r="591">
       <c r="A591" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B591" s="3" t="inlineStr">
@@ -72150,7 +72150,7 @@
     <row r="592">
       <c r="A592" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B592" s="3" t="inlineStr">
@@ -72182,7 +72182,7 @@
     <row r="593">
       <c r="A593" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B593" s="3" t="inlineStr">
@@ -72214,7 +72214,7 @@
     <row r="594">
       <c r="A594" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B594" s="3" t="inlineStr">
@@ -72246,7 +72246,7 @@
     <row r="595">
       <c r="A595" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B595" s="3" t="inlineStr">
@@ -72278,7 +72278,7 @@
     <row r="596">
       <c r="A596" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B596" s="3" t="inlineStr">
@@ -72310,7 +72310,7 @@
     <row r="597">
       <c r="A597" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B597" s="3" t="inlineStr">
@@ -72342,7 +72342,7 @@
     <row r="598">
       <c r="A598" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B598" s="3" t="inlineStr">
@@ -72374,7 +72374,7 @@
     <row r="599">
       <c r="A599" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B599" s="3" t="inlineStr">
@@ -72406,7 +72406,7 @@
     <row r="600">
       <c r="A600" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B600" s="3" t="inlineStr">
@@ -72438,7 +72438,7 @@
     <row r="601">
       <c r="A601" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B601" s="3" t="inlineStr">
@@ -72470,7 +72470,7 @@
     <row r="602">
       <c r="A602" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B602" s="3" t="inlineStr">
@@ -72502,7 +72502,7 @@
     <row r="603">
       <c r="A603" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B603" s="3" t="inlineStr">
@@ -72534,7 +72534,7 @@
     <row r="604">
       <c r="A604" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B604" s="3" t="inlineStr">
@@ -72566,7 +72566,7 @@
     <row r="605">
       <c r="A605" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B605" s="3" t="inlineStr">
@@ -72598,7 +72598,7 @@
     <row r="606">
       <c r="A606" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B606" s="3" t="inlineStr">
@@ -72630,7 +72630,7 @@
     <row r="607">
       <c r="A607" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B607" s="3" t="inlineStr">
@@ -72662,7 +72662,7 @@
     <row r="608">
       <c r="A608" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B608" s="3" t="inlineStr">
@@ -72694,7 +72694,7 @@
     <row r="609">
       <c r="A609" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B609" s="3" t="inlineStr">
@@ -72726,7 +72726,7 @@
     <row r="610">
       <c r="A610" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B610" s="3" t="inlineStr">
@@ -72758,7 +72758,7 @@
     <row r="611">
       <c r="A611" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B611" s="3" t="inlineStr">
@@ -72790,7 +72790,7 @@
     <row r="612">
       <c r="A612" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B612" s="3" t="inlineStr">
@@ -72822,7 +72822,7 @@
     <row r="613">
       <c r="A613" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B613" s="3" t="inlineStr">
@@ -72854,7 +72854,7 @@
     <row r="614">
       <c r="A614" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B614" s="3" t="inlineStr">
@@ -72886,7 +72886,7 @@
     <row r="615">
       <c r="A615" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B615" s="3" t="inlineStr">
@@ -72918,7 +72918,7 @@
     <row r="616">
       <c r="A616" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B616" s="3" t="inlineStr">
@@ -72950,7 +72950,7 @@
     <row r="617">
       <c r="A617" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B617" s="3" t="inlineStr">
@@ -72982,7 +72982,7 @@
     <row r="618">
       <c r="A618" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B618" s="3" t="inlineStr">
@@ -73014,7 +73014,7 @@
     <row r="619">
       <c r="A619" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B619" s="3" t="inlineStr">
@@ -73046,7 +73046,7 @@
     <row r="620">
       <c r="A620" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B620" s="3" t="inlineStr">
@@ -73078,7 +73078,7 @@
     <row r="621">
       <c r="A621" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B621" s="3" t="inlineStr">
@@ -73110,7 +73110,7 @@
     <row r="622">
       <c r="A622" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B622" s="3" t="inlineStr">
@@ -73142,7 +73142,7 @@
     <row r="623">
       <c r="A623" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B623" s="3" t="inlineStr">
@@ -73174,7 +73174,7 @@
     <row r="624">
       <c r="A624" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B624" s="3" t="inlineStr">
@@ -73206,7 +73206,7 @@
     <row r="625">
       <c r="A625" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B625" s="3" t="inlineStr">
@@ -73238,7 +73238,7 @@
     <row r="626">
       <c r="A626" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B626" s="3" t="inlineStr">
@@ -73270,7 +73270,7 @@
     <row r="627">
       <c r="A627" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B627" s="3" t="inlineStr">
@@ -73302,7 +73302,7 @@
     <row r="628">
       <c r="A628" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B628" s="3" t="inlineStr">
@@ -73334,7 +73334,7 @@
     <row r="629">
       <c r="A629" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B629" s="3" t="inlineStr">
@@ -73366,7 +73366,7 @@
     <row r="630">
       <c r="A630" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B630" s="3" t="inlineStr">
@@ -73398,7 +73398,7 @@
     <row r="631">
       <c r="A631" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B631" s="3" t="inlineStr">
@@ -73430,7 +73430,7 @@
     <row r="632">
       <c r="A632" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B632" s="3" t="inlineStr">
@@ -73462,7 +73462,7 @@
     <row r="633">
       <c r="A633" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B633" s="3" t="inlineStr">
@@ -73494,7 +73494,7 @@
     <row r="634">
       <c r="A634" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B634" s="3" t="inlineStr">
@@ -73526,7 +73526,7 @@
     <row r="635">
       <c r="A635" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B635" s="3" t="inlineStr">
@@ -73558,7 +73558,7 @@
     <row r="636">
       <c r="A636" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B636" s="3" t="inlineStr">
@@ -73590,7 +73590,7 @@
     <row r="637">
       <c r="A637" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B637" s="3" t="inlineStr">
@@ -73622,7 +73622,7 @@
     <row r="638">
       <c r="A638" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B638" s="3" t="inlineStr">
@@ -73654,7 +73654,7 @@
     <row r="639">
       <c r="A639" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B639" s="3" t="inlineStr">
@@ -73686,7 +73686,7 @@
     <row r="640">
       <c r="A640" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B640" s="3" t="inlineStr">
@@ -73718,7 +73718,7 @@
     <row r="641">
       <c r="A641" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B641" s="3" t="inlineStr">
@@ -73750,7 +73750,7 @@
     <row r="642">
       <c r="A642" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B642" s="3" t="inlineStr">
@@ -73782,7 +73782,7 @@
     <row r="643">
       <c r="A643" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B643" s="3" t="inlineStr">
@@ -73814,7 +73814,7 @@
     <row r="644">
       <c r="A644" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B644" s="3" t="inlineStr">
@@ -73846,7 +73846,7 @@
     <row r="645">
       <c r="A645" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B645" s="3" t="inlineStr">
@@ -73878,7 +73878,7 @@
     <row r="646">
       <c r="A646" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B646" s="3" t="inlineStr">
@@ -73910,7 +73910,7 @@
     <row r="647">
       <c r="A647" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B647" s="3" t="inlineStr">
@@ -73942,7 +73942,7 @@
     <row r="648">
       <c r="A648" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B648" s="3" t="inlineStr">
@@ -73974,7 +73974,7 @@
     <row r="649">
       <c r="A649" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B649" s="3" t="inlineStr">
@@ -74006,7 +74006,7 @@
     <row r="650">
       <c r="A650" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B650" s="3" t="inlineStr">
@@ -74038,7 +74038,7 @@
     <row r="651">
       <c r="A651" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B651" s="3" t="inlineStr">
@@ -74070,7 +74070,7 @@
     <row r="652">
       <c r="A652" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 01:01:45</t>
+          <t>2026-10-09 07:24:49</t>
         </is>
       </c>
       <c r="B652" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49 UTC</t>
+          <t>2026-10-09 16:40:41 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3477,16 +3477,16 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>Content audit: 4 issue group(s)</t>
+          <t>Content audit: 3 issue group(s)</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>37d466c17901ff2a522fb0411245613e7df2ba8c</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36">
@@ -53270,7 +53270,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -53302,7 +53302,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -53334,7 +53334,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -53366,7 +53366,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -53398,7 +53398,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -53430,7 +53430,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -53462,7 +53462,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -53494,7 +53494,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -53526,7 +53526,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -53558,7 +53558,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -53590,7 +53590,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -53622,7 +53622,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -53654,7 +53654,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -53686,7 +53686,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -53718,7 +53718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -53750,7 +53750,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -53782,7 +53782,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -53814,7 +53814,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -53846,7 +53846,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -53878,7 +53878,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -53910,7 +53910,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -53942,7 +53942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -53974,7 +53974,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -54006,7 +54006,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -54038,7 +54038,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -54070,7 +54070,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -54102,7 +54102,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -54134,7 +54134,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -54166,7 +54166,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -54198,7 +54198,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -54230,7 +54230,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -54262,7 +54262,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -54294,7 +54294,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -54326,7 +54326,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -54351,14 +54351,14 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>37d466c17901ff2a522fb0411245613e7df2ba8c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -54390,7 +54390,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -54422,7 +54422,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -54454,7 +54454,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -54486,7 +54486,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -54518,7 +54518,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -54550,7 +54550,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -54582,7 +54582,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -54614,7 +54614,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -54646,7 +54646,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -54678,7 +54678,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -54710,7 +54710,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -54742,7 +54742,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -54774,7 +54774,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -54806,7 +54806,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -54838,7 +54838,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -54870,7 +54870,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -54902,7 +54902,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -54934,7 +54934,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -54966,7 +54966,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -54998,7 +54998,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -55030,7 +55030,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -55062,7 +55062,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -55094,7 +55094,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -55126,7 +55126,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -55158,7 +55158,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -55190,7 +55190,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -55222,7 +55222,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -55254,7 +55254,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -55286,7 +55286,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -55318,7 +55318,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -55350,7 +55350,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -55382,7 +55382,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -55414,7 +55414,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -55446,7 +55446,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -55478,7 +55478,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -55510,7 +55510,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -55542,7 +55542,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -55574,7 +55574,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -55606,7 +55606,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -55638,7 +55638,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -55670,7 +55670,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -55702,7 +55702,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -55734,7 +55734,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -55766,7 +55766,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -55798,7 +55798,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -55830,7 +55830,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -55862,7 +55862,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -55894,7 +55894,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -55926,7 +55926,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -55958,7 +55958,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -55990,7 +55990,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -56022,7 +56022,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -56054,7 +56054,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -56086,7 +56086,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -56118,7 +56118,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -56150,7 +56150,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -56182,7 +56182,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -56214,7 +56214,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -56246,7 +56246,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -56278,7 +56278,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -56310,7 +56310,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -56342,7 +56342,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -56374,7 +56374,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -56406,7 +56406,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -56438,7 +56438,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -56470,7 +56470,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -56502,7 +56502,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -56534,7 +56534,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -56566,7 +56566,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -56598,7 +56598,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -56630,7 +56630,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -56662,7 +56662,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -56694,7 +56694,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -56726,7 +56726,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -56758,7 +56758,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -56790,7 +56790,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -56822,7 +56822,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -56854,7 +56854,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -56886,7 +56886,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -56918,7 +56918,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -56950,7 +56950,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -56982,7 +56982,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -57014,7 +57014,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -57046,7 +57046,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -57078,7 +57078,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -57110,7 +57110,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -57142,7 +57142,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -57174,7 +57174,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -57206,7 +57206,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -57238,7 +57238,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -57270,7 +57270,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -57302,7 +57302,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -57334,7 +57334,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -57366,7 +57366,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -57398,7 +57398,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -57430,7 +57430,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -57462,7 +57462,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -57494,7 +57494,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -57526,7 +57526,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -57558,7 +57558,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -57590,7 +57590,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -57622,7 +57622,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -57654,7 +57654,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -57686,7 +57686,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -57718,7 +57718,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -57750,7 +57750,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -57782,7 +57782,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -57814,7 +57814,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -57846,7 +57846,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -57878,7 +57878,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -57910,7 +57910,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -57942,7 +57942,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -57974,7 +57974,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -58006,7 +58006,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -58038,7 +58038,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -58070,7 +58070,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -58102,7 +58102,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -58134,7 +58134,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -58166,7 +58166,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -58198,7 +58198,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -58230,7 +58230,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -58262,7 +58262,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -58294,7 +58294,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -58326,7 +58326,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -58358,7 +58358,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -58390,7 +58390,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -58422,7 +58422,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -58454,7 +58454,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -58486,7 +58486,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -58518,7 +58518,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -58550,7 +58550,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -58582,7 +58582,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -58614,7 +58614,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -58646,7 +58646,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -58678,7 +58678,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -58710,7 +58710,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -58742,7 +58742,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -58774,7 +58774,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -58806,7 +58806,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -58838,7 +58838,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -58870,7 +58870,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -58902,7 +58902,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -58934,7 +58934,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -58966,7 +58966,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -58998,7 +58998,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -59030,7 +59030,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -59062,7 +59062,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -59094,7 +59094,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -59126,7 +59126,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -59158,7 +59158,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -59190,7 +59190,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -59222,7 +59222,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -59254,7 +59254,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -59286,7 +59286,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -59318,7 +59318,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -59350,7 +59350,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -59382,7 +59382,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -59414,7 +59414,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -59446,7 +59446,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -59478,7 +59478,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -59510,7 +59510,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -59542,7 +59542,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -59574,7 +59574,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -59606,7 +59606,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -59638,7 +59638,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -59670,7 +59670,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -59702,7 +59702,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -59734,7 +59734,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -59766,7 +59766,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -59798,7 +59798,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -59830,7 +59830,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -59862,7 +59862,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -59894,7 +59894,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -59926,7 +59926,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -59958,7 +59958,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -59990,7 +59990,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -60022,7 +60022,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -60054,7 +60054,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -60086,7 +60086,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -60118,7 +60118,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -60150,7 +60150,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -60182,7 +60182,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -60214,7 +60214,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -60246,7 +60246,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -60278,7 +60278,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -60310,7 +60310,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -60342,7 +60342,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -60374,7 +60374,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -60406,7 +60406,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -60438,7 +60438,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -60470,7 +60470,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -60502,7 +60502,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -60534,7 +60534,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -60566,7 +60566,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -60598,7 +60598,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -60630,7 +60630,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -60662,7 +60662,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -60694,7 +60694,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -60726,7 +60726,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -60758,7 +60758,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -60790,7 +60790,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -60822,7 +60822,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -60854,7 +60854,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -60886,7 +60886,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -60918,7 +60918,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -60950,7 +60950,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -60982,7 +60982,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -61014,7 +61014,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -61046,7 +61046,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -61078,7 +61078,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -61110,7 +61110,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -61142,7 +61142,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -61174,7 +61174,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -61206,7 +61206,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -61238,7 +61238,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -61270,7 +61270,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -61302,7 +61302,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -61334,7 +61334,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -61366,7 +61366,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -61398,7 +61398,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -61430,7 +61430,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -61462,7 +61462,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -61494,7 +61494,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -61526,7 +61526,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -61558,7 +61558,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -61590,7 +61590,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -61622,7 +61622,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -61654,7 +61654,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -61686,7 +61686,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -61718,7 +61718,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -61750,7 +61750,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -61782,7 +61782,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -61814,7 +61814,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -61846,7 +61846,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -61878,7 +61878,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -61910,7 +61910,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -61942,7 +61942,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -61974,7 +61974,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -62006,7 +62006,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -62038,7 +62038,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -62070,7 +62070,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -62102,7 +62102,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -62134,7 +62134,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -62166,7 +62166,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -62198,7 +62198,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -62230,7 +62230,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -62262,7 +62262,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -62294,7 +62294,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -62326,7 +62326,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -62358,7 +62358,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -62390,7 +62390,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -62422,7 +62422,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -62454,7 +62454,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -62486,7 +62486,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -62518,7 +62518,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -62550,7 +62550,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -62582,7 +62582,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -62614,7 +62614,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -62646,7 +62646,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -62678,7 +62678,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -62710,7 +62710,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -62742,7 +62742,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -62774,7 +62774,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -62806,7 +62806,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -62838,7 +62838,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
@@ -62870,7 +62870,7 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
@@ -62902,7 +62902,7 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
@@ -62934,7 +62934,7 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -62966,7 +62966,7 @@
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
@@ -62998,7 +62998,7 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -63030,7 +63030,7 @@
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
@@ -63062,7 +63062,7 @@
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
@@ -63094,7 +63094,7 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
@@ -63126,7 +63126,7 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
@@ -63158,7 +63158,7 @@
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
@@ -63190,7 +63190,7 @@
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -63222,7 +63222,7 @@
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B313" s="3" t="inlineStr">
@@ -63254,7 +63254,7 @@
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
@@ -63286,7 +63286,7 @@
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
@@ -63318,7 +63318,7 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
@@ -63350,7 +63350,7 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B317" s="3" t="inlineStr">
@@ -63382,7 +63382,7 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
@@ -63414,7 +63414,7 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
@@ -63446,7 +63446,7 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
@@ -63478,7 +63478,7 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
@@ -63510,7 +63510,7 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
@@ -63542,7 +63542,7 @@
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B323" s="3" t="inlineStr">
@@ -63574,7 +63574,7 @@
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
@@ -63606,7 +63606,7 @@
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B325" s="3" t="inlineStr">
@@ -63638,7 +63638,7 @@
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
@@ -63670,7 +63670,7 @@
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B327" s="3" t="inlineStr">
@@ -63702,7 +63702,7 @@
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
@@ -63734,7 +63734,7 @@
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B329" s="3" t="inlineStr">
@@ -63766,7 +63766,7 @@
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
@@ -63798,7 +63798,7 @@
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B331" s="3" t="inlineStr">
@@ -63830,7 +63830,7 @@
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
@@ -63862,7 +63862,7 @@
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B333" s="3" t="inlineStr">
@@ -63894,7 +63894,7 @@
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
@@ -63926,7 +63926,7 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B335" s="3" t="inlineStr">
@@ -63958,7 +63958,7 @@
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
@@ -63990,7 +63990,7 @@
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B337" s="3" t="inlineStr">
@@ -64022,7 +64022,7 @@
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
@@ -64054,7 +64054,7 @@
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B339" s="3" t="inlineStr">
@@ -64086,7 +64086,7 @@
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
@@ -64118,7 +64118,7 @@
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B341" s="3" t="inlineStr">
@@ -64150,7 +64150,7 @@
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
@@ -64182,7 +64182,7 @@
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B343" s="3" t="inlineStr">
@@ -64214,7 +64214,7 @@
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
@@ -64246,7 +64246,7 @@
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B345" s="3" t="inlineStr">
@@ -64278,7 +64278,7 @@
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
@@ -64310,7 +64310,7 @@
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B347" s="3" t="inlineStr">
@@ -64342,7 +64342,7 @@
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
@@ -64374,7 +64374,7 @@
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B349" s="3" t="inlineStr">
@@ -64406,7 +64406,7 @@
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
@@ -64438,7 +64438,7 @@
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B351" s="3" t="inlineStr">
@@ -64470,7 +64470,7 @@
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
@@ -64502,7 +64502,7 @@
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B353" s="3" t="inlineStr">
@@ -64534,7 +64534,7 @@
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
@@ -64566,7 +64566,7 @@
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B355" s="3" t="inlineStr">
@@ -64598,7 +64598,7 @@
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
@@ -64630,7 +64630,7 @@
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B357" s="3" t="inlineStr">
@@ -64662,7 +64662,7 @@
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
@@ -64694,7 +64694,7 @@
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B359" s="3" t="inlineStr">
@@ -64726,7 +64726,7 @@
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
@@ -64758,7 +64758,7 @@
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B361" s="3" t="inlineStr">
@@ -64790,7 +64790,7 @@
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
@@ -64822,7 +64822,7 @@
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B363" s="3" t="inlineStr">
@@ -64854,7 +64854,7 @@
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
@@ -64886,7 +64886,7 @@
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B365" s="3" t="inlineStr">
@@ -64918,7 +64918,7 @@
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
@@ -64950,7 +64950,7 @@
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B367" s="3" t="inlineStr">
@@ -64982,7 +64982,7 @@
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
@@ -65014,7 +65014,7 @@
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B369" s="3" t="inlineStr">
@@ -65046,7 +65046,7 @@
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
@@ -65078,7 +65078,7 @@
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B371" s="3" t="inlineStr">
@@ -65110,7 +65110,7 @@
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
@@ -65142,7 +65142,7 @@
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B373" s="3" t="inlineStr">
@@ -65174,7 +65174,7 @@
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
@@ -65206,7 +65206,7 @@
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B375" s="3" t="inlineStr">
@@ -65238,7 +65238,7 @@
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
@@ -65270,7 +65270,7 @@
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B377" s="3" t="inlineStr">
@@ -65302,7 +65302,7 @@
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
@@ -65334,7 +65334,7 @@
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B379" s="3" t="inlineStr">
@@ -65366,7 +65366,7 @@
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
@@ -65398,7 +65398,7 @@
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B381" s="3" t="inlineStr">
@@ -65430,7 +65430,7 @@
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
@@ -65462,7 +65462,7 @@
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B383" s="3" t="inlineStr">
@@ -65494,7 +65494,7 @@
     <row r="384">
       <c r="A384" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
@@ -65526,7 +65526,7 @@
     <row r="385">
       <c r="A385" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B385" s="3" t="inlineStr">
@@ -65558,7 +65558,7 @@
     <row r="386">
       <c r="A386" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
@@ -65590,7 +65590,7 @@
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B387" s="3" t="inlineStr">
@@ -65622,7 +65622,7 @@
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
@@ -65654,7 +65654,7 @@
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B389" s="3" t="inlineStr">
@@ -65686,7 +65686,7 @@
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
@@ -65718,7 +65718,7 @@
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B391" s="3" t="inlineStr">
@@ -65750,7 +65750,7 @@
     <row r="392">
       <c r="A392" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
@@ -65782,7 +65782,7 @@
     <row r="393">
       <c r="A393" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B393" s="3" t="inlineStr">
@@ -65814,7 +65814,7 @@
     <row r="394">
       <c r="A394" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
@@ -65846,7 +65846,7 @@
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B395" s="3" t="inlineStr">
@@ -65878,7 +65878,7 @@
     <row r="396">
       <c r="A396" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
@@ -65910,7 +65910,7 @@
     <row r="397">
       <c r="A397" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B397" s="3" t="inlineStr">
@@ -65942,7 +65942,7 @@
     <row r="398">
       <c r="A398" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
@@ -65974,7 +65974,7 @@
     <row r="399">
       <c r="A399" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B399" s="3" t="inlineStr">
@@ -66006,7 +66006,7 @@
     <row r="400">
       <c r="A400" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
@@ -66038,7 +66038,7 @@
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B401" s="3" t="inlineStr">
@@ -66070,7 +66070,7 @@
     <row r="402">
       <c r="A402" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
@@ -66102,7 +66102,7 @@
     <row r="403">
       <c r="A403" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B403" s="3" t="inlineStr">
@@ -66134,7 +66134,7 @@
     <row r="404">
       <c r="A404" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
@@ -66166,7 +66166,7 @@
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B405" s="3" t="inlineStr">
@@ -66198,7 +66198,7 @@
     <row r="406">
       <c r="A406" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
@@ -66230,7 +66230,7 @@
     <row r="407">
       <c r="A407" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B407" s="3" t="inlineStr">
@@ -66262,7 +66262,7 @@
     <row r="408">
       <c r="A408" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
@@ -66294,7 +66294,7 @@
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B409" s="3" t="inlineStr">
@@ -66326,7 +66326,7 @@
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
@@ -66358,7 +66358,7 @@
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B411" s="3" t="inlineStr">
@@ -66390,7 +66390,7 @@
     <row r="412">
       <c r="A412" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
@@ -66422,7 +66422,7 @@
     <row r="413">
       <c r="A413" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B413" s="3" t="inlineStr">
@@ -66454,7 +66454,7 @@
     <row r="414">
       <c r="A414" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
@@ -66486,7 +66486,7 @@
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B415" s="3" t="inlineStr">
@@ -66518,7 +66518,7 @@
     <row r="416">
       <c r="A416" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B416" s="3" t="inlineStr">
@@ -66550,7 +66550,7 @@
     <row r="417">
       <c r="A417" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B417" s="3" t="inlineStr">
@@ -66582,7 +66582,7 @@
     <row r="418">
       <c r="A418" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -66614,7 +66614,7 @@
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B419" s="3" t="inlineStr">
@@ -66646,7 +66646,7 @@
     <row r="420">
       <c r="A420" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
@@ -66678,7 +66678,7 @@
     <row r="421">
       <c r="A421" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B421" s="3" t="inlineStr">
@@ -66710,7 +66710,7 @@
     <row r="422">
       <c r="A422" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B422" s="3" t="inlineStr">
@@ -66742,7 +66742,7 @@
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B423" s="3" t="inlineStr">
@@ -66774,7 +66774,7 @@
     <row r="424">
       <c r="A424" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
@@ -66806,7 +66806,7 @@
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B425" s="3" t="inlineStr">
@@ -66838,7 +66838,7 @@
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
@@ -66870,7 +66870,7 @@
     <row r="427">
       <c r="A427" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B427" s="3" t="inlineStr">
@@ -66902,7 +66902,7 @@
     <row r="428">
       <c r="A428" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
@@ -66934,7 +66934,7 @@
     <row r="429">
       <c r="A429" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B429" s="3" t="inlineStr">
@@ -66966,7 +66966,7 @@
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
@@ -66998,7 +66998,7 @@
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B431" s="3" t="inlineStr">
@@ -67030,7 +67030,7 @@
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
@@ -67062,7 +67062,7 @@
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B433" s="3" t="inlineStr">
@@ -67094,7 +67094,7 @@
     <row r="434">
       <c r="A434" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
@@ -67126,7 +67126,7 @@
     <row r="435">
       <c r="A435" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B435" s="3" t="inlineStr">
@@ -67158,7 +67158,7 @@
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
@@ -67190,7 +67190,7 @@
     <row r="437">
       <c r="A437" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B437" s="3" t="inlineStr">
@@ -67222,7 +67222,7 @@
     <row r="438">
       <c r="A438" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
@@ -67254,7 +67254,7 @@
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B439" s="3" t="inlineStr">
@@ -67286,7 +67286,7 @@
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -67318,7 +67318,7 @@
     <row r="441">
       <c r="A441" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B441" s="3" t="inlineStr">
@@ -67350,7 +67350,7 @@
     <row r="442">
       <c r="A442" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -67382,7 +67382,7 @@
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B443" s="3" t="inlineStr">
@@ -67414,7 +67414,7 @@
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
@@ -67446,7 +67446,7 @@
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B445" s="3" t="inlineStr">
@@ -67478,7 +67478,7 @@
     <row r="446">
       <c r="A446" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
@@ -67510,7 +67510,7 @@
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B447" s="3" t="inlineStr">
@@ -67542,7 +67542,7 @@
     <row r="448">
       <c r="A448" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
@@ -67574,7 +67574,7 @@
     <row r="449">
       <c r="A449" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B449" s="3" t="inlineStr">
@@ -67606,7 +67606,7 @@
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
@@ -67638,7 +67638,7 @@
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B451" s="3" t="inlineStr">
@@ -67670,7 +67670,7 @@
     <row r="452">
       <c r="A452" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
@@ -67702,7 +67702,7 @@
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B453" s="3" t="inlineStr">
@@ -67734,7 +67734,7 @@
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
@@ -67766,7 +67766,7 @@
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B455" s="3" t="inlineStr">
@@ -67798,7 +67798,7 @@
     <row r="456">
       <c r="A456" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
@@ -67830,7 +67830,7 @@
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B457" s="3" t="inlineStr">
@@ -67862,7 +67862,7 @@
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
@@ -67894,7 +67894,7 @@
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B459" s="3" t="inlineStr">
@@ -67926,7 +67926,7 @@
     <row r="460">
       <c r="A460" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
@@ -67958,7 +67958,7 @@
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B461" s="3" t="inlineStr">
@@ -67990,7 +67990,7 @@
     <row r="462">
       <c r="A462" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
@@ -68022,7 +68022,7 @@
     <row r="463">
       <c r="A463" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B463" s="3" t="inlineStr">
@@ -68054,7 +68054,7 @@
     <row r="464">
       <c r="A464" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B464" s="3" t="inlineStr">
@@ -68086,7 +68086,7 @@
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B465" s="3" t="inlineStr">
@@ -68118,7 +68118,7 @@
     <row r="466">
       <c r="A466" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
@@ -68150,7 +68150,7 @@
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B467" s="3" t="inlineStr">
@@ -68182,7 +68182,7 @@
     <row r="468">
       <c r="A468" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
@@ -68214,7 +68214,7 @@
     <row r="469">
       <c r="A469" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B469" s="3" t="inlineStr">
@@ -68246,7 +68246,7 @@
     <row r="470">
       <c r="A470" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
@@ -68278,7 +68278,7 @@
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B471" s="3" t="inlineStr">
@@ -68310,7 +68310,7 @@
     <row r="472">
       <c r="A472" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B472" s="3" t="inlineStr">
@@ -68342,7 +68342,7 @@
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B473" s="3" t="inlineStr">
@@ -68374,7 +68374,7 @@
     <row r="474">
       <c r="A474" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B474" s="3" t="inlineStr">
@@ -68406,7 +68406,7 @@
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B475" s="3" t="inlineStr">
@@ -68438,7 +68438,7 @@
     <row r="476">
       <c r="A476" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B476" s="3" t="inlineStr">
@@ -68470,7 +68470,7 @@
     <row r="477">
       <c r="A477" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B477" s="3" t="inlineStr">
@@ -68502,7 +68502,7 @@
     <row r="478">
       <c r="A478" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B478" s="3" t="inlineStr">
@@ -68534,7 +68534,7 @@
     <row r="479">
       <c r="A479" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B479" s="3" t="inlineStr">
@@ -68566,7 +68566,7 @@
     <row r="480">
       <c r="A480" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B480" s="3" t="inlineStr">
@@ -68598,7 +68598,7 @@
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B481" s="3" t="inlineStr">
@@ -68630,7 +68630,7 @@
     <row r="482">
       <c r="A482" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B482" s="3" t="inlineStr">
@@ -68662,7 +68662,7 @@
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B483" s="3" t="inlineStr">
@@ -68694,7 +68694,7 @@
     <row r="484">
       <c r="A484" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
@@ -68726,7 +68726,7 @@
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B485" s="3" t="inlineStr">
@@ -68758,7 +68758,7 @@
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B486" s="3" t="inlineStr">
@@ -68790,7 +68790,7 @@
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B487" s="3" t="inlineStr">
@@ -68822,7 +68822,7 @@
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B488" s="3" t="inlineStr">
@@ -68854,7 +68854,7 @@
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B489" s="3" t="inlineStr">
@@ -68886,7 +68886,7 @@
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B490" s="3" t="inlineStr">
@@ -68918,7 +68918,7 @@
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B491" s="3" t="inlineStr">
@@ -68950,7 +68950,7 @@
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B492" s="3" t="inlineStr">
@@ -68982,7 +68982,7 @@
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B493" s="3" t="inlineStr">
@@ -69014,7 +69014,7 @@
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B494" s="3" t="inlineStr">
@@ -69046,7 +69046,7 @@
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B495" s="3" t="inlineStr">
@@ -69078,7 +69078,7 @@
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B496" s="3" t="inlineStr">
@@ -69110,7 +69110,7 @@
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B497" s="3" t="inlineStr">
@@ -69142,7 +69142,7 @@
     <row r="498">
       <c r="A498" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B498" s="3" t="inlineStr">
@@ -69174,7 +69174,7 @@
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B499" s="3" t="inlineStr">
@@ -69206,7 +69206,7 @@
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B500" s="3" t="inlineStr">
@@ -69238,7 +69238,7 @@
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B501" s="3" t="inlineStr">
@@ -69270,7 +69270,7 @@
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B502" s="3" t="inlineStr">
@@ -69302,7 +69302,7 @@
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B503" s="3" t="inlineStr">
@@ -69334,7 +69334,7 @@
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B504" s="3" t="inlineStr">
@@ -69366,7 +69366,7 @@
     <row r="505">
       <c r="A505" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B505" s="3" t="inlineStr">
@@ -69398,7 +69398,7 @@
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B506" s="3" t="inlineStr">
@@ -69430,7 +69430,7 @@
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B507" s="3" t="inlineStr">
@@ -69462,7 +69462,7 @@
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B508" s="3" t="inlineStr">
@@ -69494,7 +69494,7 @@
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B509" s="3" t="inlineStr">
@@ -69526,7 +69526,7 @@
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B510" s="3" t="inlineStr">
@@ -69558,7 +69558,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B511" s="3" t="inlineStr">
@@ -69590,7 +69590,7 @@
     <row r="512">
       <c r="A512" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B512" s="3" t="inlineStr">
@@ -69622,7 +69622,7 @@
     <row r="513">
       <c r="A513" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B513" s="3" t="inlineStr">
@@ -69654,7 +69654,7 @@
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B514" s="3" t="inlineStr">
@@ -69686,7 +69686,7 @@
     <row r="515">
       <c r="A515" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B515" s="3" t="inlineStr">
@@ -69718,7 +69718,7 @@
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B516" s="3" t="inlineStr">
@@ -69750,7 +69750,7 @@
     <row r="517">
       <c r="A517" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B517" s="3" t="inlineStr">
@@ -69782,7 +69782,7 @@
     <row r="518">
       <c r="A518" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B518" s="3" t="inlineStr">
@@ -69814,7 +69814,7 @@
     <row r="519">
       <c r="A519" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B519" s="3" t="inlineStr">
@@ -69846,7 +69846,7 @@
     <row r="520">
       <c r="A520" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B520" s="3" t="inlineStr">
@@ -69878,7 +69878,7 @@
     <row r="521">
       <c r="A521" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B521" s="3" t="inlineStr">
@@ -69910,7 +69910,7 @@
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B522" s="3" t="inlineStr">
@@ -69942,7 +69942,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B523" s="3" t="inlineStr">
@@ -69974,7 +69974,7 @@
     <row r="524">
       <c r="A524" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B524" s="3" t="inlineStr">
@@ -70006,7 +70006,7 @@
     <row r="525">
       <c r="A525" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B525" s="3" t="inlineStr">
@@ -70038,7 +70038,7 @@
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B526" s="3" t="inlineStr">
@@ -70070,7 +70070,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B527" s="3" t="inlineStr">
@@ -70102,7 +70102,7 @@
     <row r="528">
       <c r="A528" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B528" s="3" t="inlineStr">
@@ -70134,7 +70134,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B529" s="3" t="inlineStr">
@@ -70166,7 +70166,7 @@
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B530" s="3" t="inlineStr">
@@ -70198,7 +70198,7 @@
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B531" s="3" t="inlineStr">
@@ -70230,7 +70230,7 @@
     <row r="532">
       <c r="A532" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B532" s="3" t="inlineStr">
@@ -70262,7 +70262,7 @@
     <row r="533">
       <c r="A533" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B533" s="3" t="inlineStr">
@@ -70294,7 +70294,7 @@
     <row r="534">
       <c r="A534" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B534" s="3" t="inlineStr">
@@ -70326,7 +70326,7 @@
     <row r="535">
       <c r="A535" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B535" s="3" t="inlineStr">
@@ -70358,7 +70358,7 @@
     <row r="536">
       <c r="A536" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B536" s="3" t="inlineStr">
@@ -70390,7 +70390,7 @@
     <row r="537">
       <c r="A537" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B537" s="3" t="inlineStr">
@@ -70422,7 +70422,7 @@
     <row r="538">
       <c r="A538" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B538" s="3" t="inlineStr">
@@ -70454,7 +70454,7 @@
     <row r="539">
       <c r="A539" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B539" s="3" t="inlineStr">
@@ -70486,7 +70486,7 @@
     <row r="540">
       <c r="A540" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B540" s="3" t="inlineStr">
@@ -70518,7 +70518,7 @@
     <row r="541">
       <c r="A541" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B541" s="3" t="inlineStr">
@@ -70550,7 +70550,7 @@
     <row r="542">
       <c r="A542" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B542" s="3" t="inlineStr">
@@ -70582,7 +70582,7 @@
     <row r="543">
       <c r="A543" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B543" s="3" t="inlineStr">
@@ -70614,7 +70614,7 @@
     <row r="544">
       <c r="A544" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B544" s="3" t="inlineStr">
@@ -70646,7 +70646,7 @@
     <row r="545">
       <c r="A545" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B545" s="3" t="inlineStr">
@@ -70678,7 +70678,7 @@
     <row r="546">
       <c r="A546" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B546" s="3" t="inlineStr">
@@ -70710,7 +70710,7 @@
     <row r="547">
       <c r="A547" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B547" s="3" t="inlineStr">
@@ -70742,7 +70742,7 @@
     <row r="548">
       <c r="A548" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B548" s="3" t="inlineStr">
@@ -70774,7 +70774,7 @@
     <row r="549">
       <c r="A549" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B549" s="3" t="inlineStr">
@@ -70806,7 +70806,7 @@
     <row r="550">
       <c r="A550" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B550" s="3" t="inlineStr">
@@ -70838,7 +70838,7 @@
     <row r="551">
       <c r="A551" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B551" s="3" t="inlineStr">
@@ -70870,7 +70870,7 @@
     <row r="552">
       <c r="A552" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B552" s="3" t="inlineStr">
@@ -70902,7 +70902,7 @@
     <row r="553">
       <c r="A553" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B553" s="3" t="inlineStr">
@@ -70934,7 +70934,7 @@
     <row r="554">
       <c r="A554" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B554" s="3" t="inlineStr">
@@ -70966,7 +70966,7 @@
     <row r="555">
       <c r="A555" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B555" s="3" t="inlineStr">
@@ -70998,7 +70998,7 @@
     <row r="556">
       <c r="A556" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B556" s="3" t="inlineStr">
@@ -71030,7 +71030,7 @@
     <row r="557">
       <c r="A557" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B557" s="3" t="inlineStr">
@@ -71062,7 +71062,7 @@
     <row r="558">
       <c r="A558" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B558" s="3" t="inlineStr">
@@ -71094,7 +71094,7 @@
     <row r="559">
       <c r="A559" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B559" s="3" t="inlineStr">
@@ -71126,7 +71126,7 @@
     <row r="560">
       <c r="A560" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B560" s="3" t="inlineStr">
@@ -71158,7 +71158,7 @@
     <row r="561">
       <c r="A561" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B561" s="3" t="inlineStr">
@@ -71190,7 +71190,7 @@
     <row r="562">
       <c r="A562" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B562" s="3" t="inlineStr">
@@ -71222,7 +71222,7 @@
     <row r="563">
       <c r="A563" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B563" s="3" t="inlineStr">
@@ -71254,7 +71254,7 @@
     <row r="564">
       <c r="A564" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B564" s="3" t="inlineStr">
@@ -71286,7 +71286,7 @@
     <row r="565">
       <c r="A565" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B565" s="3" t="inlineStr">
@@ -71318,7 +71318,7 @@
     <row r="566">
       <c r="A566" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B566" s="3" t="inlineStr">
@@ -71350,7 +71350,7 @@
     <row r="567">
       <c r="A567" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B567" s="3" t="inlineStr">
@@ -71382,7 +71382,7 @@
     <row r="568">
       <c r="A568" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B568" s="3" t="inlineStr">
@@ -71414,7 +71414,7 @@
     <row r="569">
       <c r="A569" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B569" s="3" t="inlineStr">
@@ -71446,7 +71446,7 @@
     <row r="570">
       <c r="A570" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B570" s="3" t="inlineStr">
@@ -71478,7 +71478,7 @@
     <row r="571">
       <c r="A571" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B571" s="3" t="inlineStr">
@@ -71510,7 +71510,7 @@
     <row r="572">
       <c r="A572" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B572" s="3" t="inlineStr">
@@ -71542,7 +71542,7 @@
     <row r="573">
       <c r="A573" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B573" s="3" t="inlineStr">
@@ -71574,7 +71574,7 @@
     <row r="574">
       <c r="A574" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B574" s="3" t="inlineStr">
@@ -71606,7 +71606,7 @@
     <row r="575">
       <c r="A575" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B575" s="3" t="inlineStr">
@@ -71638,7 +71638,7 @@
     <row r="576">
       <c r="A576" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B576" s="3" t="inlineStr">
@@ -71670,7 +71670,7 @@
     <row r="577">
       <c r="A577" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B577" s="3" t="inlineStr">
@@ -71702,7 +71702,7 @@
     <row r="578">
       <c r="A578" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B578" s="3" t="inlineStr">
@@ -71734,7 +71734,7 @@
     <row r="579">
       <c r="A579" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B579" s="3" t="inlineStr">
@@ -71766,7 +71766,7 @@
     <row r="580">
       <c r="A580" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B580" s="3" t="inlineStr">
@@ -71798,7 +71798,7 @@
     <row r="581">
       <c r="A581" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B581" s="3" t="inlineStr">
@@ -71830,7 +71830,7 @@
     <row r="582">
       <c r="A582" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B582" s="3" t="inlineStr">
@@ -71862,7 +71862,7 @@
     <row r="583">
       <c r="A583" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B583" s="3" t="inlineStr">
@@ -71894,7 +71894,7 @@
     <row r="584">
       <c r="A584" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B584" s="3" t="inlineStr">
@@ -71926,7 +71926,7 @@
     <row r="585">
       <c r="A585" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B585" s="3" t="inlineStr">
@@ -71958,7 +71958,7 @@
     <row r="586">
       <c r="A586" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B586" s="3" t="inlineStr">
@@ -71990,7 +71990,7 @@
     <row r="587">
       <c r="A587" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B587" s="3" t="inlineStr">
@@ -72022,7 +72022,7 @@
     <row r="588">
       <c r="A588" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B588" s="3" t="inlineStr">
@@ -72054,7 +72054,7 @@
     <row r="589">
       <c r="A589" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B589" s="3" t="inlineStr">
@@ -72086,7 +72086,7 @@
     <row r="590">
       <c r="A590" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B590" s="3" t="inlineStr">
@@ -72118,7 +72118,7 @@
     <row r="591">
       <c r="A591" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B591" s="3" t="inlineStr">
@@ -72150,7 +72150,7 @@
     <row r="592">
       <c r="A592" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B592" s="3" t="inlineStr">
@@ -72182,7 +72182,7 @@
     <row r="593">
       <c r="A593" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B593" s="3" t="inlineStr">
@@ -72214,7 +72214,7 @@
     <row r="594">
       <c r="A594" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B594" s="3" t="inlineStr">
@@ -72246,7 +72246,7 @@
     <row r="595">
       <c r="A595" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B595" s="3" t="inlineStr">
@@ -72278,7 +72278,7 @@
     <row r="596">
       <c r="A596" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B596" s="3" t="inlineStr">
@@ -72310,7 +72310,7 @@
     <row r="597">
       <c r="A597" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B597" s="3" t="inlineStr">
@@ -72342,7 +72342,7 @@
     <row r="598">
       <c r="A598" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B598" s="3" t="inlineStr">
@@ -72374,7 +72374,7 @@
     <row r="599">
       <c r="A599" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B599" s="3" t="inlineStr">
@@ -72406,7 +72406,7 @@
     <row r="600">
       <c r="A600" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B600" s="3" t="inlineStr">
@@ -72438,7 +72438,7 @@
     <row r="601">
       <c r="A601" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B601" s="3" t="inlineStr">
@@ -72470,7 +72470,7 @@
     <row r="602">
       <c r="A602" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B602" s="3" t="inlineStr">
@@ -72502,7 +72502,7 @@
     <row r="603">
       <c r="A603" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B603" s="3" t="inlineStr">
@@ -72534,7 +72534,7 @@
     <row r="604">
       <c r="A604" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B604" s="3" t="inlineStr">
@@ -72566,7 +72566,7 @@
     <row r="605">
       <c r="A605" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B605" s="3" t="inlineStr">
@@ -72598,7 +72598,7 @@
     <row r="606">
       <c r="A606" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B606" s="3" t="inlineStr">
@@ -72630,7 +72630,7 @@
     <row r="607">
       <c r="A607" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B607" s="3" t="inlineStr">
@@ -72662,7 +72662,7 @@
     <row r="608">
       <c r="A608" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B608" s="3" t="inlineStr">
@@ -72694,7 +72694,7 @@
     <row r="609">
       <c r="A609" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B609" s="3" t="inlineStr">
@@ -72726,7 +72726,7 @@
     <row r="610">
       <c r="A610" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B610" s="3" t="inlineStr">
@@ -72758,7 +72758,7 @@
     <row r="611">
       <c r="A611" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B611" s="3" t="inlineStr">
@@ -72790,7 +72790,7 @@
     <row r="612">
       <c r="A612" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B612" s="3" t="inlineStr">
@@ -72822,7 +72822,7 @@
     <row r="613">
       <c r="A613" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B613" s="3" t="inlineStr">
@@ -72854,7 +72854,7 @@
     <row r="614">
       <c r="A614" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B614" s="3" t="inlineStr">
@@ -72886,7 +72886,7 @@
     <row r="615">
       <c r="A615" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B615" s="3" t="inlineStr">
@@ -72918,7 +72918,7 @@
     <row r="616">
       <c r="A616" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B616" s="3" t="inlineStr">
@@ -72950,7 +72950,7 @@
     <row r="617">
       <c r="A617" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B617" s="3" t="inlineStr">
@@ -72982,7 +72982,7 @@
     <row r="618">
       <c r="A618" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B618" s="3" t="inlineStr">
@@ -73014,7 +73014,7 @@
     <row r="619">
       <c r="A619" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B619" s="3" t="inlineStr">
@@ -73046,7 +73046,7 @@
     <row r="620">
       <c r="A620" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B620" s="3" t="inlineStr">
@@ -73078,7 +73078,7 @@
     <row r="621">
       <c r="A621" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B621" s="3" t="inlineStr">
@@ -73110,7 +73110,7 @@
     <row r="622">
       <c r="A622" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B622" s="3" t="inlineStr">
@@ -73142,7 +73142,7 @@
     <row r="623">
       <c r="A623" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B623" s="3" t="inlineStr">
@@ -73174,7 +73174,7 @@
     <row r="624">
       <c r="A624" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B624" s="3" t="inlineStr">
@@ -73206,7 +73206,7 @@
     <row r="625">
       <c r="A625" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B625" s="3" t="inlineStr">
@@ -73238,7 +73238,7 @@
     <row r="626">
       <c r="A626" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B626" s="3" t="inlineStr">
@@ -73270,7 +73270,7 @@
     <row r="627">
       <c r="A627" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B627" s="3" t="inlineStr">
@@ -73302,7 +73302,7 @@
     <row r="628">
       <c r="A628" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B628" s="3" t="inlineStr">
@@ -73334,7 +73334,7 @@
     <row r="629">
       <c r="A629" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B629" s="3" t="inlineStr">
@@ -73366,7 +73366,7 @@
     <row r="630">
       <c r="A630" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B630" s="3" t="inlineStr">
@@ -73398,7 +73398,7 @@
     <row r="631">
       <c r="A631" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B631" s="3" t="inlineStr">
@@ -73430,7 +73430,7 @@
     <row r="632">
       <c r="A632" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B632" s="3" t="inlineStr">
@@ -73462,7 +73462,7 @@
     <row r="633">
       <c r="A633" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B633" s="3" t="inlineStr">
@@ -73494,7 +73494,7 @@
     <row r="634">
       <c r="A634" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B634" s="3" t="inlineStr">
@@ -73526,7 +73526,7 @@
     <row r="635">
       <c r="A635" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B635" s="3" t="inlineStr">
@@ -73558,7 +73558,7 @@
     <row r="636">
       <c r="A636" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B636" s="3" t="inlineStr">
@@ -73590,7 +73590,7 @@
     <row r="637">
       <c r="A637" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B637" s="3" t="inlineStr">
@@ -73622,7 +73622,7 @@
     <row r="638">
       <c r="A638" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B638" s="3" t="inlineStr">
@@ -73654,7 +73654,7 @@
     <row r="639">
       <c r="A639" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B639" s="3" t="inlineStr">
@@ -73686,7 +73686,7 @@
     <row r="640">
       <c r="A640" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B640" s="3" t="inlineStr">
@@ -73718,7 +73718,7 @@
     <row r="641">
       <c r="A641" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B641" s="3" t="inlineStr">
@@ -73750,7 +73750,7 @@
     <row r="642">
       <c r="A642" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B642" s="3" t="inlineStr">
@@ -73782,7 +73782,7 @@
     <row r="643">
       <c r="A643" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B643" s="3" t="inlineStr">
@@ -73814,7 +73814,7 @@
     <row r="644">
       <c r="A644" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B644" s="3" t="inlineStr">
@@ -73846,7 +73846,7 @@
     <row r="645">
       <c r="A645" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B645" s="3" t="inlineStr">
@@ -73878,7 +73878,7 @@
     <row r="646">
       <c r="A646" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B646" s="3" t="inlineStr">
@@ -73910,7 +73910,7 @@
     <row r="647">
       <c r="A647" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B647" s="3" t="inlineStr">
@@ -73942,7 +73942,7 @@
     <row r="648">
       <c r="A648" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B648" s="3" t="inlineStr">
@@ -73974,7 +73974,7 @@
     <row r="649">
       <c r="A649" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B649" s="3" t="inlineStr">
@@ -74006,7 +74006,7 @@
     <row r="650">
       <c r="A650" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B650" s="3" t="inlineStr">
@@ -74038,7 +74038,7 @@
     <row r="651">
       <c r="A651" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B651" s="3" t="inlineStr">
@@ -74070,7 +74070,7 @@
     <row r="652">
       <c r="A652" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:39:49</t>
+          <t>2026-10-09 16:40:41</t>
         </is>
       </c>
       <c r="B652" s="3" t="inlineStr">

--- a/college-page-audit-dashboard.xlsx
+++ b/college-page-audit-dashboard.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41 UTC</t>
+          <t>2026-10-09 16:45:10 UTC</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>37d466c17901ff2a522fb0411245613e7df2ba8c</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
       <c r="P135" s="3" t="n">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="O136" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
       <c r="P136" s="3" t="n">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="O137" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
       <c r="P137" s="3" t="n">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
       <c r="P138" s="3" t="n">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
       <c r="P139" s="3" t="n">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
       <c r="P140" s="3" t="n">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
       <c r="P141" s="3" t="n">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
       <c r="P142" s="3" t="n">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
       <c r="P144" s="3" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="O145" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
       <c r="P145" s="3" t="n">
@@ -53270,7 +53270,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -53302,7 +53302,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -53334,7 +53334,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -53366,7 +53366,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -53398,7 +53398,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -53430,7 +53430,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -53462,7 +53462,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -53494,7 +53494,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -53526,7 +53526,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -53558,7 +53558,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -53590,7 +53590,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -53622,7 +53622,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -53654,7 +53654,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -53686,7 +53686,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -53718,7 +53718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -53750,7 +53750,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -53782,7 +53782,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -53814,7 +53814,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -53846,7 +53846,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -53878,7 +53878,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -53910,7 +53910,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -53942,7 +53942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -53974,7 +53974,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -54006,7 +54006,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -54038,7 +54038,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -54070,7 +54070,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -54102,7 +54102,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -54134,7 +54134,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -54166,7 +54166,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -54198,7 +54198,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -54230,7 +54230,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -54262,7 +54262,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -54294,7 +54294,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -54326,7 +54326,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -54351,14 +54351,14 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>37d466c17901ff2a522fb0411245613e7df2ba8c</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -54390,7 +54390,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -54422,7 +54422,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -54454,7 +54454,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -54486,7 +54486,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -54518,7 +54518,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -54550,7 +54550,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -54582,7 +54582,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -54614,7 +54614,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -54646,7 +54646,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -54678,7 +54678,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -54710,7 +54710,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -54742,7 +54742,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -54774,7 +54774,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -54806,7 +54806,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -54838,7 +54838,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -54870,7 +54870,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -54902,7 +54902,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -54934,7 +54934,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -54966,7 +54966,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -54998,7 +54998,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -55030,7 +55030,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -55062,7 +55062,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -55094,7 +55094,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -55126,7 +55126,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -55158,7 +55158,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -55190,7 +55190,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -55222,7 +55222,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -55254,7 +55254,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -55286,7 +55286,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -55318,7 +55318,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -55350,7 +55350,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -55382,7 +55382,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -55414,7 +55414,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -55446,7 +55446,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -55478,7 +55478,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -55510,7 +55510,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -55542,7 +55542,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -55574,7 +55574,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -55606,7 +55606,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -55638,7 +55638,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -55670,7 +55670,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -55702,7 +55702,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -55734,7 +55734,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -55766,7 +55766,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -55798,7 +55798,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -55830,7 +55830,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -55862,7 +55862,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -55894,7 +55894,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -55926,7 +55926,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -55958,7 +55958,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -55990,7 +55990,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -56022,7 +56022,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -56054,7 +56054,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -56086,7 +56086,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -56118,7 +56118,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -56150,7 +56150,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -56182,7 +56182,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -56214,7 +56214,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -56246,7 +56246,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -56278,7 +56278,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -56310,7 +56310,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -56342,7 +56342,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -56374,7 +56374,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -56406,7 +56406,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -56438,7 +56438,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -56470,7 +56470,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -56502,7 +56502,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -56534,7 +56534,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -56566,7 +56566,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -56598,7 +56598,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -56630,7 +56630,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -56662,7 +56662,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -56694,7 +56694,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -56726,7 +56726,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -56758,7 +56758,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -56790,7 +56790,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -56822,7 +56822,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -56854,7 +56854,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -56886,7 +56886,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -56918,7 +56918,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -56950,7 +56950,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -56982,7 +56982,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -57014,7 +57014,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -57046,7 +57046,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -57078,7 +57078,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -57110,7 +57110,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -57142,7 +57142,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -57174,7 +57174,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -57206,7 +57206,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -57238,7 +57238,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -57270,7 +57270,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -57302,7 +57302,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -57334,7 +57334,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -57366,7 +57366,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -57398,7 +57398,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -57430,7 +57430,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -57462,7 +57462,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -57494,7 +57494,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -57526,7 +57526,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -57551,14 +57551,14 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -57583,14 +57583,14 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -57615,14 +57615,14 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -57647,14 +57647,14 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -57679,14 +57679,14 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -57711,14 +57711,14 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -57743,14 +57743,14 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -57775,14 +57775,14 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -57814,7 +57814,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -57839,14 +57839,14 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -57871,14 +57871,14 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>a62526056f6d7f72a2d58753cfc5eadb1343ec6f</t>
+          <t>87fa0103e657574bdd8fe306f383524d682fe5e3</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -57910,7 +57910,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -57942,7 +57942,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -57974,7 +57974,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -58006,7 +58006,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -58038,7 +58038,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -58070,7 +58070,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -58102,7 +58102,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -58134,7 +58134,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -58166,7 +58166,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -58198,7 +58198,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -58230,7 +58230,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -58262,7 +58262,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -58294,7 +58294,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -58326,7 +58326,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -58358,7 +58358,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -58390,7 +58390,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -58422,7 +58422,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -58454,7 +58454,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -58486,7 +58486,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -58518,7 +58518,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -58550,7 +58550,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -58582,7 +58582,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -58614,7 +58614,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -58646,7 +58646,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -58678,7 +58678,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -58710,7 +58710,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -58742,7 +58742,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -58774,7 +58774,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -58806,7 +58806,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -58838,7 +58838,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -58870,7 +58870,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -58902,7 +58902,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -58934,7 +58934,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -58966,7 +58966,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -58998,7 +58998,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -59030,7 +59030,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -59062,7 +59062,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -59094,7 +59094,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -59126,7 +59126,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -59158,7 +59158,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -59190,7 +59190,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -59222,7 +59222,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -59254,7 +59254,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -59286,7 +59286,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -59318,7 +59318,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -59350,7 +59350,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -59382,7 +59382,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -59414,7 +59414,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -59446,7 +59446,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -59478,7 +59478,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -59510,7 +59510,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -59542,7 +59542,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -59574,7 +59574,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -59606,7 +59606,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -59638,7 +59638,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -59670,7 +59670,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -59702,7 +59702,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -59734,7 +59734,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -59766,7 +59766,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -59798,7 +59798,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -59830,7 +59830,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -59862,7 +59862,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -59894,7 +59894,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -59926,7 +59926,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -59958,7 +59958,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -59990,7 +59990,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -60022,7 +60022,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -60054,7 +60054,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -60086,7 +60086,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -60118,7 +60118,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -60150,7 +60150,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -60182,7 +60182,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -60214,7 +60214,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -60246,7 +60246,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -60278,7 +60278,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -60310,7 +60310,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -60342,7 +60342,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -60374,7 +60374,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -60406,7 +60406,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -60438,7 +60438,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -60470,7 +60470,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -60502,7 +60502,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -60534,7 +60534,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -60566,7 +60566,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -60598,7 +60598,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -60630,7 +60630,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -60662,7 +60662,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -60694,7 +60694,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -60726,7 +60726,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -60758,7 +60758,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -60790,7 +60790,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -60822,7 +60822,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -60854,7 +60854,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -60886,7 +60886,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -60918,7 +60918,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -60950,7 +60950,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -60982,7 +60982,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -61014,7 +61014,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -61046,7 +61046,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -61078,7 +61078,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -61110,7 +61110,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -61142,7 +61142,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -61174,7 +61174,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -61206,7 +61206,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -61238,7 +61238,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -61270,7 +61270,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -61302,7 +61302,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -61334,7 +61334,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -61366,7 +61366,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -61398,7 +61398,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -61430,7 +61430,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:40:41</t>
+          <t>2026-10-09 16:45:10</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -61462,7 +61462,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-       